--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="7" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="4" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name=" Dict 1" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="240">
   <si>
     <t>signup_date</t>
   </si>
@@ -759,6 +759,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -791,7 +795,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -816,6 +820,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -826,11 +842,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -870,14 +887,44 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -1376,9 +1423,319 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>45872</v>
+      </c>
+      <c r="D2" s="10" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>45903</v>
+      </c>
+      <c r="D3" s="10" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G3">
+        <f>Loan!D28</f>
+        <v>27133.333333333332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3">
+        <v>45933</v>
+      </c>
+      <c r="D4" s="10" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>45903</v>
+      </c>
+      <c r="D5" s="10" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>45933</v>
+      </c>
+      <c r="D6" s="10" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3">
+        <v>45964</v>
+      </c>
+      <c r="D7" s="10" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="28">
+        <v>1</v>
+      </c>
+      <c r="C8" s="29">
+        <v>45874</v>
+      </c>
+      <c r="D8" s="30" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="28">
+        <v>2</v>
+      </c>
+      <c r="C9" s="29">
+        <v>45905</v>
+      </c>
+      <c r="D9" s="30" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="28">
+        <v>3</v>
+      </c>
+      <c r="C10" s="29">
+        <v>45935</v>
+      </c>
+      <c r="D10" s="31" t="e">
+        <f>D9</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="13">
+        <v>45937</v>
+      </c>
+      <c r="D11" s="6" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="13">
+        <v>45968</v>
+      </c>
+      <c r="D12" s="6" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="13">
+        <v>45998</v>
+      </c>
+      <c r="D13" s="6" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6" t="e">
+        <f>#REF!/#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2753,17 +3110,17 @@
     <col min="2" max="2" width="11.26953125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1796875" style="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="26" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
@@ -2776,7 +3133,7 @@
       <c r="D1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F1" s="5" t="s">
@@ -2785,10 +3142,10 @@
       <c r="G1" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="25" t="s">
         <v>97</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -2814,7 +3171,7 @@
       <c r="D2" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="22">
         <v>300000</v>
       </c>
       <c r="F2" s="7">
@@ -2823,10 +3180,10 @@
       <c r="G2" s="7">
         <v>725</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="24">
         <v>20000</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="24">
         <v>29500</v>
       </c>
       <c r="J2" s="7" t="s">
@@ -2852,7 +3209,7 @@
       <c r="D3" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="22">
         <v>100000</v>
       </c>
       <c r="F3" s="7">
@@ -2861,10 +3218,10 @@
       <c r="G3" s="7">
         <v>650</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="24">
         <v>15000</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="24">
         <v>18500</v>
       </c>
       <c r="J3" s="7" t="s">
@@ -2890,7 +3247,7 @@
       <c r="D4" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="22">
         <v>500000</v>
       </c>
       <c r="F4" s="7">
@@ -2899,10 +3256,10 @@
       <c r="G4" s="7">
         <v>780</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="24">
         <v>30000</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="24">
         <v>37000</v>
       </c>
       <c r="J4" s="7" t="s">
@@ -2928,7 +3285,7 @@
       <c r="D5" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="22">
         <v>600000</v>
       </c>
       <c r="F5" s="7">
@@ -2937,10 +3294,10 @@
       <c r="G5" s="7">
         <v>590</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="24">
         <v>45000</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="24">
         <v>43000</v>
       </c>
       <c r="J5" s="7" t="s">
@@ -2966,7 +3323,7 @@
       <c r="D6" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="22">
         <v>80000</v>
       </c>
       <c r="F6" s="7">
@@ -2975,10 +3332,10 @@
       <c r="G6" s="7">
         <v>520</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="24">
         <v>22000</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="24">
         <v>28500</v>
       </c>
       <c r="J6" s="7" t="s">
@@ -3004,7 +3361,7 @@
       <c r="D7" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="22">
         <v>700000</v>
       </c>
       <c r="F7" s="7">
@@ -3013,10 +3370,10 @@
       <c r="G7" s="7">
         <v>735</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="24">
         <v>35000</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="24">
         <v>47000</v>
       </c>
       <c r="J7" s="7" t="s">
@@ -3042,7 +3399,7 @@
       <c r="D8" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="22">
         <v>200000</v>
       </c>
       <c r="F8" s="7">
@@ -3051,10 +3408,10 @@
       <c r="G8" s="7">
         <v>680</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="24">
         <v>12000</v>
       </c>
-      <c r="I8" s="7">
+      <c r="I8" s="24">
         <v>21000</v>
       </c>
       <c r="J8" s="7" t="s">
@@ -3080,7 +3437,7 @@
       <c r="D9" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="22">
         <v>1000000</v>
       </c>
       <c r="F9" s="7">
@@ -3089,10 +3446,10 @@
       <c r="G9" s="7">
         <v>760</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="24">
         <v>60000</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="24">
         <v>52000</v>
       </c>
       <c r="J9" s="7" t="s">
@@ -3118,7 +3475,7 @@
       <c r="D10" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="22">
         <v>120000</v>
       </c>
       <c r="F10" s="7">
@@ -3127,10 +3484,10 @@
       <c r="G10" s="7">
         <v>605</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="24">
         <v>18000</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="24">
         <v>21000</v>
       </c>
       <c r="J10" s="7" t="s">
@@ -3156,7 +3513,7 @@
       <c r="D11" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="22">
         <v>350000</v>
       </c>
       <c r="F11" s="7">
@@ -3165,10 +3522,10 @@
       <c r="G11" s="7">
         <v>745</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="24">
         <v>20000</v>
       </c>
-      <c r="I11" s="7">
+      <c r="I11" s="24">
         <v>33000</v>
       </c>
       <c r="J11" s="7" t="s">
@@ -3194,7 +3551,7 @@
       <c r="D12" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="22">
         <v>120000</v>
       </c>
       <c r="F12" s="7">
@@ -3203,10 +3560,10 @@
       <c r="G12" s="7">
         <v>730</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="24">
         <v>15000</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="24">
         <v>22000</v>
       </c>
       <c r="J12" s="7" t="s">
@@ -3232,7 +3589,7 @@
       <c r="D13" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="22">
         <v>900000</v>
       </c>
       <c r="F13" s="7">
@@ -3241,10 +3598,10 @@
       <c r="G13" s="7">
         <v>790</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="24">
         <v>40000</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="24">
         <v>61000</v>
       </c>
       <c r="J13" s="7" t="s">
@@ -3270,7 +3627,7 @@
       <c r="D14" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="22">
         <v>250000</v>
       </c>
       <c r="F14" s="7">
@@ -3279,10 +3636,10 @@
       <c r="G14" s="7">
         <v>540</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="24">
         <v>25000</v>
       </c>
-      <c r="I14" s="7">
+      <c r="I14" s="24">
         <v>26000</v>
       </c>
       <c r="J14" s="7" t="s">
@@ -3308,7 +3665,7 @@
       <c r="D15" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="22">
         <v>150000</v>
       </c>
       <c r="F15" s="7">
@@ -3317,10 +3674,10 @@
       <c r="G15" s="7">
         <v>770</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="24">
         <v>18000</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="24">
         <v>24000</v>
       </c>
       <c r="J15" s="7" t="s">
@@ -3346,7 +3703,7 @@
       <c r="D16" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="22">
         <v>300000</v>
       </c>
       <c r="F16" s="7">
@@ -3355,10 +3712,10 @@
       <c r="G16" s="7">
         <v>610</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="24">
         <v>28000</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="24">
         <v>31000</v>
       </c>
       <c r="J16" s="7" t="s">
@@ -3554,7 +3911,7 @@
       <c r="I4" s="8">
         <v>46300</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="17" t="s">
         <v>225</v>
       </c>
       <c r="K4" s="7">
@@ -4196,7 +4553,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>238</v>
       </c>
     </row>
@@ -4250,16 +4607,13 @@
         <f>K2/H2</f>
         <v>19000</v>
       </c>
-      <c r="F25" t="s">
-        <v>66</v>
-      </c>
       <c r="G25" s="13"/>
       <c r="H25" s="16">
-        <f>SUMIFS(D25:D27, A25:A27,F25, C25:C27, "&lt;="&amp;C27)</f>
+        <f>SUMIFS(D25:D27, A25:A27,A2, C25:C27, "&lt;="&amp;C27)</f>
         <v>57000</v>
       </c>
       <c r="I25" s="6">
-        <f>SUMIFS(D25:D27, A25:A27,F25, C25:C27, "&lt;="&amp;C27)</f>
+        <f>SUMIFS(D25:D27, A25:A27,A2, C25:C27, "&lt;="&amp;C27)</f>
         <v>57000</v>
       </c>
       <c r="J25" s="20" t="s">
@@ -4319,7 +4673,7 @@
         <f>SUMIFS(D28:D30, A28:A30,A3,C28:C30,"&lt;="&amp;C30)</f>
         <v>81400</v>
       </c>
-      <c r="J28" s="18" t="s">
+      <c r="J28" s="19" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4354,46 +4708,46 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="28">
         <v>1</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="29">
         <v>45874</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="30">
         <f>K4/H4</f>
         <v>32666.666666666668</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="28">
         <v>2</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="29">
         <v>45905</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="30">
         <f>K4/H4</f>
         <v>32666.666666666668</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="28">
         <v>3</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="29">
         <v>45935</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="31">
         <f>D32</f>
         <v>32666.666666666668</v>
       </c>
@@ -4405,7 +4759,7 @@
         <f>SUMIFS(D31:D32,A31:A32, A4,C31:C32, "&lt;="&amp;C33)</f>
         <v>65333.333333333336</v>
       </c>
-      <c r="J33" s="19">
+      <c r="J33" s="27">
         <f>MAX(0,H33-I33)</f>
         <v>32666.666666666664</v>
       </c>

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="4" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="4" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name=" Dict 1" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="241">
   <si>
     <t>signup_date</t>
   </si>
@@ -753,6 +753,9 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>repayment_date</t>
   </si>
 </sst>
 </file>
@@ -761,7 +764,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -847,7 +850,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -895,22 +898,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -922,6 +925,22 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1423,317 +1442,307 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" style="9"/>
+    <col min="6" max="6" width="14.90625" style="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="34" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="7">
         <v>1</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="8">
         <v>45872</v>
       </c>
-      <c r="D2" s="10" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="D2" s="35">
+        <f>Loan!D25</f>
+        <v>19000</v>
+      </c>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="7">
         <v>2</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="8">
         <v>45903</v>
       </c>
-      <c r="D3" s="10" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G3">
+      <c r="D3" s="35">
+        <f>Loan!D25</f>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="7">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8">
+        <v>45933</v>
+      </c>
+      <c r="D4" s="35">
+        <f>Loan!D25</f>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="7">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
+        <v>45903</v>
+      </c>
+      <c r="D5" s="35">
+        <f>E6</f>
+        <v>27133.333333333332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2</v>
+      </c>
+      <c r="C6" s="8">
+        <v>45933</v>
+      </c>
+      <c r="D6" s="35">
+        <f>E6</f>
+        <v>27133.333333333332</v>
+      </c>
+      <c r="E6" s="9">
         <f>Loan!D28</f>
         <v>27133.333333333332</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="7">
         <v>3</v>
       </c>
-      <c r="C4" s="3">
-        <v>45933</v>
-      </c>
-      <c r="D4" s="10" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="C7" s="8">
+        <v>45964</v>
+      </c>
+      <c r="D7" s="35">
+        <f>E6</f>
+        <v>27133.333333333332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="33">
         <v>1</v>
       </c>
-      <c r="C5" s="3">
-        <v>45903</v>
-      </c>
-      <c r="D5" s="10" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="C8" s="32">
+        <v>45874</v>
+      </c>
+      <c r="D8" s="36">
+        <f>E8</f>
+        <v>32666.666666666668</v>
+      </c>
+      <c r="E8" s="9">
+        <f>Loan!D31</f>
+        <v>32666.666666666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="33">
         <v>2</v>
       </c>
-      <c r="C6" s="3">
-        <v>45933</v>
-      </c>
-      <c r="D6" s="10" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="C9" s="32">
+        <v>45905</v>
+      </c>
+      <c r="D9" s="36">
+        <f>E8</f>
+        <v>32666.666666666668</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="33">
         <v>3</v>
       </c>
-      <c r="C7" s="3">
-        <v>45964</v>
-      </c>
-      <c r="D7" s="10" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="28">
-        <v>1</v>
-      </c>
-      <c r="C8" s="29">
-        <v>45874</v>
-      </c>
-      <c r="D8" s="30" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="28">
-        <v>2</v>
-      </c>
-      <c r="C9" s="29">
-        <v>45905</v>
-      </c>
-      <c r="D9" s="30" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="28">
-        <v>3</v>
-      </c>
-      <c r="C10" s="29">
+      <c r="C10" s="32">
         <v>45935</v>
       </c>
-      <c r="D10" s="31" t="e">
+      <c r="D10" s="37">
         <f>D9</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+        <v>32666.666666666668</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="7">
         <v>1</v>
       </c>
       <c r="C11" s="13">
         <v>45937</v>
       </c>
-      <c r="D11" s="6" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="D11" s="26">
+        <f>E11</f>
+        <v>42066.666666666664</v>
+      </c>
+      <c r="E11" s="9">
+        <f>Loan!D34</f>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="7">
         <v>2</v>
       </c>
       <c r="C12" s="13">
         <v>45968</v>
       </c>
-      <c r="D12" s="6" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="D12" s="26">
+        <f>E11</f>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="7">
         <v>3</v>
       </c>
       <c r="C13" s="13">
         <v>45998</v>
       </c>
-      <c r="D13" s="6" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+      <c r="D13" s="26">
+        <f>E11</f>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="7">
         <v>1</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="D14" s="26" t="e">
+        <f>Loan!D37+Installment!F1</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="7">
         <v>2</v>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="D15" s="26" t="e">
+        <f>D14</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="7">
         <v>3</v>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6" t="e">
-        <f>#REF!/#REF!</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="D16" s="26" t="e">
+        <f>D15</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -24,6 +24,7 @@
     <sheet name="Installment" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1670,9 +1671,16 @@
       <c r="B14" s="7">
         <v>1</v>
       </c>
-      <c r="D14" s="26" t="e">
-        <f>Loan!D37+Installment!F1</f>
-        <v>#VALUE!</v>
+      <c r="C14" s="13">
+        <v>45937</v>
+      </c>
+      <c r="D14" s="26">
+        <f>D15</f>
+        <v>49533.333333333336</v>
+      </c>
+      <c r="E14" s="9">
+        <f>Loan!D37</f>
+        <v>49533.333333333336</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1682,9 +1690,12 @@
       <c r="B15" s="7">
         <v>2</v>
       </c>
-      <c r="D15" s="26" t="e">
-        <f>D14</f>
-        <v>#VALUE!</v>
+      <c r="C15" s="13">
+        <v>45968</v>
+      </c>
+      <c r="D15" s="26">
+        <f>E14</f>
+        <v>49533.333333333336</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1694,9 +1705,12 @@
       <c r="B16" s="7">
         <v>3</v>
       </c>
-      <c r="D16" s="26" t="e">
+      <c r="C16" s="13">
+        <v>45998</v>
+      </c>
+      <c r="D16" s="26">
         <f>D15</f>
-        <v>#VALUE!</v>
+        <v>49533.333333333336</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -24,7 +24,6 @@
     <sheet name="Installment" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="261">
   <si>
     <t>signup_date</t>
   </si>
@@ -291,21 +290,9 @@
     <t>C010</t>
   </si>
   <si>
-    <t>Referral</t>
-  </si>
-  <si>
     <t>Business Owner</t>
   </si>
   <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>Agent</t>
-  </si>
-  <si>
-    <t>Instagram</t>
-  </si>
-  <si>
     <t>Delta</t>
   </si>
   <si>
@@ -354,18 +341,12 @@
     <t>Business Loan</t>
   </si>
   <si>
-    <t>Declined</t>
-  </si>
-  <si>
     <t>Low Bureau Score</t>
   </si>
   <si>
     <t>A005</t>
   </si>
   <si>
-    <t>High Debt-to-Income</t>
-  </si>
-  <si>
     <t>A011</t>
   </si>
   <si>
@@ -375,18 +356,12 @@
     <t>A013</t>
   </si>
   <si>
-    <t>Poor Credit History</t>
-  </si>
-  <si>
     <t>A014</t>
   </si>
   <si>
     <t>A015</t>
   </si>
   <si>
-    <t>High Debt Burden</t>
-  </si>
-  <si>
     <t>Anambra</t>
   </si>
   <si>
@@ -705,27 +680,6 @@
     <t>total_amount</t>
   </si>
   <si>
-    <t>repayment_status</t>
-  </si>
-  <si>
-    <t>on-time</t>
-  </si>
-  <si>
-    <t>late</t>
-  </si>
-  <si>
-    <t>partial</t>
-  </si>
-  <si>
-    <t>missed</t>
-  </si>
-  <si>
-    <t>cured</t>
-  </si>
-  <si>
-    <t>prepaid</t>
-  </si>
-  <si>
     <t>processing_fees</t>
   </si>
   <si>
@@ -753,10 +707,115 @@
     <t>Installments</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>repayment_date</t>
+    <t>Abia</t>
+  </si>
+  <si>
+    <t>Uyo</t>
+  </si>
+  <si>
+    <t>Kwara</t>
+  </si>
+  <si>
+    <t>customer_names</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solomon Yakubu </t>
+  </si>
+  <si>
+    <t>Aminat Abdul</t>
+  </si>
+  <si>
+    <t>Jabari Woji</t>
+  </si>
+  <si>
+    <t>Usman Hazeem</t>
+  </si>
+  <si>
+    <t>Ademola Adeola</t>
+  </si>
+  <si>
+    <t>Onyekachi Anyanwu</t>
+  </si>
+  <si>
+    <t>Olivia Idu</t>
+  </si>
+  <si>
+    <t>Amarachi Oke</t>
+  </si>
+  <si>
+    <t>Oyin Lekan</t>
+  </si>
+  <si>
+    <t>Ambrose Okafor</t>
+  </si>
+  <si>
+    <t>Grace Nwaji</t>
+  </si>
+  <si>
+    <t>Nsikak Effiong</t>
+  </si>
+  <si>
+    <t>Clinton Onyekwere</t>
+  </si>
+  <si>
+    <t>Zechariah Odo</t>
+  </si>
+  <si>
+    <t>Mubarak Damilola</t>
+  </si>
+  <si>
+    <t>Arinze Onyema</t>
+  </si>
+  <si>
+    <t>Edafe Isoghene</t>
+  </si>
+  <si>
+    <t>Rufai Hamzat</t>
+  </si>
+  <si>
+    <t>Tunde Abiola</t>
+  </si>
+  <si>
+    <t>Clement Orji</t>
+  </si>
+  <si>
+    <t>LO16</t>
+  </si>
+  <si>
+    <t>LO11</t>
+  </si>
+  <si>
+    <t>Payment Date</t>
+  </si>
+  <si>
+    <t>Null</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>On-time</t>
+  </si>
+  <si>
+    <t>Late</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Missed</t>
+  </si>
+  <si>
+    <t>Prepaid</t>
+  </si>
+  <si>
+    <t>Cured</t>
+  </si>
+  <si>
+    <t>Payment_amount</t>
+  </si>
+  <si>
+    <t>outstanding</t>
   </si>
 </sst>
 </file>
@@ -767,7 +826,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -798,8 +857,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -808,25 +878,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -851,7 +903,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -894,14 +946,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -915,33 +959,49 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1264,7 +1324,7 @@
         <v>36</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>38</v>
@@ -1304,7 +1364,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>38</v>
@@ -1344,7 +1404,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>38</v>
@@ -1364,7 +1424,7 @@
         <v>48</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>38</v>
@@ -1384,7 +1444,7 @@
         <v>50</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>38</v>
@@ -1424,7 +1484,7 @@
         <v>54</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>38</v>
@@ -1443,35 +1503,64 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" style="9"/>
-    <col min="6" max="6" width="14.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.453125" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="6" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" style="9"/>
+    <col min="12" max="12" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>259</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="K1" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D1" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="L1" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>66</v>
       </c>
@@ -1481,13 +1570,30 @@
       <c r="C2" s="8">
         <v>45872</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="28">
         <f>Loan!D25</f>
         <v>19000</v>
       </c>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E2" s="36">
+        <v>45872</v>
+      </c>
+      <c r="F2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G2" s="38">
+        <f>D2</f>
+        <v>19000</v>
+      </c>
+      <c r="H2" s="38">
+        <f>MAX(0,G2-D2)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="22">
+        <f>SUMIFS(D2:D2,A2:A2,A2)</f>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>66</v>
       </c>
@@ -1497,12 +1603,30 @@
       <c r="C3" s="8">
         <v>45903</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="28">
         <f>Loan!D25</f>
         <v>19000</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E3" s="36">
+        <v>45903</v>
+      </c>
+      <c r="F3" t="s">
+        <v>253</v>
+      </c>
+      <c r="G3" s="38">
+        <f>D3</f>
+        <v>19000</v>
+      </c>
+      <c r="H3" s="38">
+        <f>MAX(0,D3-G3)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="22">
+        <f>SUMIFS(D2:D3,A2:A3,A3)</f>
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>66</v>
       </c>
@@ -1512,12 +1636,30 @@
       <c r="C4" s="8">
         <v>45933</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="28">
         <f>Loan!D25</f>
         <v>19000</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E4" s="36">
+        <v>45933</v>
+      </c>
+      <c r="F4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G4" s="38">
+        <f>D4</f>
+        <v>19000</v>
+      </c>
+      <c r="H4" s="38">
+        <f>MAX(0,D4-G4)</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="22">
+        <f>SUMIFS(D2:D4,A2:A4,A4)</f>
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>70</v>
       </c>
@@ -1527,12 +1669,38 @@
       <c r="C5" s="8">
         <v>45903</v>
       </c>
-      <c r="D5" s="35">
-        <f>E6</f>
+      <c r="D5" s="28">
+        <f>Loan!J3/Loan!H3</f>
         <v>27133.333333333332</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E5" s="36">
+        <v>45903</v>
+      </c>
+      <c r="F5" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="38">
+        <f>MAX(0,D5-G5)</f>
+        <v>27133.333333333332</v>
+      </c>
+      <c r="I5" s="22">
+        <f>SUMIFS(D5:D5,A5,A5:A5)</f>
+        <v>27133.333333333332</v>
+      </c>
+      <c r="J5" s="38">
+        <f>MAX(0,G5-H5)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="41">
+        <f>I5-J5</f>
+        <v>27133.333333333332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>70</v>
       </c>
@@ -1542,16 +1710,38 @@
       <c r="C6" s="8">
         <v>45933</v>
       </c>
-      <c r="D6" s="35">
-        <f>E6</f>
+      <c r="D6" s="28">
+        <f>D5</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="E6" s="9">
-        <f>Loan!D28</f>
+      <c r="E6" s="36">
+        <v>45933</v>
+      </c>
+      <c r="F6" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="38">
+        <f t="shared" ref="H6:H7" si="0">MAX(0,D6-G6)</f>
         <v>27133.333333333332</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I6" s="22">
+        <f>SUMIFS(D5:D6,A5:A6,A5)</f>
+        <v>54266.666666666664</v>
+      </c>
+      <c r="J6" s="38">
+        <f t="shared" ref="J6:J7" si="1">MAX(0,G6-H6)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="41">
+        <f>I6-J6</f>
+        <v>54266.666666666664</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>70</v>
       </c>
@@ -1561,61 +1751,158 @@
       <c r="C7" s="8">
         <v>45964</v>
       </c>
-      <c r="D7" s="35">
-        <f>E6</f>
+      <c r="D7" s="28">
+        <f>D5</f>
         <v>27133.333333333332</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
+      <c r="E7" s="36">
+        <v>45964</v>
+      </c>
+      <c r="F7" t="s">
+        <v>254</v>
+      </c>
+      <c r="G7" s="6">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="38">
+        <f t="shared" si="0"/>
+        <v>27133.333333333332</v>
+      </c>
+      <c r="I7" s="22">
+        <f>SUMIFS(D5:D7,A5:A7,A7)</f>
+        <v>81400</v>
+      </c>
+      <c r="J7" s="38">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="41">
+        <f>I7-J7</f>
+        <v>81400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="30">
         <v>1</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="31">
         <v>45874</v>
       </c>
-      <c r="D8" s="36">
-        <f>E8</f>
+      <c r="D8" s="32">
+        <f>Loan!J4/Loan!H4</f>
         <v>32666.666666666668</v>
       </c>
-      <c r="E8" s="9">
-        <f>Loan!D31</f>
+      <c r="E8" s="36">
+        <v>45874</v>
+      </c>
+      <c r="F8" t="s">
+        <v>255</v>
+      </c>
+      <c r="G8" s="22">
+        <v>13000</v>
+      </c>
+      <c r="H8" s="22">
+        <f>MAX(0,D8-G8)</f>
+        <v>19666.666666666668</v>
+      </c>
+      <c r="I8" s="22">
+        <f>SUMIFS(D8:D8,A8:A8,A8)</f>
         <v>32666.666666666668</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="33" t="s">
+      <c r="J8" s="38">
+        <f>G8</f>
+        <v>13000</v>
+      </c>
+      <c r="K8" s="41">
+        <f>I8-J8</f>
+        <v>19666.666666666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="30">
         <v>2</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="31">
         <v>45905</v>
       </c>
-      <c r="D9" s="36">
-        <f>E8</f>
+      <c r="D9" s="32">
+        <f>D8</f>
         <v>32666.666666666668</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="33" t="s">
+      <c r="E9" s="36">
+        <v>45905</v>
+      </c>
+      <c r="F9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G9" s="38">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="22">
+        <f t="shared" ref="H9:H10" si="2">MAX(0,D9-G9)</f>
+        <v>22666.666666666668</v>
+      </c>
+      <c r="I9" s="22">
+        <f>SUMIFS(D8:D9,A8:A9,A9)</f>
+        <v>65333.333333333336</v>
+      </c>
+      <c r="J9" s="38">
+        <f>G8+G9</f>
+        <v>23000</v>
+      </c>
+      <c r="K9" s="41">
+        <f>I9-J9</f>
+        <v>42333.333333333336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="33">
-        <v>3</v>
-      </c>
-      <c r="C10" s="32">
+      <c r="B10" s="30">
+        <v>3</v>
+      </c>
+      <c r="C10" s="31">
         <v>45935</v>
       </c>
-      <c r="D10" s="37">
-        <f>D9</f>
+      <c r="D10" s="33">
+        <f>D8</f>
         <v>32666.666666666668</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E10" s="36">
+        <v>45935</v>
+      </c>
+      <c r="F10" t="s">
+        <v>255</v>
+      </c>
+      <c r="G10" s="22">
+        <v>14000</v>
+      </c>
+      <c r="H10" s="22">
+        <f t="shared" si="2"/>
+        <v>18666.666666666668</v>
+      </c>
+      <c r="I10" s="22">
+        <f>SUMIFS(D8:D10,A8:A10,A10)</f>
+        <v>98000</v>
+      </c>
+      <c r="J10" s="38">
+        <f>G8+G9+G10</f>
+        <v>37000</v>
+      </c>
+      <c r="K10" s="41">
+        <f>I10-J10</f>
+        <v>61000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>74</v>
       </c>
@@ -1625,16 +1912,30 @@
       <c r="C11" s="13">
         <v>45937</v>
       </c>
-      <c r="D11" s="26">
-        <f>E11</f>
+      <c r="D11" s="22">
+        <f>Loan!J5/Loan!H5</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E11" s="9">
-        <f>Loan!D34</f>
+      <c r="E11" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11" t="s">
+        <v>256</v>
+      </c>
+      <c r="G11" s="38">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="38">
+        <f>D11+G11</f>
         <v>42066.666666666664</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="I11" s="22">
+        <f>D11</f>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
         <v>74</v>
       </c>
@@ -1644,12 +1945,30 @@
       <c r="C12" s="13">
         <v>45968</v>
       </c>
-      <c r="D12" s="26">
-        <f>E11</f>
+      <c r="D12" s="22">
+        <f>D11</f>
         <v>42066.666666666664</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E12" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" t="s">
+        <v>256</v>
+      </c>
+      <c r="G12" s="38">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="38">
+        <f t="shared" ref="H12:H13" si="3">D12+G12</f>
+        <v>42066.666666666664</v>
+      </c>
+      <c r="I12" s="22">
+        <f t="shared" ref="I12:I13" si="4">D12</f>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>74</v>
       </c>
@@ -1659,12 +1978,30 @@
       <c r="C13" s="13">
         <v>45998</v>
       </c>
-      <c r="D13" s="26">
-        <f>E11</f>
+      <c r="D13" s="22">
+        <f>D11</f>
         <v>42066.666666666664</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E13" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="F13" t="s">
+        <v>256</v>
+      </c>
+      <c r="G13" s="38">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="38">
+        <f t="shared" si="3"/>
+        <v>42066.666666666664</v>
+      </c>
+      <c r="I13" s="22">
+        <f t="shared" si="4"/>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>76</v>
       </c>
@@ -1674,92 +2011,1040 @@
       <c r="C14" s="13">
         <v>45937</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="22">
+        <f>Loan!J6/Loan!H6</f>
+        <v>49533.333333333336</v>
+      </c>
+      <c r="E14" s="36">
+        <v>45718</v>
+      </c>
+      <c r="F14" t="s">
+        <v>257</v>
+      </c>
+      <c r="I14" s="22">
+        <f>D14</f>
+        <v>49533.333333333336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="7">
+        <v>2</v>
+      </c>
+      <c r="C15" s="13">
+        <v>45968</v>
+      </c>
+      <c r="D15" s="22">
+        <f>D14</f>
+        <v>49533.333333333336</v>
+      </c>
+      <c r="E15" s="36">
+        <v>45748</v>
+      </c>
+      <c r="F15" t="s">
+        <v>257</v>
+      </c>
+      <c r="I15" s="22">
+        <f t="shared" ref="I15:I16" si="5">D15</f>
+        <v>49533.333333333336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="7">
+        <v>3</v>
+      </c>
+      <c r="C16" s="13">
+        <v>45998</v>
+      </c>
+      <c r="D16" s="22">
         <f>D15</f>
         <v>49533.333333333336</v>
       </c>
-      <c r="E14" s="9">
-        <f>Loan!D37</f>
+      <c r="E16" s="36">
+        <v>45778</v>
+      </c>
+      <c r="F16" t="s">
+        <v>257</v>
+      </c>
+      <c r="I16" s="22">
+        <f t="shared" si="5"/>
         <v>49533.333333333336</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="7">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="22">
+        <f>Loan!J7/Loan!H7</f>
+        <v>57666.666666666664</v>
+      </c>
+      <c r="F17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I17" s="22">
+        <f>D17</f>
+        <v>57666.666666666664</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="7">
         <v>2</v>
       </c>
-      <c r="C15" s="13">
-        <v>45968</v>
-      </c>
-      <c r="D15" s="26">
-        <f>E14</f>
-        <v>49533.333333333336</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="7">
-        <v>3</v>
-      </c>
-      <c r="C16" s="13">
-        <v>45998</v>
-      </c>
-      <c r="D16" s="26">
-        <f>D15</f>
-        <v>49533.333333333336</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="D18" s="22">
+        <f>Loan!J7/Loan!H7</f>
+        <v>57666.666666666664</v>
+      </c>
+      <c r="E18" s="36">
+        <v>45760</v>
+      </c>
+      <c r="F18" t="s">
+        <v>258</v>
+      </c>
+      <c r="I18" s="22">
+        <f t="shared" ref="I18:I19" si="6">D18</f>
+        <v>57666.666666666664</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="7">
+        <v>3</v>
+      </c>
+      <c r="D19" s="22">
+        <f>Loan!J7/Loan!H7</f>
+        <v>57666.666666666664</v>
+      </c>
+      <c r="E19" s="36">
+        <v>45790</v>
+      </c>
+      <c r="F19" t="s">
+        <v>258</v>
+      </c>
+      <c r="I19" s="22">
+        <f t="shared" si="6"/>
+        <v>57666.666666666664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="22">
+        <f>Loan!J8/Loan!H8</f>
+        <v>64300</v>
+      </c>
+      <c r="E20" s="36">
+        <v>45737</v>
+      </c>
+      <c r="F20" t="s">
+        <v>253</v>
+      </c>
+      <c r="I20" s="22">
+        <f>D20</f>
+        <v>64300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="7">
+        <v>2</v>
+      </c>
+      <c r="D21" s="22">
+        <f>D20</f>
+        <v>64300</v>
+      </c>
+      <c r="E21" s="36">
+        <v>45767</v>
+      </c>
+      <c r="F21" t="s">
+        <v>253</v>
+      </c>
+      <c r="I21" s="22">
+        <f t="shared" ref="I21:I22" si="7">D21</f>
+        <v>64300</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="7">
+        <v>3</v>
+      </c>
+      <c r="D22" s="22">
+        <f>D21</f>
+        <v>64300</v>
+      </c>
+      <c r="E22" s="36">
+        <v>45797</v>
+      </c>
+      <c r="F22" t="s">
+        <v>253</v>
+      </c>
+      <c r="I22" s="22">
+        <f t="shared" si="7"/>
+        <v>64300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="7">
+        <v>1</v>
+      </c>
+      <c r="D23" s="22">
+        <f>Loan!J9/Loan!H9</f>
+        <v>22733.333333333332</v>
+      </c>
+      <c r="E23" s="36">
+        <v>45749</v>
+      </c>
+      <c r="F23" t="s">
+        <v>254</v>
+      </c>
+      <c r="I23" s="22">
+        <f>D23</f>
+        <v>22733.333333333332</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="7">
+        <v>2</v>
+      </c>
+      <c r="D24" s="22">
+        <f>D23</f>
+        <v>22733.333333333332</v>
+      </c>
+      <c r="E24" s="36">
+        <v>45784</v>
+      </c>
+      <c r="F24" t="s">
+        <v>254</v>
+      </c>
+      <c r="I24" s="22">
+        <f t="shared" ref="I24:I25" si="8">D24</f>
+        <v>22733.333333333332</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="7">
+        <v>3</v>
+      </c>
+      <c r="D25" s="22">
+        <f>D24</f>
+        <v>22733.333333333332</v>
+      </c>
+      <c r="E25" s="36">
+        <v>45819</v>
+      </c>
+      <c r="F25" t="s">
+        <v>254</v>
+      </c>
+      <c r="I25" s="22">
+        <f t="shared" si="8"/>
+        <v>22733.333333333332</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B26" s="7">
+        <v>1</v>
+      </c>
+      <c r="D26" s="22">
+        <f>Loan!J10/Loan!H10</f>
+        <v>30533.333333333332</v>
+      </c>
+      <c r="E26" s="36">
+        <v>45751</v>
+      </c>
+      <c r="F26" t="s">
+        <v>255</v>
+      </c>
+      <c r="I26" s="22">
+        <f>D26</f>
+        <v>30533.333333333332</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="7">
+        <v>2</v>
+      </c>
+      <c r="D27" s="22">
+        <f>D26</f>
+        <v>30533.333333333332</v>
+      </c>
+      <c r="E27" s="36">
+        <v>45781</v>
+      </c>
+      <c r="F27" t="s">
+        <v>255</v>
+      </c>
+      <c r="I27" s="22">
+        <f t="shared" ref="I27:I28" si="9">D27</f>
+        <v>30533.333333333332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B28" s="7">
+        <v>3</v>
+      </c>
+      <c r="D28" s="22">
+        <f>D27</f>
+        <v>30533.333333333332</v>
+      </c>
+      <c r="E28" s="36">
+        <v>45811</v>
+      </c>
+      <c r="F28" t="s">
+        <v>255</v>
+      </c>
+      <c r="I28" s="22">
+        <f t="shared" si="9"/>
+        <v>30533.333333333332</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" s="7">
+        <v>1</v>
+      </c>
+      <c r="D29" s="22">
+        <f>Loan!J11/Loan!H11</f>
+        <v>38333.333333333336</v>
+      </c>
+      <c r="F29" t="s">
+        <v>256</v>
+      </c>
+      <c r="I29" s="22">
+        <f>D29</f>
+        <v>38333.333333333336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="7">
+        <v>2</v>
+      </c>
+      <c r="D30" s="22">
+        <f>D29</f>
+        <v>38333.333333333336</v>
+      </c>
+      <c r="F30" t="s">
+        <v>256</v>
+      </c>
+      <c r="I30" s="22">
+        <f t="shared" ref="I30:I31" si="10">D30</f>
+        <v>38333.333333333336</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B31" s="7">
+        <v>3</v>
+      </c>
+      <c r="D31" s="22">
+        <f>D30</f>
+        <v>38333.333333333336</v>
+      </c>
+      <c r="F31" t="s">
+        <v>256</v>
+      </c>
+      <c r="I31" s="22">
+        <f t="shared" si="10"/>
+        <v>38333.333333333336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B32" s="7">
+        <v>1</v>
+      </c>
+      <c r="D32" s="22">
+        <f>Loan!J12/Loan!H12</f>
+        <v>45800</v>
+      </c>
+      <c r="E32" s="36">
+        <v>45760</v>
+      </c>
+      <c r="F32" t="s">
+        <v>257</v>
+      </c>
+      <c r="I32" s="22">
+        <f>D32</f>
+        <v>45800</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" s="7">
+        <v>2</v>
+      </c>
+      <c r="D33" s="22">
+        <f>D32</f>
+        <v>45800</v>
+      </c>
+      <c r="E33" s="36">
+        <v>45790</v>
+      </c>
+      <c r="F33" t="s">
+        <v>257</v>
+      </c>
+      <c r="I33" s="22">
+        <f t="shared" ref="I33:I34" si="11">D33</f>
+        <v>45800</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B34" s="7">
+        <v>3</v>
+      </c>
+      <c r="D34" s="22">
+        <f>D33</f>
+        <v>45800</v>
+      </c>
+      <c r="E34" s="36">
+        <v>45820</v>
+      </c>
+      <c r="F34" t="s">
+        <v>257</v>
+      </c>
+      <c r="I34" s="22">
+        <f t="shared" si="11"/>
+        <v>45800</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B35" s="7">
+        <v>1</v>
+      </c>
+      <c r="D35" s="22">
+        <f>Loan!J13/Loan!H13</f>
+        <v>53266.666666666664</v>
+      </c>
+      <c r="F35" t="s">
+        <v>258</v>
+      </c>
+      <c r="I35" s="22">
+        <f>D36</f>
+        <v>53266.666666666664</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="7">
+        <v>2</v>
+      </c>
+      <c r="D36" s="22">
+        <f>D35</f>
+        <v>53266.666666666664</v>
+      </c>
+      <c r="E36" s="36">
+        <v>45802</v>
+      </c>
+      <c r="F36" t="s">
+        <v>258</v>
+      </c>
+      <c r="I36" s="22">
+        <f>D37</f>
+        <v>53266.666666666664</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" s="7">
+        <v>3</v>
+      </c>
+      <c r="D37" s="22">
+        <f>D36</f>
+        <v>53266.666666666664</v>
+      </c>
+      <c r="E37" s="36">
+        <v>45832</v>
+      </c>
+      <c r="F37" t="s">
+        <v>258</v>
+      </c>
+      <c r="I37" s="22">
+        <f>D37</f>
+        <v>53266.666666666664</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B38" s="7">
+        <v>1</v>
+      </c>
+      <c r="D38" s="22">
+        <f>Loan!J14/Loan!H14</f>
+        <v>61400</v>
+      </c>
+      <c r="E38" s="36">
+        <v>45779</v>
+      </c>
+      <c r="F38" t="s">
+        <v>253</v>
+      </c>
+      <c r="I38" s="22">
+        <f>D38</f>
+        <v>61400</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="7">
+        <v>2</v>
+      </c>
+      <c r="D39" s="22">
+        <f>D38</f>
+        <v>61400</v>
+      </c>
+      <c r="E39" s="36">
+        <v>45809</v>
+      </c>
+      <c r="F39" t="s">
+        <v>253</v>
+      </c>
+      <c r="I39" s="22">
+        <f t="shared" ref="I39:I40" si="12">D39</f>
+        <v>61400</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" s="7">
+        <v>3</v>
+      </c>
+      <c r="D40" s="22">
+        <f>D39</f>
+        <v>61400</v>
+      </c>
+      <c r="E40" s="36">
+        <v>45839</v>
+      </c>
+      <c r="F40" t="s">
+        <v>253</v>
+      </c>
+      <c r="I40" s="22">
+        <f t="shared" si="12"/>
+        <v>61400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B41" s="7">
+        <v>1</v>
+      </c>
+      <c r="D41" s="22">
+        <f>Loan!J15/Loan!H15</f>
+        <v>68866.666666666672</v>
+      </c>
+      <c r="E41" s="36">
+        <v>45791</v>
+      </c>
+      <c r="F41" t="s">
+        <v>254</v>
+      </c>
+      <c r="I41" s="22">
+        <f>D41</f>
+        <v>68866.666666666672</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" s="7">
+        <v>2</v>
+      </c>
+      <c r="D42" s="22">
+        <f>D41</f>
+        <v>68866.666666666672</v>
+      </c>
+      <c r="E42" s="36">
+        <v>45826</v>
+      </c>
+      <c r="F42" t="s">
+        <v>254</v>
+      </c>
+      <c r="I42" s="22">
+        <f t="shared" ref="I42:I43" si="13">D42</f>
+        <v>68866.666666666672</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B43" s="7">
+        <v>3</v>
+      </c>
+      <c r="D43" s="22">
+        <f>D42</f>
+        <v>68866.666666666672</v>
+      </c>
+      <c r="E43" s="36">
+        <v>45861</v>
+      </c>
+      <c r="F43" t="s">
+        <v>254</v>
+      </c>
+      <c r="I43" s="22">
+        <f t="shared" si="13"/>
+        <v>68866.666666666672</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B44" s="7">
+        <v>1</v>
+      </c>
+      <c r="D44" s="22">
+        <f>Loan!J16/Loan!H16</f>
+        <v>76333.333333333328</v>
+      </c>
+      <c r="E44" s="36">
+        <v>45793</v>
+      </c>
+      <c r="F44" t="s">
+        <v>255</v>
+      </c>
+      <c r="I44" s="22">
+        <f>D44</f>
+        <v>76333.333333333328</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B45" s="7">
+        <v>2</v>
+      </c>
+      <c r="D45" s="22">
+        <f>D44</f>
+        <v>76333.333333333328</v>
+      </c>
+      <c r="E45" s="36">
+        <v>45823</v>
+      </c>
+      <c r="F45" t="s">
+        <v>255</v>
+      </c>
+      <c r="I45" s="22">
+        <f t="shared" ref="I45:I46" si="14">D45</f>
+        <v>76333.333333333328</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B46" s="7">
+        <v>3</v>
+      </c>
+      <c r="D46" s="22">
+        <f>D45</f>
+        <v>76333.333333333328</v>
+      </c>
+      <c r="E46" s="36">
+        <v>45853</v>
+      </c>
+      <c r="F46" t="s">
+        <v>255</v>
+      </c>
+      <c r="I46" s="22">
+        <f t="shared" si="14"/>
+        <v>76333.333333333328</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B47" s="7">
+        <v>1</v>
+      </c>
+      <c r="D47" s="22">
+        <f>Loan!J17/Loan!H17</f>
+        <v>26800</v>
+      </c>
+      <c r="F47" t="s">
+        <v>256</v>
+      </c>
+      <c r="I47" s="22">
+        <f>D47</f>
+        <v>26800</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B48" s="7">
+        <v>2</v>
+      </c>
+      <c r="D48" s="22">
+        <f>D47</f>
+        <v>26800</v>
+      </c>
+      <c r="F48" t="s">
+        <v>256</v>
+      </c>
+      <c r="I48" s="22">
+        <f t="shared" ref="I48:I49" si="15">D48</f>
+        <v>26800</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B49" s="7">
+        <v>3</v>
+      </c>
+      <c r="D49" s="22">
+        <f>D48</f>
+        <v>26800</v>
+      </c>
+      <c r="F49" t="s">
+        <v>256</v>
+      </c>
+      <c r="I49" s="22">
+        <f t="shared" si="15"/>
+        <v>26800</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B50" s="7">
+        <v>1</v>
+      </c>
+      <c r="D50" s="22">
+        <f>Loan!J18/Loan!H18</f>
+        <v>34266.666666666664</v>
+      </c>
+      <c r="E50" s="36">
+        <v>45802</v>
+      </c>
+      <c r="F50" t="s">
+        <v>257</v>
+      </c>
+      <c r="I50" s="22">
+        <f>D50</f>
+        <v>34266.666666666664</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B51" s="7">
+        <v>2</v>
+      </c>
+      <c r="D51" s="22">
+        <f>D50</f>
+        <v>34266.666666666664</v>
+      </c>
+      <c r="E51" s="36">
+        <v>45832</v>
+      </c>
+      <c r="F51" t="s">
+        <v>257</v>
+      </c>
+      <c r="I51" s="22">
+        <f t="shared" ref="I51:I52" si="16">D51</f>
+        <v>34266.666666666664</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" s="7">
+        <v>3</v>
+      </c>
+      <c r="D52" s="22">
+        <f>D51</f>
+        <v>34266.666666666664</v>
+      </c>
+      <c r="E52" s="36">
+        <v>45862</v>
+      </c>
+      <c r="F52" t="s">
+        <v>257</v>
+      </c>
+      <c r="I52" s="22">
+        <f t="shared" si="16"/>
+        <v>34266.666666666664</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="22">
+        <f>Loan!J19/Loan!H19</f>
+        <v>42066.666666666664</v>
+      </c>
+      <c r="F53" t="s">
+        <v>258</v>
+      </c>
+      <c r="I53" s="22">
+        <f>D53</f>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" s="7">
+        <v>2</v>
+      </c>
+      <c r="D54" s="22">
+        <f>D53</f>
+        <v>42066.666666666664</v>
+      </c>
+      <c r="E54" s="36">
+        <v>45844</v>
+      </c>
+      <c r="F54" t="s">
+        <v>258</v>
+      </c>
+      <c r="I54" s="22">
+        <f t="shared" ref="I54:I55" si="17">D54</f>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="7">
+        <v>3</v>
+      </c>
+      <c r="D55" s="22">
+        <f>D54</f>
+        <v>42066.666666666664</v>
+      </c>
+      <c r="E55" s="36">
+        <v>45874</v>
+      </c>
+      <c r="F55" t="s">
+        <v>258</v>
+      </c>
+      <c r="I55" s="22">
+        <f t="shared" si="17"/>
+        <v>42066.666666666664</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B56" s="7">
+        <v>1</v>
+      </c>
+      <c r="D56" s="22">
+        <f>Loan!J20/Loan!H20</f>
+        <v>19000</v>
+      </c>
+      <c r="E56" s="36">
+        <v>45821</v>
+      </c>
+      <c r="F56" t="s">
+        <v>253</v>
+      </c>
+      <c r="I56" s="22">
+        <f>D56</f>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B57" s="7">
+        <v>2</v>
+      </c>
+      <c r="D57" s="22">
+        <f>D56</f>
+        <v>19000</v>
+      </c>
+      <c r="E57" s="36">
+        <v>45851</v>
+      </c>
+      <c r="F57" t="s">
+        <v>253</v>
+      </c>
+      <c r="I57" s="22">
+        <f t="shared" ref="I57:I58" si="18">D57</f>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="7">
+        <v>3</v>
+      </c>
+      <c r="D58" s="22">
+        <f>D56</f>
+        <v>19000</v>
+      </c>
+      <c r="E58" s="36">
+        <v>45881</v>
+      </c>
+      <c r="F58" t="s">
+        <v>253</v>
+      </c>
+      <c r="I58" s="22">
+        <f t="shared" si="18"/>
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="7" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="7" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="7" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A24" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
-        <v>203</v>
-      </c>
+      <c r="B59" s="7">
+        <v>1</v>
+      </c>
+      <c r="D59" s="22">
+        <f>Loan!J21/Loan!H21</f>
+        <v>28333.333333333332</v>
+      </c>
+      <c r="E59" s="36">
+        <v>45833</v>
+      </c>
+      <c r="F59" t="s">
+        <v>254</v>
+      </c>
+      <c r="I59" s="22">
+        <f>D59</f>
+        <v>28333.333333333332</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B60" s="7">
+        <v>2</v>
+      </c>
+      <c r="D60" s="22">
+        <f>D59</f>
+        <v>28333.333333333332</v>
+      </c>
+      <c r="E60" s="36">
+        <v>45868</v>
+      </c>
+      <c r="F60" t="s">
+        <v>254</v>
+      </c>
+      <c r="I60" s="22">
+        <f t="shared" ref="I60:I61" si="19">D60</f>
+        <v>28333.333333333332</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B61" s="7">
+        <v>3</v>
+      </c>
+      <c r="D61" s="22">
+        <f>D59</f>
+        <v>28333.333333333332</v>
+      </c>
+      <c r="E61" s="36">
+        <v>45903</v>
+      </c>
+      <c r="F61" t="s">
+        <v>254</v>
+      </c>
+      <c r="I61" s="22">
+        <f t="shared" si="19"/>
+        <v>28333.333333333332</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1789,7 +3074,7 @@
         <v>33</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>35</v>
@@ -1800,13 +3085,13 @@
         <v>57</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>67</v>
@@ -1820,13 +3105,13 @@
         <v>6</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>7</v>
@@ -1837,16 +3122,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E4" s="8">
         <v>45839</v>
@@ -1860,16 +3145,16 @@
         <v>28</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>39</v>
@@ -1880,13 +3165,13 @@
         <v>29</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E6" s="7">
         <v>300000</v>
@@ -1900,13 +3185,13 @@
         <v>62</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E7" s="7">
         <v>12</v>
@@ -1917,16 +3202,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>44</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E8" s="7">
         <v>720</v>
@@ -1937,16 +3222,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E9" s="7">
         <v>20000</v>
@@ -1957,16 +3242,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E10" s="7">
         <v>29000</v>
@@ -1977,19 +3262,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>102</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>39</v>
@@ -1997,19 +3282,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>39</v>
@@ -2017,16 +3302,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E13" s="7">
         <v>1</v>
@@ -2065,7 +3350,7 @@
         <v>33</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>35</v>
@@ -2076,13 +3361,13 @@
         <v>56</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>66</v>
@@ -2096,13 +3381,13 @@
         <v>57</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>67</v>
@@ -2116,13 +3401,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>7</v>
@@ -2136,13 +3421,13 @@
         <v>58</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E5" s="8">
         <v>45840</v>
@@ -2156,13 +3441,13 @@
         <v>59</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E6" s="7">
         <v>300000</v>
@@ -2176,13 +3461,13 @@
         <v>60</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E7" s="7">
         <v>24</v>
@@ -2196,13 +3481,13 @@
         <v>61</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E8" s="7">
         <v>5000</v>
@@ -2216,13 +3501,13 @@
         <v>62</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E9" s="7">
         <v>12</v>
@@ -2236,13 +3521,13 @@
         <v>63</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E10" s="8">
         <v>46205</v>
@@ -2256,13 +3541,13 @@
         <v>64</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>68</v>
@@ -2276,13 +3561,13 @@
         <v>65</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>69</v>
@@ -2320,7 +3605,7 @@
         <v>33</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>35</v>
@@ -2331,13 +3616,13 @@
         <v>56</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>66</v>
@@ -2348,16 +3633,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>44</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E3" s="7">
         <v>1</v>
@@ -2368,16 +3653,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E4" s="8">
         <v>45871</v>
@@ -2388,16 +3673,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E5" s="7">
         <v>25000</v>
@@ -2408,16 +3693,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E6" s="7">
         <v>6000</v>
@@ -2428,16 +3713,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E7" s="7">
         <v>500</v>
@@ -2478,7 +3763,7 @@
         <v>33</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>35</v>
@@ -2486,19 +3771,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>39</v>
@@ -2509,13 +3794,13 @@
         <v>56</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>66</v>
@@ -2526,16 +3811,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E4" s="8">
         <v>45870</v>
@@ -2546,16 +3831,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E5" s="7">
         <v>31500</v>
@@ -2566,19 +3851,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2609,7 +3894,7 @@
         <v>33</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>35</v>
@@ -2617,16 +3902,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E2" s="8">
         <v>45900</v>
@@ -2640,13 +3925,13 @@
         <v>56</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>66</v>
@@ -2657,16 +3942,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E4" s="7">
         <v>275000</v>
@@ -2677,16 +3962,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>49</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E5" s="7">
         <v>6000</v>
@@ -2697,16 +3982,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E6" s="7">
         <v>15</v>
@@ -2717,19 +4002,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>39</v>
@@ -2737,19 +4022,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>39</v>
@@ -2757,16 +4042,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E9" s="7">
         <v>0</v>
@@ -2778,7 +4063,7 @@
     <row r="12" spans="1:6" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="7" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2788,16 +4073,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.90625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="22" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.7265625" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2805,7 +4090,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -2816,7 +4101,7 @@
       <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="21" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="5" t="s">
@@ -2826,15 +4111,15 @@
         <v>51</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8">
-        <v>46025</v>
+      <c r="B2" s="8" t="s">
+        <v>228</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>16</v>
@@ -2845,7 +4130,7 @@
       <c r="E2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="20">
         <v>250000</v>
       </c>
       <c r="G2" s="7" t="s">
@@ -2854,16 +4139,16 @@
       <c r="H2" s="7">
         <v>18</v>
       </c>
-      <c r="I2" s="7" t="s">
-        <v>55</v>
+      <c r="I2" s="8">
+        <v>46025</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8">
-        <v>46025</v>
+      <c r="B3" s="8" t="s">
+        <v>229</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -2874,7 +4159,7 @@
       <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="20">
         <v>180000</v>
       </c>
       <c r="G3" s="7" t="s">
@@ -2883,16 +4168,16 @@
       <c r="H3" s="7">
         <v>17</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>85</v>
+      <c r="I3" s="8">
+        <v>46025</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8">
-        <v>46055</v>
+      <c r="B4" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -2901,9 +4186,9 @@
         <v>41</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F4" s="7">
+        <v>85</v>
+      </c>
+      <c r="F4" s="20">
         <v>520000</v>
       </c>
       <c r="G4" s="7" t="s">
@@ -2912,16 +4197,16 @@
       <c r="H4" s="7">
         <v>16</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>87</v>
+      <c r="I4" s="8">
+        <v>46055</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="8">
-        <v>46054</v>
+      <c r="B5" s="8" t="s">
+        <v>231</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
@@ -2932,7 +4217,7 @@
       <c r="E5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="20">
         <v>320000</v>
       </c>
       <c r="G5" s="7" t="s">
@@ -2941,16 +4226,16 @@
       <c r="H5" s="7">
         <v>15</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>88</v>
+      <c r="I5" s="8">
+        <v>46054</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8">
-        <v>45728</v>
+      <c r="B6" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -2961,7 +4246,7 @@
       <c r="E6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="20">
         <v>150000</v>
       </c>
       <c r="G6" s="7" t="s">
@@ -2970,16 +4255,16 @@
       <c r="H6" s="7">
         <v>14</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>55</v>
+      <c r="I6" s="8">
+        <v>45728</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8">
-        <v>45759</v>
+      <c r="B7" s="8" t="s">
+        <v>233</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>21</v>
@@ -2988,9 +4273,9 @@
         <v>38</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="7">
+        <v>85</v>
+      </c>
+      <c r="F7" s="20">
         <v>470000</v>
       </c>
       <c r="G7" s="7" t="s">
@@ -2999,19 +4284,19 @@
       <c r="H7" s="7">
         <v>13</v>
       </c>
-      <c r="I7" s="7" t="s">
-        <v>89</v>
+      <c r="I7" s="8">
+        <v>45759</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="8">
-        <v>45787</v>
+      <c r="B8" s="8" t="s">
+        <v>234</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2">
         <v>24</v>
@@ -3019,7 +4304,7 @@
       <c r="E8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="20">
         <v>170000</v>
       </c>
       <c r="G8" s="7" t="s">
@@ -3028,27 +4313,27 @@
       <c r="H8" s="7">
         <v>12</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>85</v>
+      <c r="I8" s="8">
+        <v>45787</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8">
-        <v>45785</v>
+      <c r="B9" s="8" t="s">
+        <v>235</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2">
         <v>45</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="7">
+        <v>88</v>
+      </c>
+      <c r="F9" s="20">
         <v>600000</v>
       </c>
       <c r="G9" s="7" t="s">
@@ -3057,19 +4342,19 @@
       <c r="H9" s="7">
         <v>11</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>88</v>
+      <c r="I9" s="8">
+        <v>45785</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="8">
-        <v>45813</v>
+      <c r="B10" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D10" s="2">
         <v>30</v>
@@ -3077,7 +4362,7 @@
       <c r="E10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="20">
         <v>210000</v>
       </c>
       <c r="G10" s="7" t="s">
@@ -3086,8 +4371,8 @@
       <c r="H10" s="7">
         <v>10</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>55</v>
+      <c r="I10" s="8">
+        <v>45813</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -3095,10 +4380,10 @@
         <v>84</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D11" s="2">
         <v>34</v>
@@ -3106,7 +4391,7 @@
       <c r="E11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="20">
         <v>390000</v>
       </c>
       <c r="G11" s="7" t="s">
@@ -3115,8 +4400,298 @@
       <c r="H11" s="7">
         <v>9</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="2">
+        <v>32</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="20">
+        <v>250000</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="7">
+        <v>18</v>
+      </c>
+      <c r="I12" s="8">
+        <v>46025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D13" s="2">
+        <v>27</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="20">
+        <v>180000</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="7">
+        <v>17</v>
+      </c>
+      <c r="I13" s="8">
+        <v>46025</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2">
+        <v>41</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="20">
+        <v>520000</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="7">
+        <v>16</v>
+      </c>
+      <c r="I14" s="8">
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>87</v>
+      </c>
+      <c r="D15" s="2">
+        <v>36</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="20">
+        <v>320000</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="7">
+        <v>15</v>
+      </c>
+      <c r="I15" s="8">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D16" s="2">
+        <v>29</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="20">
+        <v>150000</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="7">
+        <v>14</v>
+      </c>
+      <c r="I16" s="8">
+        <v>45728</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="2">
+        <v>38</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="20">
+        <v>470000</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="7">
+        <v>13</v>
+      </c>
+      <c r="I17" s="8">
+        <v>45759</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="2">
+        <v>24</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="20">
+        <v>170000</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="7">
+        <v>12</v>
+      </c>
+      <c r="I18" s="8">
+        <v>45787</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="2">
+        <v>45</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F19" s="20">
+        <v>600000</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="7">
+        <v>11</v>
+      </c>
+      <c r="I19" s="8">
+        <v>45785</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="2">
+        <v>30</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="20">
+        <v>210000</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="7">
+        <v>10</v>
+      </c>
+      <c r="I20" s="8">
+        <v>45813</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="2">
+        <v>34</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="20">
+        <v>390000</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="7">
+        <v>9</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3126,24 +4701,23 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.26953125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.1796875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" style="19" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" style="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="22" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>57</v>
       </c>
@@ -3151,7 +4725,7 @@
         <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>28</v>
@@ -3163,25 +4737,22 @@
         <v>62</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H1" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>67</v>
       </c>
@@ -3192,9 +4763,9 @@
         <v>45810</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="22">
+        <v>97</v>
+      </c>
+      <c r="E2" s="18">
         <v>300000</v>
       </c>
       <c r="F2" s="7">
@@ -3203,23 +4774,20 @@
       <c r="G2" s="7">
         <v>725</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="20">
         <v>20000</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="20">
         <v>29500</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L2" s="7">
+        <v>98</v>
+      </c>
+      <c r="K2" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>71</v>
       </c>
@@ -3230,9 +4798,9 @@
         <v>45811</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="22">
+        <v>99</v>
+      </c>
+      <c r="E3" s="18">
         <v>100000</v>
       </c>
       <c r="F3" s="7">
@@ -3241,23 +4809,20 @@
       <c r="G3" s="7">
         <v>650</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="20">
         <v>15000</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="20">
         <v>18500</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L3" s="7">
+        <v>98</v>
+      </c>
+      <c r="K3" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
@@ -3268,9 +4833,9 @@
         <v>45812</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="22">
+        <v>97</v>
+      </c>
+      <c r="E4" s="18">
         <v>500000</v>
       </c>
       <c r="F4" s="7">
@@ -3279,25 +4844,22 @@
       <c r="G4" s="7">
         <v>780</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="20">
         <v>30000</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="20">
         <v>37000</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L4" s="7">
+        <v>98</v>
+      </c>
+      <c r="K4" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>10</v>
@@ -3306,9 +4868,9 @@
         <v>45813</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" s="22">
+        <v>101</v>
+      </c>
+      <c r="E5" s="18">
         <v>600000</v>
       </c>
       <c r="F5" s="7">
@@ -3317,25 +4879,22 @@
       <c r="G5" s="7">
         <v>590</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="20">
         <v>45000</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="20">
         <v>43000</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="L5" s="7">
+        <v>98</v>
+      </c>
+      <c r="K5" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>11</v>
@@ -3344,9 +4903,9 @@
         <v>45814</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="22">
+        <v>99</v>
+      </c>
+      <c r="E6" s="18">
         <v>80000</v>
       </c>
       <c r="F6" s="7">
@@ -3355,23 +4914,20 @@
       <c r="G6" s="7">
         <v>520</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="20">
         <v>22000</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="20">
         <v>28500</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="L6" s="7">
+        <v>98</v>
+      </c>
+      <c r="K6" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>75</v>
       </c>
@@ -3382,9 +4938,9 @@
         <v>45815</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="22">
+        <v>101</v>
+      </c>
+      <c r="E7" s="18">
         <v>700000</v>
       </c>
       <c r="F7" s="7">
@@ -3393,23 +4949,20 @@
       <c r="G7" s="7">
         <v>735</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="20">
         <v>35000</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="20">
         <v>47000</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L7" s="7">
+        <v>98</v>
+      </c>
+      <c r="K7" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>77</v>
       </c>
@@ -3420,9 +4973,9 @@
         <v>45816</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="22">
+        <v>97</v>
+      </c>
+      <c r="E8" s="18">
         <v>200000</v>
       </c>
       <c r="F8" s="7">
@@ -3431,23 +4984,20 @@
       <c r="G8" s="7">
         <v>680</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="20">
         <v>12000</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="20">
         <v>21000</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" s="7">
+        <v>98</v>
+      </c>
+      <c r="K8" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>79</v>
       </c>
@@ -3458,9 +5008,9 @@
         <v>45817</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="22">
+        <v>101</v>
+      </c>
+      <c r="E9" s="18">
         <v>1000000</v>
       </c>
       <c r="F9" s="7">
@@ -3469,23 +5019,20 @@
       <c r="G9" s="7">
         <v>760</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="20">
         <v>60000</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="20">
         <v>52000</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L9" s="7">
+        <v>98</v>
+      </c>
+      <c r="K9" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>81</v>
       </c>
@@ -3496,9 +5043,9 @@
         <v>45818</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="22">
+        <v>99</v>
+      </c>
+      <c r="E10" s="18">
         <v>120000</v>
       </c>
       <c r="F10" s="7">
@@ -3507,23 +5054,20 @@
       <c r="G10" s="7">
         <v>605</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="20">
         <v>18000</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="20">
         <v>21000</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L10" s="7">
+        <v>98</v>
+      </c>
+      <c r="K10" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>83</v>
       </c>
@@ -3534,9 +5078,9 @@
         <v>45819</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="22">
+        <v>97</v>
+      </c>
+      <c r="E11" s="18">
         <v>350000</v>
       </c>
       <c r="F11" s="7">
@@ -3545,36 +5089,33 @@
       <c r="G11" s="7">
         <v>745</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="20">
         <v>20000</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="20">
         <v>33000</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L11" s="7">
+        <v>98</v>
+      </c>
+      <c r="K11" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C12" s="8">
         <v>45820</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="22">
+        <v>99</v>
+      </c>
+      <c r="E12" s="18">
         <v>120000</v>
       </c>
       <c r="F12" s="7">
@@ -3583,36 +5124,33 @@
       <c r="G12" s="7">
         <v>730</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="20">
         <v>15000</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="20">
         <v>22000</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L12" s="7">
+        <v>98</v>
+      </c>
+      <c r="K12" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="C13" s="8">
         <v>45821</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="22">
+        <v>101</v>
+      </c>
+      <c r="E13" s="18">
         <v>900000</v>
       </c>
       <c r="F13" s="7">
@@ -3621,36 +5159,33 @@
       <c r="G13" s="7">
         <v>790</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="20">
         <v>40000</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="20">
         <v>61000</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L13" s="7">
+        <v>98</v>
+      </c>
+      <c r="K13" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C14" s="8">
         <v>45822</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="22">
+        <v>97</v>
+      </c>
+      <c r="E14" s="18">
         <v>250000</v>
       </c>
       <c r="F14" s="7">
@@ -3659,36 +5194,33 @@
       <c r="G14" s="7">
         <v>540</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="20">
         <v>25000</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="20">
         <v>26000</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="L14" s="7">
+        <v>98</v>
+      </c>
+      <c r="K14" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C15" s="8">
         <v>45823</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" s="22">
+        <v>99</v>
+      </c>
+      <c r="E15" s="18">
         <v>150000</v>
       </c>
       <c r="F15" s="7">
@@ -3697,36 +5229,33 @@
       <c r="G15" s="7">
         <v>770</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="20">
         <v>18000</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="20">
         <v>24000</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" s="7">
+        <v>98</v>
+      </c>
+      <c r="K15" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C16" s="8">
         <v>45824</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="22">
+        <v>97</v>
+      </c>
+      <c r="E16" s="18">
         <v>300000</v>
       </c>
       <c r="F16" s="7">
@@ -3735,20 +5264,192 @@
       <c r="G16" s="7">
         <v>610</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="20">
         <v>28000</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="20">
         <v>31000</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="L16" s="7">
+        <v>98</v>
+      </c>
+      <c r="K16" s="7">
         <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C17" s="8">
+        <v>45825</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="19">
+        <v>240000</v>
+      </c>
+      <c r="F17" s="7">
+        <v>3</v>
+      </c>
+      <c r="G17" s="7">
+        <v>450</v>
+      </c>
+      <c r="H17" s="22">
+        <v>15000</v>
+      </c>
+      <c r="I17" s="22">
+        <v>55000</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K17" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" s="8">
+        <v>45826</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="19">
+        <v>150000</v>
+      </c>
+      <c r="F18" s="7">
+        <v>3</v>
+      </c>
+      <c r="G18" s="7">
+        <v>500</v>
+      </c>
+      <c r="H18" s="22">
+        <v>35000</v>
+      </c>
+      <c r="I18" s="22">
+        <v>24000</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K18" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="8">
+        <v>45827</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E19" s="19">
+        <v>250000</v>
+      </c>
+      <c r="F19" s="7">
+        <v>3</v>
+      </c>
+      <c r="G19" s="7">
+        <v>600</v>
+      </c>
+      <c r="H19" s="22">
+        <v>25000</v>
+      </c>
+      <c r="I19" s="22">
+        <v>60000</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K19" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C20" s="8">
+        <v>45828</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="19">
+        <v>600000</v>
+      </c>
+      <c r="F20" s="7">
+        <v>3</v>
+      </c>
+      <c r="G20" s="7">
+        <v>342</v>
+      </c>
+      <c r="H20" s="22">
+        <v>8000</v>
+      </c>
+      <c r="I20" s="22">
+        <v>250000</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K20" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="8">
+        <v>45829</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="19">
+        <v>450000</v>
+      </c>
+      <c r="F21" s="7">
+        <v>3</v>
+      </c>
+      <c r="G21" s="7">
+        <v>768</v>
+      </c>
+      <c r="H21" s="22">
+        <v>3000</v>
+      </c>
+      <c r="I21" s="22">
+        <v>120000</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K21" s="7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3758,7 +5459,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U48"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.6328125" style="6" bestFit="1" customWidth="1"/>
@@ -3768,14 +5469,17 @@
     <col min="7" max="7" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.26953125" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.90625" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.7265625" style="6"/>
+    <col min="14" max="14" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
@@ -3792,10 +5496,10 @@
         <v>59</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>62</v>
@@ -3804,34 +5508,14 @@
         <v>63</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>235</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="U1" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>66</v>
       </c>
@@ -3860,15 +5544,12 @@
       <c r="I2" s="8">
         <v>46298</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="K2" s="7">
+      <c r="J2" s="7">
         <f>E2*F2*3+E2+G2</f>
         <v>57000</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
@@ -3897,15 +5578,12 @@
       <c r="I3" s="8">
         <v>46299</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="K3" s="7">
+      <c r="J3" s="7">
         <f>E3*F3*3+G3+E3</f>
         <v>81400</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>72</v>
       </c>
@@ -3934,20 +5612,17 @@
       <c r="I4" s="8">
         <v>46300</v>
       </c>
-      <c r="J4" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="K4" s="7">
+      <c r="J4" s="7">
         <f>E2*F2*3+G4+E4</f>
         <v>98000</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>10</v>
@@ -3971,20 +5646,17 @@
       <c r="I5" s="8">
         <v>46301</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" ref="K5:K21" si="1">E5*F5*H5+G5+E5</f>
+      <c r="J5" s="7">
+        <f t="shared" ref="J5:J21" si="1">E5*F5*H5+G5+E5</f>
         <v>126200</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>11</v>
@@ -4008,15 +5680,12 @@
       <c r="I6" s="8">
         <v>46302</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="K6" s="7">
+      <c r="J6" s="7">
         <f t="shared" si="1"/>
         <v>148600</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
@@ -4045,15 +5714,12 @@
       <c r="I7" s="8">
         <v>46303</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="K7" s="7">
+      <c r="J7" s="7">
         <f t="shared" si="1"/>
         <v>173000</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
@@ -4082,15 +5748,12 @@
       <c r="I8" s="8">
         <v>46304</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="K8" s="7">
+      <c r="J8" s="7">
         <f t="shared" si="1"/>
         <v>192900</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>82</v>
       </c>
@@ -4119,21 +5782,14 @@
       <c r="I9" s="8">
         <v>46305</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="K9" s="7">
+      <c r="J9" s="7">
         <f t="shared" si="1"/>
         <v>68200</v>
       </c>
-      <c r="L9">
-        <f>E9*F9*3+G9</f>
-        <v>8200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>81</v>
@@ -4160,17 +5816,14 @@
       <c r="I10" s="8">
         <v>46306</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="K10" s="7">
+      <c r="J10" s="7">
         <f t="shared" si="1"/>
         <v>91600</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>83</v>
@@ -4197,23 +5850,20 @@
       <c r="I11" s="8">
         <v>46307</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="K11" s="7">
+      <c r="J11" s="7">
         <f t="shared" si="1"/>
         <v>115000</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D12" s="8">
         <v>45852</v>
@@ -4234,23 +5884,20 @@
       <c r="I12" s="8">
         <v>46308</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="K12" s="7">
+      <c r="J12" s="7">
         <f t="shared" si="1"/>
         <v>137400</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D13" s="8">
         <v>45853</v>
@@ -4271,23 +5918,20 @@
       <c r="I13" s="8">
         <v>46309</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="K13" s="7">
+      <c r="J13" s="7">
         <f t="shared" si="1"/>
         <v>159800</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D14" s="8">
         <v>45854</v>
@@ -4308,23 +5952,20 @@
       <c r="I14" s="8">
         <v>46310</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="K14" s="7">
+      <c r="J14" s="7">
         <f t="shared" si="1"/>
         <v>184200</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D15" s="8">
         <v>45855</v>
@@ -4345,23 +5986,20 @@
       <c r="I15" s="8">
         <v>46311</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="K15" s="7">
+      <c r="J15" s="7">
         <f t="shared" si="1"/>
         <v>206600</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D16" s="8">
         <v>45856</v>
@@ -4382,23 +6020,20 @@
       <c r="I16" s="8">
         <v>46312</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="K16" s="7">
+      <c r="J16" s="7">
         <f t="shared" si="1"/>
         <v>229000</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D17" s="8">
         <v>45857</v>
@@ -4419,23 +6054,20 @@
       <c r="I17" s="8">
         <v>46313</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="K17" s="7">
+      <c r="J17" s="7">
         <f t="shared" si="1"/>
         <v>80400</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D18" s="8">
         <v>45858</v>
@@ -4456,23 +6088,20 @@
       <c r="I18" s="8">
         <v>46314</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="K18" s="7">
+      <c r="J18" s="7">
         <f t="shared" si="1"/>
         <v>102800</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D19" s="8">
         <v>45859</v>
@@ -4493,23 +6122,20 @@
       <c r="I19" s="8">
         <v>46315</v>
       </c>
-      <c r="J19" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="K19" s="7">
+      <c r="J19" s="7">
         <f t="shared" si="1"/>
         <v>126200</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D20" s="8">
         <v>45860</v>
@@ -4530,23 +6156,20 @@
       <c r="I20" s="8">
         <v>46316</v>
       </c>
-      <c r="J20" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="K20" s="7">
+      <c r="J20" s="7">
         <f t="shared" si="1"/>
         <v>57000</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D21" s="8">
         <v>45861</v>
@@ -4567,56 +6190,52 @@
       <c r="I21" s="8">
         <v>46317</v>
       </c>
-      <c r="J21" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="K21" s="7">
+      <c r="J21" s="7">
         <f t="shared" si="1"/>
         <v>85000</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B23" s="18" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K22" s="15" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B23" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="L23" s="15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="14" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="L24" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="M24" s="14" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>66</v>
       </c>
@@ -4627,7 +6246,7 @@
         <v>45872</v>
       </c>
       <c r="D25" s="10">
-        <f>K2/H2</f>
+        <f>J2/H2</f>
         <v>19000</v>
       </c>
       <c r="G25" s="13"/>
@@ -4639,11 +6258,8 @@
         <f>SUMIFS(D25:D27, A25:A27,A2, C25:C27, "&lt;="&amp;C27)</f>
         <v>57000</v>
       </c>
-      <c r="J25" s="20" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>66</v>
       </c>
@@ -4654,11 +6270,11 @@
         <v>45903</v>
       </c>
       <c r="D26" s="10">
-        <f>K2/H2</f>
+        <f>J2/H2</f>
         <v>19000</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>66</v>
       </c>
@@ -4669,11 +6285,11 @@
         <v>45933</v>
       </c>
       <c r="D27" s="10">
-        <f>K2/H2</f>
+        <f>J2/H2</f>
         <v>19000</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>70</v>
       </c>
@@ -4684,7 +6300,7 @@
         <v>45903</v>
       </c>
       <c r="D28" s="10">
-        <f>K3/H3</f>
+        <f>J3/H3</f>
         <v>27133.333333333332</v>
       </c>
       <c r="G28" s="13"/>
@@ -4696,11 +6312,8 @@
         <f>SUMIFS(D28:D30, A28:A30,A3,C28:C30,"&lt;="&amp;C30)</f>
         <v>81400</v>
       </c>
-      <c r="J28" s="19" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>70</v>
       </c>
@@ -4711,11 +6324,11 @@
         <v>45933</v>
       </c>
       <c r="D29" s="10">
-        <f>K3/H3</f>
+        <f>J3/H3</f>
         <v>27133.333333333332</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>70</v>
       </c>
@@ -4726,51 +6339,51 @@
         <v>45964</v>
       </c>
       <c r="D30" s="10">
-        <f>K3/H3</f>
+        <f>J3/H3</f>
         <v>27133.333333333332</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A31" s="28" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A31" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="23">
         <v>1</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="24">
         <v>45874</v>
       </c>
-      <c r="D31" s="30">
-        <f>K4/H4</f>
+      <c r="D31" s="25">
+        <f>J4/H4</f>
         <v>32666.666666666668</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A32" s="28" t="s">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A32" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="23">
         <v>2</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="24">
         <v>45905</v>
       </c>
-      <c r="D32" s="30">
-        <f>K4/H4</f>
+      <c r="D32" s="25">
+        <f>J4/H4</f>
         <v>32666.666666666668</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A33" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="28">
-        <v>3</v>
-      </c>
-      <c r="C33" s="29">
+      <c r="B33" s="23">
+        <v>3</v>
+      </c>
+      <c r="C33" s="24">
         <v>45935</v>
       </c>
-      <c r="D33" s="31">
+      <c r="D33" s="26">
         <f>D32</f>
         <v>32666.666666666668</v>
       </c>
@@ -4782,16 +6395,12 @@
         <f>SUMIFS(D31:D32,A31:A32, A4,C31:C32, "&lt;="&amp;C33)</f>
         <v>65333.333333333336</v>
       </c>
-      <c r="J33" s="27">
-        <f>MAX(0,H33-I33)</f>
-        <v>32666.666666666664</v>
-      </c>
-      <c r="K33" s="13">
+      <c r="J33" s="13">
         <f>C33</f>
         <v>45935</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>74</v>
       </c>
@@ -4802,11 +6411,11 @@
         <v>45937</v>
       </c>
       <c r="D34" s="6">
-        <f>K5/H5</f>
+        <f>J5/H5</f>
         <v>42066.666666666664</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>74</v>
       </c>
@@ -4817,11 +6426,11 @@
         <v>45968</v>
       </c>
       <c r="D35" s="6">
-        <f>K5/H5</f>
+        <f>J5/H5</f>
         <v>42066.666666666664</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>74</v>
       </c>
@@ -4832,11 +6441,11 @@
         <v>45998</v>
       </c>
       <c r="D36" s="6">
-        <f>K5/H5</f>
+        <f>J5/H5</f>
         <v>42066.666666666664</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>76</v>
       </c>
@@ -4844,11 +6453,11 @@
         <v>1</v>
       </c>
       <c r="D37" s="6">
-        <f>K6/H6</f>
+        <f>J6/H6</f>
         <v>49533.333333333336</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>76</v>
       </c>
@@ -4856,11 +6465,11 @@
         <v>2</v>
       </c>
       <c r="D38" s="6">
-        <f>K6/H5</f>
+        <f>J6/H5</f>
         <v>49533.333333333336</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>76</v>
       </c>
@@ -4868,53 +6477,53 @@
         <v>3</v>
       </c>
       <c r="D39" s="6">
-        <f>K6/H6</f>
+        <f>J6/H6</f>
         <v>49533.333333333336</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
         <v>195</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="258">
   <si>
     <t>signup_date</t>
   </si>
@@ -704,9 +704,6 @@
     <t>cumulative_paid</t>
   </si>
   <si>
-    <t>Installments</t>
-  </si>
-  <si>
     <t>Abia</t>
   </si>
   <si>
@@ -783,12 +780,6 @@
   </si>
   <si>
     <t>LO11</t>
-  </si>
-  <si>
-    <t>Payment Date</t>
-  </si>
-  <si>
-    <t>Null</t>
   </si>
   <si>
     <t>Scenario</t>
@@ -826,7 +817,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -860,11 +851,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -878,23 +880,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="4" tint="-0.24994659260841701"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -903,15 +919,12 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -930,22 +943,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -959,48 +962,52 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1287,212 +1294,212 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.90625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="18.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>45672</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>34</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>350000</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1506,1541 +1513,1679 @@
   <dimension ref="A1:M62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.90625" style="36" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="6" customWidth="1"/>
-    <col min="9" max="9" width="14.26953125" style="22" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7265625" style="9"/>
-    <col min="12" max="12" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" style="22" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" style="22" customWidth="1"/>
+    <col min="7" max="7" width="16" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" style="5" customWidth="1"/>
+    <col min="9" max="9" width="14.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" style="8"/>
+    <col min="12" max="12" width="21.26953125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="I1" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="J1" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="K1" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="L1" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="M1" s="35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="6">
+        <v>1</v>
+      </c>
+      <c r="C2" s="26">
+        <v>45871</v>
+      </c>
+      <c r="D2" s="18">
+        <f>Loan!J2/Loan!H2</f>
+        <v>19000</v>
+      </c>
+      <c r="E2" s="26">
+        <v>45871</v>
+      </c>
+      <c r="F2" t="s">
         <v>250</v>
       </c>
-      <c r="F1" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="G1" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="H1" s="39" t="s">
-        <v>260</v>
-      </c>
-      <c r="I1" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="K1" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="7">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8">
-        <v>45872</v>
-      </c>
-      <c r="D2" s="28">
-        <f>Loan!D25</f>
-        <v>19000</v>
-      </c>
-      <c r="E2" s="36">
-        <v>45872</v>
-      </c>
-      <c r="F2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G2" s="38">
+      <c r="G2" s="23">
         <f>D2</f>
         <v>19000</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H2" s="23">
         <f>MAX(0,G2-D2)</f>
         <v>0</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="17">
         <f>SUMIFS(D2:D2,A2:A2,A2)</f>
         <v>19000</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="8">
-        <v>45903</v>
-      </c>
-      <c r="D3" s="28">
-        <f>Loan!D25</f>
+      <c r="C3" s="26">
+        <v>45902</v>
+      </c>
+      <c r="D3" s="18">
+        <f>Loan!J2/Loan!H2</f>
         <v>19000</v>
       </c>
-      <c r="E3" s="36">
-        <v>45903</v>
+      <c r="E3" s="26">
+        <v>45902</v>
       </c>
       <c r="F3" t="s">
-        <v>253</v>
-      </c>
-      <c r="G3" s="38">
+        <v>250</v>
+      </c>
+      <c r="G3" s="23">
         <f>D3</f>
         <v>19000</v>
       </c>
-      <c r="H3" s="38">
+      <c r="H3" s="23">
         <f>MAX(0,D3-G3)</f>
         <v>0</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="17">
         <f>SUMIFS(D2:D3,A2:A3,A3)</f>
         <v>38000</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
-        <v>45933</v>
-      </c>
-      <c r="D4" s="28">
-        <f>Loan!D25</f>
+      <c r="C4" s="26">
+        <v>45932</v>
+      </c>
+      <c r="D4" s="18">
+        <f>Loan!J2/Loan!H2</f>
         <v>19000</v>
       </c>
-      <c r="E4" s="36">
-        <v>45933</v>
+      <c r="E4" s="26">
+        <v>45932</v>
       </c>
       <c r="F4" t="s">
-        <v>253</v>
-      </c>
-      <c r="G4" s="38">
+        <v>250</v>
+      </c>
+      <c r="G4" s="23">
         <f>D4</f>
         <v>19000</v>
       </c>
-      <c r="H4" s="38">
+      <c r="H4" s="23">
         <f>MAX(0,D4-G4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="17">
         <f>SUMIFS(D2:D4,A2:A4,A4)</f>
         <v>57000</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="26">
         <v>45903</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="18">
         <f>Loan!J3/Loan!H3</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="26">
         <v>45903</v>
       </c>
       <c r="F5" t="s">
-        <v>254</v>
-      </c>
-      <c r="G5" s="6">
+        <v>251</v>
+      </c>
+      <c r="G5" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="23">
         <f>MAX(0,D5-G5)</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="17">
         <f>SUMIFS(D5:D5,A5,A5:A5)</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="J5" s="38">
+      <c r="J5" s="23">
         <f>MAX(0,G5-H5)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="24">
         <f>I5-J5</f>
         <v>27133.333333333332</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="26">
         <v>45933</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="18">
         <f>D5</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="26">
         <v>45933</v>
       </c>
       <c r="F6" t="s">
-        <v>254</v>
-      </c>
-      <c r="G6" s="6">
+        <v>251</v>
+      </c>
+      <c r="G6" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="23">
         <f t="shared" ref="H6:H7" si="0">MAX(0,D6-G6)</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="17">
         <f>SUMIFS(D5:D6,A5:A6,A5)</f>
         <v>54266.666666666664</v>
       </c>
-      <c r="J6" s="38">
+      <c r="J6" s="23">
         <f t="shared" ref="J6:J7" si="1">MAX(0,G6-H6)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="41">
+      <c r="K6" s="24">
         <f>I6-J6</f>
         <v>54266.666666666664</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="26">
         <v>45964</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="18">
         <f>D5</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="26">
         <v>45964</v>
       </c>
       <c r="F7" t="s">
-        <v>254</v>
-      </c>
-      <c r="G7" s="6">
+        <v>251</v>
+      </c>
+      <c r="G7" s="5">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="23">
         <f t="shared" si="0"/>
         <v>27133.333333333332</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="17">
         <f>SUMIFS(D5:D7,A5:A7,A7)</f>
         <v>81400</v>
       </c>
-      <c r="J7" s="38">
+      <c r="J7" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="41">
+      <c r="K7" s="24">
         <f>I7-J7</f>
         <v>81400</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="19">
         <v>1</v>
       </c>
-      <c r="C8" s="31">
-        <v>45874</v>
-      </c>
-      <c r="D8" s="32">
+      <c r="C8" s="26">
+        <v>45873</v>
+      </c>
+      <c r="D8" s="20">
         <f>Loan!J4/Loan!H4</f>
         <v>32666.666666666668</v>
       </c>
-      <c r="E8" s="36">
-        <v>45874</v>
+      <c r="E8" s="26">
+        <v>45873</v>
       </c>
       <c r="F8" t="s">
-        <v>255</v>
-      </c>
-      <c r="G8" s="22">
+        <v>252</v>
+      </c>
+      <c r="G8" s="17">
         <v>13000</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="17">
         <f>MAX(0,D8-G8)</f>
         <v>19666.666666666668</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="17">
         <f>SUMIFS(D8:D8,A8:A8,A8)</f>
         <v>32666.666666666668</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="23">
         <f>G8</f>
         <v>13000</v>
       </c>
-      <c r="K8" s="41">
+      <c r="K8" s="24">
         <f>I8-J8</f>
         <v>19666.666666666668</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="19">
         <v>2</v>
       </c>
-      <c r="C9" s="31">
-        <v>45905</v>
-      </c>
-      <c r="D9" s="32">
+      <c r="C9" s="26">
+        <v>45904</v>
+      </c>
+      <c r="D9" s="20">
         <f>D8</f>
         <v>32666.666666666668</v>
       </c>
-      <c r="E9" s="36">
-        <v>45905</v>
+      <c r="E9" s="26">
+        <v>45904</v>
       </c>
       <c r="F9" t="s">
-        <v>255</v>
-      </c>
-      <c r="G9" s="38">
+        <v>252</v>
+      </c>
+      <c r="G9" s="23">
         <v>10000</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="17">
         <f t="shared" ref="H9:H10" si="2">MAX(0,D9-G9)</f>
         <v>22666.666666666668</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="17">
         <f>SUMIFS(D8:D9,A8:A9,A9)</f>
         <v>65333.333333333336</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9" s="23">
         <f>G8+G9</f>
         <v>23000</v>
       </c>
-      <c r="K9" s="41">
+      <c r="K9" s="24">
         <f>I9-J9</f>
         <v>42333.333333333336</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="19">
         <v>3</v>
       </c>
-      <c r="C10" s="31">
-        <v>45935</v>
-      </c>
-      <c r="D10" s="33">
+      <c r="C10" s="26">
+        <v>45934</v>
+      </c>
+      <c r="D10" s="21">
         <f>D8</f>
         <v>32666.666666666668</v>
       </c>
-      <c r="E10" s="36">
-        <v>45935</v>
+      <c r="E10" s="26">
+        <v>45934</v>
       </c>
       <c r="F10" t="s">
-        <v>255</v>
-      </c>
-      <c r="G10" s="22">
+        <v>252</v>
+      </c>
+      <c r="G10" s="17">
         <v>14000</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="17">
         <f t="shared" si="2"/>
         <v>18666.666666666668</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="17">
         <f>SUMIFS(D8:D10,A8:A10,A10)</f>
         <v>98000</v>
       </c>
-      <c r="J10" s="38">
+      <c r="J10" s="23">
         <f>G8+G9+G10</f>
         <v>37000</v>
       </c>
-      <c r="K10" s="41">
+      <c r="K10" s="24">
         <f>I10-J10</f>
         <v>61000</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>1</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="26">
         <v>45937</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="17">
         <f>Loan!J5/Loan!H5</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E11" s="36" t="s">
-        <v>251</v>
+      <c r="E11" s="26">
+        <v>45947</v>
       </c>
       <c r="F11" t="s">
-        <v>256</v>
-      </c>
-      <c r="G11" s="38">
+        <v>253</v>
+      </c>
+      <c r="G11" s="23">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="23">
         <f>D11+G11</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="17">
         <f>D11</f>
         <v>42066.666666666664</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>2</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="26">
         <v>45968</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="17">
         <f>D11</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>251</v>
+      <c r="E12" s="26">
+        <v>45975</v>
       </c>
       <c r="F12" t="s">
-        <v>256</v>
-      </c>
-      <c r="G12" s="38">
+        <v>253</v>
+      </c>
+      <c r="G12" s="23">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="23">
         <f t="shared" ref="H12:H13" si="3">D12+G12</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="17">
         <f t="shared" ref="I12:I13" si="4">D12</f>
         <v>42066.666666666664</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>3</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="26">
         <v>45998</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="17">
         <f>D11</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E13" s="36" t="s">
-        <v>251</v>
+      <c r="E13" s="26">
+        <v>46010</v>
       </c>
       <c r="F13" t="s">
-        <v>256</v>
-      </c>
-      <c r="G13" s="38">
+        <v>253</v>
+      </c>
+      <c r="G13" s="23">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="23">
         <f t="shared" si="3"/>
         <v>42066.666666666664</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="17">
         <f t="shared" si="4"/>
         <v>42066.666666666664</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>1</v>
       </c>
-      <c r="C14" s="13">
-        <v>45937</v>
-      </c>
-      <c r="D14" s="22">
+      <c r="C14" s="26">
+        <v>45969</v>
+      </c>
+      <c r="D14" s="17">
         <f>Loan!J6/Loan!H6</f>
         <v>49533.333333333336</v>
       </c>
-      <c r="E14" s="36">
-        <v>45718</v>
+      <c r="E14" s="26">
+        <v>45979</v>
       </c>
       <c r="F14" t="s">
-        <v>257</v>
-      </c>
-      <c r="I14" s="22">
+        <v>254</v>
+      </c>
+      <c r="I14" s="17">
         <f>D14</f>
         <v>49533.333333333336</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>2</v>
       </c>
-      <c r="C15" s="13">
-        <v>45968</v>
-      </c>
-      <c r="D15" s="22">
+      <c r="C15" s="26">
+        <v>45999</v>
+      </c>
+      <c r="D15" s="17">
         <f>D14</f>
         <v>49533.333333333336</v>
       </c>
-      <c r="E15" s="36">
-        <v>45748</v>
+      <c r="E15" s="26">
+        <v>46006</v>
       </c>
       <c r="F15" t="s">
-        <v>257</v>
-      </c>
-      <c r="I15" s="22">
+        <v>254</v>
+      </c>
+      <c r="I15" s="17">
         <f t="shared" ref="I15:I16" si="5">D15</f>
         <v>49533.333333333336</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>3</v>
       </c>
-      <c r="C16" s="13">
-        <v>45998</v>
-      </c>
-      <c r="D16" s="22">
+      <c r="C16" s="26">
+        <v>46030</v>
+      </c>
+      <c r="D16" s="17">
         <f>D15</f>
         <v>49533.333333333336</v>
       </c>
-      <c r="E16" s="36">
-        <v>45778</v>
+      <c r="E16" s="26">
+        <v>46042</v>
       </c>
       <c r="F16" t="s">
-        <v>257</v>
-      </c>
-      <c r="I16" s="22">
+        <v>254</v>
+      </c>
+      <c r="I16" s="17">
         <f t="shared" si="5"/>
         <v>49533.333333333336</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>1</v>
       </c>
-      <c r="D17" s="22">
+      <c r="C17" s="26">
+        <v>45878</v>
+      </c>
+      <c r="D17" s="17">
         <f>Loan!J7/Loan!H7</f>
         <v>57666.666666666664</v>
       </c>
+      <c r="E17" s="26">
+        <v>45888</v>
+      </c>
       <c r="F17" t="s">
-        <v>258</v>
-      </c>
-      <c r="I17" s="22">
+        <v>255</v>
+      </c>
+      <c r="I17" s="17">
         <f>D17</f>
         <v>57666.666666666664</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>2</v>
       </c>
-      <c r="D18" s="22">
+      <c r="C18" s="26">
+        <v>45909</v>
+      </c>
+      <c r="D18" s="17">
         <f>Loan!J7/Loan!H7</f>
         <v>57666.666666666664</v>
       </c>
-      <c r="E18" s="36">
-        <v>45760</v>
+      <c r="E18" s="26">
+        <v>45916</v>
       </c>
       <c r="F18" t="s">
-        <v>258</v>
-      </c>
-      <c r="I18" s="22">
+        <v>255</v>
+      </c>
+      <c r="I18" s="17">
         <f t="shared" ref="I18:I19" si="6">D18</f>
         <v>57666.666666666664</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="6">
         <v>3</v>
       </c>
-      <c r="D19" s="22">
+      <c r="C19" s="26">
+        <v>45939</v>
+      </c>
+      <c r="D19" s="17">
         <f>Loan!J7/Loan!H7</f>
         <v>57666.666666666664</v>
       </c>
-      <c r="E19" s="36">
-        <v>45790</v>
+      <c r="E19" s="26">
+        <v>45951</v>
       </c>
       <c r="F19" t="s">
-        <v>258</v>
-      </c>
-      <c r="I19" s="22">
+        <v>255</v>
+      </c>
+      <c r="I19" s="17">
         <f t="shared" si="6"/>
         <v>57666.666666666664</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="6">
         <v>1</v>
       </c>
-      <c r="D20" s="22">
+      <c r="C20" s="26">
+        <v>45879</v>
+      </c>
+      <c r="D20" s="17">
         <f>Loan!J8/Loan!H8</f>
         <v>64300</v>
       </c>
-      <c r="E20" s="36">
-        <v>45737</v>
+      <c r="E20" s="26">
+        <v>45879</v>
       </c>
       <c r="F20" t="s">
-        <v>253</v>
-      </c>
-      <c r="I20" s="22">
+        <v>250</v>
+      </c>
+      <c r="I20" s="17">
         <f>D20</f>
         <v>64300</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="6">
         <v>2</v>
       </c>
-      <c r="D21" s="22">
+      <c r="C21" s="26">
+        <v>45910</v>
+      </c>
+      <c r="D21" s="17">
         <f>D20</f>
         <v>64300</v>
       </c>
-      <c r="E21" s="36">
-        <v>45767</v>
+      <c r="E21" s="26">
+        <v>45910</v>
       </c>
       <c r="F21" t="s">
-        <v>253</v>
-      </c>
-      <c r="I21" s="22">
+        <v>250</v>
+      </c>
+      <c r="I21" s="17">
         <f t="shared" ref="I21:I22" si="7">D21</f>
         <v>64300</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="6">
         <v>3</v>
       </c>
-      <c r="D22" s="22">
+      <c r="C22" s="26">
+        <v>45940</v>
+      </c>
+      <c r="D22" s="17">
         <f>D21</f>
         <v>64300</v>
       </c>
-      <c r="E22" s="36">
-        <v>45797</v>
+      <c r="E22" s="26">
+        <v>45940</v>
       </c>
       <c r="F22" t="s">
-        <v>253</v>
-      </c>
-      <c r="I22" s="22">
+        <v>250</v>
+      </c>
+      <c r="I22" s="17">
         <f t="shared" si="7"/>
         <v>64300</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="6">
         <v>1</v>
       </c>
-      <c r="D23" s="22">
+      <c r="C23" s="26">
+        <v>45880</v>
+      </c>
+      <c r="D23" s="17">
         <f>Loan!J9/Loan!H9</f>
         <v>22733.333333333332</v>
       </c>
-      <c r="E23" s="36">
-        <v>45749</v>
+      <c r="E23" s="26">
+        <v>45880</v>
       </c>
       <c r="F23" t="s">
-        <v>254</v>
-      </c>
-      <c r="I23" s="22">
+        <v>251</v>
+      </c>
+      <c r="I23" s="17">
         <f>D23</f>
         <v>22733.333333333332</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="6">
         <v>2</v>
       </c>
-      <c r="D24" s="22">
+      <c r="C24" s="26">
+        <v>45911</v>
+      </c>
+      <c r="D24" s="17">
         <f>D23</f>
         <v>22733.333333333332</v>
       </c>
-      <c r="E24" s="36">
-        <v>45784</v>
+      <c r="E24" s="26">
+        <v>45911</v>
       </c>
       <c r="F24" t="s">
-        <v>254</v>
-      </c>
-      <c r="I24" s="22">
+        <v>251</v>
+      </c>
+      <c r="I24" s="17">
         <f t="shared" ref="I24:I25" si="8">D24</f>
         <v>22733.333333333332</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
         <v>3</v>
       </c>
-      <c r="D25" s="22">
+      <c r="C25" s="26">
+        <v>45941</v>
+      </c>
+      <c r="D25" s="17">
         <f>D24</f>
         <v>22733.333333333332</v>
       </c>
-      <c r="E25" s="36">
-        <v>45819</v>
+      <c r="E25" s="26">
+        <v>45941</v>
       </c>
       <c r="F25" t="s">
-        <v>254</v>
-      </c>
-      <c r="I25" s="22">
+        <v>251</v>
+      </c>
+      <c r="I25" s="17">
         <f t="shared" si="8"/>
         <v>22733.333333333332</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <v>1</v>
       </c>
-      <c r="D26" s="22">
+      <c r="C26" s="26">
+        <v>45881</v>
+      </c>
+      <c r="D26" s="17">
         <f>Loan!J10/Loan!H10</f>
         <v>30533.333333333332</v>
       </c>
-      <c r="E26" s="36">
-        <v>45751</v>
+      <c r="E26" s="26">
+        <v>45881</v>
       </c>
       <c r="F26" t="s">
-        <v>255</v>
-      </c>
-      <c r="I26" s="22">
+        <v>252</v>
+      </c>
+      <c r="I26" s="17">
         <f>D26</f>
         <v>30533.333333333332</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="6">
         <v>2</v>
       </c>
-      <c r="D27" s="22">
+      <c r="C27" s="26">
+        <v>45912</v>
+      </c>
+      <c r="D27" s="17">
         <f>D26</f>
         <v>30533.333333333332</v>
       </c>
-      <c r="E27" s="36">
-        <v>45781</v>
+      <c r="E27" s="26">
+        <v>45912</v>
       </c>
       <c r="F27" t="s">
-        <v>255</v>
-      </c>
-      <c r="I27" s="22">
+        <v>252</v>
+      </c>
+      <c r="I27" s="17">
         <f t="shared" ref="I27:I28" si="9">D27</f>
         <v>30533.333333333332</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="6">
         <v>3</v>
       </c>
-      <c r="D28" s="22">
+      <c r="C28" s="26">
+        <v>45942</v>
+      </c>
+      <c r="D28" s="17">
         <f>D27</f>
         <v>30533.333333333332</v>
       </c>
-      <c r="E28" s="36">
-        <v>45811</v>
+      <c r="E28" s="26">
+        <v>45942</v>
       </c>
       <c r="F28" t="s">
-        <v>255</v>
-      </c>
-      <c r="I28" s="22">
+        <v>252</v>
+      </c>
+      <c r="I28" s="17">
         <f t="shared" si="9"/>
         <v>30533.333333333332</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="6">
         <v>1</v>
       </c>
-      <c r="D29" s="22">
+      <c r="C29" s="26">
+        <v>45882</v>
+      </c>
+      <c r="D29" s="17">
         <f>Loan!J11/Loan!H11</f>
         <v>38333.333333333336</v>
       </c>
+      <c r="E29" s="26">
+        <v>45948</v>
+      </c>
       <c r="F29" t="s">
-        <v>256</v>
-      </c>
-      <c r="I29" s="22">
+        <v>253</v>
+      </c>
+      <c r="I29" s="17">
         <f>D29</f>
         <v>38333.333333333336</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="6">
         <v>2</v>
       </c>
-      <c r="D30" s="22">
+      <c r="C30" s="26">
+        <v>45913</v>
+      </c>
+      <c r="D30" s="17">
         <f>D29</f>
         <v>38333.333333333336</v>
       </c>
+      <c r="E30" s="26">
+        <v>45949</v>
+      </c>
       <c r="F30" t="s">
-        <v>256</v>
-      </c>
-      <c r="I30" s="22">
+        <v>253</v>
+      </c>
+      <c r="I30" s="17">
         <f t="shared" ref="I30:I31" si="10">D30</f>
         <v>38333.333333333336</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="6">
         <v>3</v>
       </c>
-      <c r="D31" s="22">
+      <c r="C31" s="26">
+        <v>45943</v>
+      </c>
+      <c r="D31" s="17">
         <f>D30</f>
         <v>38333.333333333336</v>
       </c>
+      <c r="E31" s="26">
+        <v>45950</v>
+      </c>
       <c r="F31" t="s">
-        <v>256</v>
-      </c>
-      <c r="I31" s="22">
+        <v>253</v>
+      </c>
+      <c r="I31" s="17">
         <f t="shared" si="10"/>
         <v>38333.333333333336</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="6">
         <v>1</v>
       </c>
-      <c r="D32" s="22">
+      <c r="C32" s="26">
+        <v>45883</v>
+      </c>
+      <c r="D32" s="17">
         <f>Loan!J12/Loan!H12</f>
         <v>45800</v>
       </c>
-      <c r="E32" s="36">
-        <v>45760</v>
+      <c r="E32" s="26">
+        <v>45865</v>
       </c>
       <c r="F32" t="s">
-        <v>257</v>
-      </c>
-      <c r="I32" s="22">
+        <v>254</v>
+      </c>
+      <c r="I32" s="17">
         <f>D32</f>
         <v>45800</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="6">
         <v>2</v>
       </c>
-      <c r="D33" s="22">
+      <c r="C33" s="26">
+        <v>45914</v>
+      </c>
+      <c r="D33" s="17">
         <f>D32</f>
         <v>45800</v>
       </c>
-      <c r="E33" s="36">
-        <v>45790</v>
+      <c r="E33" s="26">
+        <v>45901</v>
       </c>
       <c r="F33" t="s">
-        <v>257</v>
-      </c>
-      <c r="I33" s="22">
+        <v>254</v>
+      </c>
+      <c r="I33" s="17">
         <f t="shared" ref="I33:I34" si="11">D33</f>
         <v>45800</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B34" s="7">
+      <c r="A34" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B34" s="6">
         <v>3</v>
       </c>
-      <c r="D34" s="22">
+      <c r="C34" s="26">
+        <v>45944</v>
+      </c>
+      <c r="D34" s="17">
         <f>D33</f>
         <v>45800</v>
       </c>
-      <c r="E34" s="36">
-        <v>45820</v>
+      <c r="E34" s="26">
+        <v>45936</v>
       </c>
       <c r="F34" t="s">
-        <v>257</v>
-      </c>
-      <c r="I34" s="22">
+        <v>254</v>
+      </c>
+      <c r="I34" s="17">
         <f t="shared" si="11"/>
         <v>45800</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="6">
         <v>1</v>
       </c>
-      <c r="D35" s="22">
+      <c r="C35" s="26">
+        <v>45884</v>
+      </c>
+      <c r="D35" s="17">
         <f>Loan!J13/Loan!H13</f>
         <v>53266.666666666664</v>
       </c>
+      <c r="E35" s="26">
+        <v>45866</v>
+      </c>
       <c r="F35" t="s">
-        <v>258</v>
-      </c>
-      <c r="I35" s="22">
+        <v>255</v>
+      </c>
+      <c r="I35" s="17">
         <f>D36</f>
         <v>53266.666666666664</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="6">
         <v>2</v>
       </c>
-      <c r="D36" s="22">
+      <c r="C36" s="26">
+        <v>45915</v>
+      </c>
+      <c r="D36" s="17">
         <f>D35</f>
         <v>53266.666666666664</v>
       </c>
-      <c r="E36" s="36">
-        <v>45802</v>
+      <c r="E36" s="26">
+        <v>45902</v>
       </c>
       <c r="F36" t="s">
-        <v>258</v>
-      </c>
-      <c r="I36" s="22">
+        <v>255</v>
+      </c>
+      <c r="I36" s="17">
         <f>D37</f>
         <v>53266.666666666664</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="6">
         <v>3</v>
       </c>
-      <c r="D37" s="22">
+      <c r="C37" s="26">
+        <v>45945</v>
+      </c>
+      <c r="D37" s="17">
         <f>D36</f>
         <v>53266.666666666664</v>
       </c>
-      <c r="E37" s="36">
-        <v>45832</v>
+      <c r="E37" s="26">
+        <v>45937</v>
       </c>
       <c r="F37" t="s">
-        <v>258</v>
-      </c>
-      <c r="I37" s="22">
+        <v>255</v>
+      </c>
+      <c r="I37" s="17">
         <f>D37</f>
         <v>53266.666666666664</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="6">
         <v>1</v>
       </c>
-      <c r="D38" s="22">
+      <c r="C38" s="26">
+        <v>45885</v>
+      </c>
+      <c r="D38" s="17">
         <f>Loan!J14/Loan!H14</f>
         <v>61400</v>
       </c>
-      <c r="E38" s="36">
-        <v>45779</v>
+      <c r="E38" s="26">
+        <v>45867</v>
       </c>
       <c r="F38" t="s">
-        <v>253</v>
-      </c>
-      <c r="I38" s="22">
+        <v>250</v>
+      </c>
+      <c r="I38" s="17">
         <f>D38</f>
         <v>61400</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="6">
         <v>2</v>
       </c>
-      <c r="D39" s="22">
+      <c r="C39" s="26">
+        <v>45916</v>
+      </c>
+      <c r="D39" s="17">
         <f>D38</f>
         <v>61400</v>
       </c>
-      <c r="E39" s="36">
-        <v>45809</v>
+      <c r="E39" s="26">
+        <v>45903</v>
       </c>
       <c r="F39" t="s">
-        <v>253</v>
-      </c>
-      <c r="I39" s="22">
+        <v>250</v>
+      </c>
+      <c r="I39" s="17">
         <f t="shared" ref="I39:I40" si="12">D39</f>
         <v>61400</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="6">
         <v>3</v>
       </c>
-      <c r="D40" s="22">
+      <c r="C40" s="26">
+        <v>45946</v>
+      </c>
+      <c r="D40" s="17">
         <f>D39</f>
         <v>61400</v>
       </c>
-      <c r="E40" s="36">
-        <v>45839</v>
+      <c r="E40" s="26">
+        <v>45938</v>
       </c>
       <c r="F40" t="s">
-        <v>253</v>
-      </c>
-      <c r="I40" s="22">
+        <v>250</v>
+      </c>
+      <c r="I40" s="17">
         <f t="shared" si="12"/>
         <v>61400</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="6">
         <v>1</v>
       </c>
-      <c r="D41" s="22">
+      <c r="C41" s="26">
+        <v>45886</v>
+      </c>
+      <c r="D41" s="17">
         <f>Loan!J15/Loan!H15</f>
         <v>68866.666666666672</v>
       </c>
-      <c r="E41" s="36">
-        <v>45791</v>
+      <c r="E41" s="26">
+        <v>45916</v>
       </c>
       <c r="F41" t="s">
-        <v>254</v>
-      </c>
-      <c r="I41" s="22">
+        <v>251</v>
+      </c>
+      <c r="I41" s="17">
         <f>D41</f>
         <v>68866.666666666672</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="6">
         <v>2</v>
       </c>
-      <c r="D42" s="22">
+      <c r="C42" s="26">
+        <v>45917</v>
+      </c>
+      <c r="D42" s="17">
         <f>D41</f>
         <v>68866.666666666672</v>
       </c>
-      <c r="E42" s="36">
-        <v>45826</v>
+      <c r="E42" s="26">
+        <v>45952</v>
       </c>
       <c r="F42" t="s">
-        <v>254</v>
-      </c>
-      <c r="I42" s="22">
+        <v>251</v>
+      </c>
+      <c r="I42" s="17">
         <f t="shared" ref="I42:I43" si="13">D42</f>
         <v>68866.666666666672</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="6">
         <v>3</v>
       </c>
-      <c r="D43" s="22">
+      <c r="C43" s="26">
+        <v>45947</v>
+      </c>
+      <c r="D43" s="17">
         <f>D42</f>
         <v>68866.666666666672</v>
       </c>
-      <c r="E43" s="36">
-        <v>45861</v>
+      <c r="E43" s="26">
+        <v>45917</v>
       </c>
       <c r="F43" t="s">
-        <v>254</v>
-      </c>
-      <c r="I43" s="22">
+        <v>251</v>
+      </c>
+      <c r="I43" s="17">
         <f t="shared" si="13"/>
         <v>68866.666666666672</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="6">
         <v>1</v>
       </c>
-      <c r="D44" s="22">
+      <c r="C44" s="26">
+        <v>45887</v>
+      </c>
+      <c r="D44" s="17">
         <f>Loan!J16/Loan!H16</f>
         <v>76333.333333333328</v>
       </c>
-      <c r="E44" s="36">
-        <v>45793</v>
+      <c r="E44" s="26">
+        <v>45953</v>
       </c>
       <c r="F44" t="s">
-        <v>255</v>
-      </c>
-      <c r="I44" s="22">
+        <v>252</v>
+      </c>
+      <c r="I44" s="17">
         <f>D44</f>
         <v>76333.333333333328</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="6">
         <v>2</v>
       </c>
-      <c r="D45" s="22">
+      <c r="C45" s="26">
+        <v>45918</v>
+      </c>
+      <c r="D45" s="17">
         <f>D44</f>
         <v>76333.333333333328</v>
       </c>
-      <c r="E45" s="36">
-        <v>45823</v>
+      <c r="E45" s="26">
+        <v>45918</v>
       </c>
       <c r="F45" t="s">
-        <v>255</v>
-      </c>
-      <c r="I45" s="22">
+        <v>252</v>
+      </c>
+      <c r="I45" s="17">
         <f t="shared" ref="I45:I46" si="14">D45</f>
         <v>76333.333333333328</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="6">
         <v>3</v>
       </c>
-      <c r="D46" s="22">
+      <c r="C46" s="26">
+        <v>45948</v>
+      </c>
+      <c r="D46" s="17">
         <f>D45</f>
         <v>76333.333333333328</v>
       </c>
-      <c r="E46" s="36">
-        <v>45853</v>
+      <c r="E46" s="26">
+        <v>45954</v>
       </c>
       <c r="F46" t="s">
-        <v>255</v>
-      </c>
-      <c r="I46" s="22">
+        <v>252</v>
+      </c>
+      <c r="I46" s="17">
         <f t="shared" si="14"/>
         <v>76333.333333333328</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="6">
         <v>1</v>
       </c>
-      <c r="D47" s="22">
+      <c r="C47" s="26">
+        <v>45888</v>
+      </c>
+      <c r="D47" s="17">
         <f>Loan!J17/Loan!H17</f>
         <v>26800</v>
       </c>
+      <c r="E47" s="26">
+        <v>45919</v>
+      </c>
       <c r="F47" t="s">
-        <v>256</v>
-      </c>
-      <c r="I47" s="22">
+        <v>253</v>
+      </c>
+      <c r="I47" s="17">
         <f>D47</f>
         <v>26800</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="6">
         <v>2</v>
       </c>
-      <c r="D48" s="22">
+      <c r="C48" s="26">
+        <v>45919</v>
+      </c>
+      <c r="D48" s="17">
         <f>D47</f>
         <v>26800</v>
       </c>
+      <c r="E48" s="26">
+        <v>45955</v>
+      </c>
       <c r="F48" t="s">
-        <v>256</v>
-      </c>
-      <c r="I48" s="22">
+        <v>253</v>
+      </c>
+      <c r="I48" s="17">
         <f t="shared" ref="I48:I49" si="15">D48</f>
         <v>26800</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A49" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="B49" s="7">
+      <c r="A49" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B49" s="6">
         <v>3</v>
       </c>
-      <c r="D49" s="22">
+      <c r="C49" s="26">
+        <v>45949</v>
+      </c>
+      <c r="D49" s="17">
         <f>D48</f>
         <v>26800</v>
       </c>
+      <c r="E49" s="26">
+        <v>45920</v>
+      </c>
       <c r="F49" t="s">
-        <v>256</v>
-      </c>
-      <c r="I49" s="22">
+        <v>253</v>
+      </c>
+      <c r="I49" s="17">
         <f t="shared" si="15"/>
         <v>26800</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="6">
         <v>1</v>
       </c>
-      <c r="D50" s="22">
+      <c r="C50" s="26">
+        <v>45889</v>
+      </c>
+      <c r="D50" s="17">
         <f>Loan!J18/Loan!H18</f>
         <v>34266.666666666664</v>
       </c>
-      <c r="E50" s="36">
-        <v>45802</v>
+      <c r="E50" s="26">
+        <v>45956</v>
       </c>
       <c r="F50" t="s">
-        <v>257</v>
-      </c>
-      <c r="I50" s="22">
+        <v>254</v>
+      </c>
+      <c r="I50" s="17">
         <f>D50</f>
         <v>34266.666666666664</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="6">
         <v>2</v>
       </c>
-      <c r="D51" s="22">
+      <c r="C51" s="26">
+        <v>45920</v>
+      </c>
+      <c r="D51" s="17">
         <f>D50</f>
         <v>34266.666666666664</v>
       </c>
-      <c r="E51" s="36">
-        <v>45832</v>
+      <c r="E51" s="26">
+        <v>45952</v>
       </c>
       <c r="F51" t="s">
-        <v>257</v>
-      </c>
-      <c r="I51" s="22">
+        <v>254</v>
+      </c>
+      <c r="I51" s="17">
         <f t="shared" ref="I51:I52" si="16">D51</f>
         <v>34266.666666666664</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A52" s="7" t="s">
+      <c r="A52" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="6">
         <v>3</v>
       </c>
-      <c r="D52" s="22">
+      <c r="C52" s="26">
+        <v>45950</v>
+      </c>
+      <c r="D52" s="17">
         <f>D51</f>
         <v>34266.666666666664</v>
       </c>
-      <c r="E52" s="36">
-        <v>45862</v>
+      <c r="E52" s="26">
+        <v>45963</v>
       </c>
       <c r="F52" t="s">
-        <v>257</v>
-      </c>
-      <c r="I52" s="22">
+        <v>254</v>
+      </c>
+      <c r="I52" s="17">
         <f t="shared" si="16"/>
         <v>34266.666666666664</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A53" s="7" t="s">
+      <c r="A53" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="6">
         <v>1</v>
       </c>
-      <c r="D53" s="22">
+      <c r="C53" s="26">
+        <v>45890</v>
+      </c>
+      <c r="D53" s="17">
         <f>Loan!J19/Loan!H19</f>
         <v>42066.666666666664</v>
       </c>
+      <c r="E53" s="26">
+        <v>45973</v>
+      </c>
       <c r="F53" t="s">
-        <v>258</v>
-      </c>
-      <c r="I53" s="22">
+        <v>255</v>
+      </c>
+      <c r="I53" s="17">
         <f>D53</f>
         <v>42066.666666666664</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="6">
         <v>2</v>
       </c>
-      <c r="D54" s="22">
+      <c r="C54" s="26">
+        <v>45921</v>
+      </c>
+      <c r="D54" s="17">
         <f>D53</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E54" s="36">
-        <v>45844</v>
-      </c>
       <c r="F54" t="s">
-        <v>258</v>
-      </c>
-      <c r="I54" s="22">
+        <v>255</v>
+      </c>
+      <c r="I54" s="17">
         <f t="shared" ref="I54:I55" si="17">D54</f>
         <v>42066.666666666664</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="6">
         <v>3</v>
       </c>
-      <c r="D55" s="22">
+      <c r="C55" s="26">
+        <v>45951</v>
+      </c>
+      <c r="D55" s="17">
         <f>D54</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E55" s="36">
-        <v>45874</v>
-      </c>
       <c r="F55" t="s">
-        <v>258</v>
-      </c>
-      <c r="I55" s="22">
+        <v>255</v>
+      </c>
+      <c r="I55" s="17">
         <f t="shared" si="17"/>
         <v>42066.666666666664</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="6">
         <v>1</v>
       </c>
-      <c r="D56" s="22">
+      <c r="C56" s="26">
+        <v>45891</v>
+      </c>
+      <c r="D56" s="17">
         <f>Loan!J20/Loan!H20</f>
         <v>19000</v>
       </c>
-      <c r="E56" s="36">
-        <v>45821</v>
-      </c>
       <c r="F56" t="s">
-        <v>253</v>
-      </c>
-      <c r="I56" s="22">
+        <v>250</v>
+      </c>
+      <c r="I56" s="17">
         <f>D56</f>
         <v>19000</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="6">
         <v>2</v>
       </c>
-      <c r="D57" s="22">
+      <c r="C57" s="26">
+        <v>45922</v>
+      </c>
+      <c r="D57" s="17">
         <f>D56</f>
         <v>19000</v>
       </c>
-      <c r="E57" s="36">
-        <v>45851</v>
-      </c>
       <c r="F57" t="s">
-        <v>253</v>
-      </c>
-      <c r="I57" s="22">
+        <v>250</v>
+      </c>
+      <c r="I57" s="17">
         <f t="shared" ref="I57:I58" si="18">D57</f>
         <v>19000</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="6">
         <v>3</v>
       </c>
-      <c r="D58" s="22">
+      <c r="C58" s="26">
+        <v>45952</v>
+      </c>
+      <c r="D58" s="17">
         <f>D56</f>
         <v>19000</v>
       </c>
-      <c r="E58" s="36">
-        <v>45881</v>
-      </c>
       <c r="F58" t="s">
-        <v>253</v>
-      </c>
-      <c r="I58" s="22">
+        <v>250</v>
+      </c>
+      <c r="I58" s="17">
         <f t="shared" si="18"/>
         <v>19000</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="6">
         <v>1</v>
       </c>
-      <c r="D59" s="22">
+      <c r="C59" s="26">
+        <v>45892</v>
+      </c>
+      <c r="D59" s="17">
         <f>Loan!J21/Loan!H21</f>
         <v>28333.333333333332</v>
       </c>
-      <c r="E59" s="36">
-        <v>45833</v>
-      </c>
       <c r="F59" t="s">
-        <v>254</v>
-      </c>
-      <c r="I59" s="22">
+        <v>251</v>
+      </c>
+      <c r="I59" s="17">
         <f>D59</f>
         <v>28333.333333333332</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="6">
         <v>2</v>
       </c>
-      <c r="D60" s="22">
+      <c r="C60" s="26">
+        <v>45923</v>
+      </c>
+      <c r="D60" s="17">
         <f>D59</f>
         <v>28333.333333333332</v>
       </c>
-      <c r="E60" s="36">
-        <v>45868</v>
-      </c>
       <c r="F60" t="s">
-        <v>254</v>
-      </c>
-      <c r="I60" s="22">
+        <v>251</v>
+      </c>
+      <c r="I60" s="17">
         <f t="shared" ref="I60:I61" si="19">D60</f>
         <v>28333.333333333332</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="6">
         <v>3</v>
       </c>
-      <c r="D61" s="22">
+      <c r="C61" s="26">
+        <v>45953</v>
+      </c>
+      <c r="D61" s="17">
         <f>D59</f>
         <v>28333.333333333332</v>
       </c>
-      <c r="E61" s="36">
-        <v>45903</v>
-      </c>
       <c r="F61" t="s">
-        <v>254</v>
-      </c>
-      <c r="I61" s="22">
+        <v>251</v>
+      </c>
+      <c r="I61" s="17">
         <f t="shared" si="19"/>
         <v>28333.333333333332</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A62" s="7"/>
+      <c r="A62" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3053,7 +3198,7 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
@@ -3061,262 +3206,262 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>45839</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>300000</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>12</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>720</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>20000</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>29000</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>1</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3328,248 +3473,248 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>45840</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>300000</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>24</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>5000</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>12</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>46205</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3583,151 +3728,151 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>1</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>45871</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>25000</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>6000</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>500</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>39</v>
       </c>
     </row>
@@ -3741,128 +3886,128 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>45870</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>31500</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>161</v>
       </c>
     </row>
@@ -3876,44 +4021,44 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.90625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>45900</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -3921,19 +4066,19 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>66</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -3941,19 +4086,19 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>275000</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -3961,19 +4106,19 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>6000</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -3981,19 +4126,19 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>15</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -4001,19 +4146,19 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>174</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -4021,19 +4166,19 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>177</v>
       </c>
       <c r="F8" s="2" t="s">
@@ -4041,19 +4186,19 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>0</v>
       </c>
       <c r="F9" s="2" t="s">
@@ -4061,8 +4206,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="4"/>
-      <c r="B12" s="7" t="s">
+      <c r="A12" s="3"/>
+      <c r="B12" s="6" t="s">
         <v>180</v>
       </c>
     </row>
@@ -4076,21 +4221,21 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.90625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" style="22" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.90625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>227</v>
+      <c r="B1" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -4098,28 +4243,28 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>228</v>
+      <c r="B2" s="7" t="s">
+        <v>227</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>16</v>
@@ -4127,28 +4272,28 @@
       <c r="D2" s="2">
         <v>32</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="15">
         <v>250000</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>18</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="7">
         <v>46025</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>229</v>
+      <c r="B3" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
@@ -4156,28 +4301,28 @@
       <c r="D3" s="2">
         <v>27</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="15">
         <v>180000</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>17</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="7">
         <v>46025</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>230</v>
+      <c r="B4" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>18</v>
@@ -4185,28 +4330,28 @@
       <c r="D4" s="2">
         <v>41</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="15">
         <v>520000</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>16</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <v>46055</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>231</v>
+      <c r="B5" s="7" t="s">
+        <v>230</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
@@ -4214,28 +4359,28 @@
       <c r="D5" s="2">
         <v>36</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="15">
         <v>320000</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>15</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>46054</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>232</v>
+      <c r="B6" s="7" t="s">
+        <v>231</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
@@ -4243,28 +4388,28 @@
       <c r="D6" s="2">
         <v>29</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="15">
         <v>150000</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>14</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>45728</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>233</v>
+      <c r="B7" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>21</v>
@@ -4272,28 +4417,28 @@
       <c r="D7" s="2">
         <v>38</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="15">
         <v>470000</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>13</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <v>45759</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>234</v>
+      <c r="B8" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>86</v>
@@ -4301,28 +4446,28 @@
       <c r="D8" s="2">
         <v>24</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="15">
         <v>170000</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>12</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>45787</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>235</v>
+      <c r="B9" s="7" t="s">
+        <v>234</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>87</v>
@@ -4330,28 +4475,28 @@
       <c r="D9" s="2">
         <v>45</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="15">
         <v>600000</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>11</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <v>45785</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>236</v>
+      <c r="B10" s="7" t="s">
+        <v>235</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>89</v>
@@ -4359,28 +4504,28 @@
       <c r="D10" s="2">
         <v>30</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="15">
         <v>210000</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>10</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="7">
         <v>45813</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>237</v>
+      <c r="B11" s="5" t="s">
+        <v>236</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>109</v>
@@ -4388,86 +4533,86 @@
       <c r="D11" s="2">
         <v>34</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="15">
         <v>390000</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>9</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="5" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>238</v>
+      <c r="B12" s="7" t="s">
+        <v>237</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D12" s="2">
         <v>32</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="15">
         <v>250000</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>18</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>46025</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>239</v>
+      <c r="B13" s="7" t="s">
+        <v>238</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D13" s="2">
         <v>27</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="15">
         <v>180000</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>17</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <v>46025</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>240</v>
+      <c r="B14" s="7" t="s">
+        <v>239</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>18</v>
@@ -4475,28 +4620,28 @@
       <c r="D14" s="2">
         <v>41</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="15">
         <v>520000</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>16</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <v>46055</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>241</v>
+      <c r="B15" s="7" t="s">
+        <v>240</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>87</v>
@@ -4504,57 +4649,57 @@
       <c r="D15" s="2">
         <v>36</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="15">
         <v>320000</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>15</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="7">
         <v>46054</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>242</v>
+      <c r="B16" s="7" t="s">
+        <v>241</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D16" s="2">
         <v>29</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="15">
         <v>150000</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="6">
         <v>14</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <v>45728</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>243</v>
+      <c r="B17" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>21</v>
@@ -4562,28 +4707,28 @@
       <c r="D17" s="2">
         <v>38</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="15">
         <v>470000</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <v>13</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <v>45759</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>244</v>
+      <c r="B18" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>86</v>
@@ -4591,28 +4736,28 @@
       <c r="D18" s="2">
         <v>24</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="15">
         <v>170000</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="6">
         <v>12</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="7">
         <v>45787</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>245</v>
+      <c r="B19" s="7" t="s">
+        <v>244</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>87</v>
@@ -4620,28 +4765,28 @@
       <c r="D19" s="2">
         <v>45</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="15">
         <v>600000</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>11</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="7">
         <v>45785</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>246</v>
+      <c r="B20" s="7" t="s">
+        <v>245</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>89</v>
@@ -4649,28 +4794,28 @@
       <c r="D20" s="2">
         <v>30</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="15">
         <v>210000</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>10</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="7">
         <v>45813</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>247</v>
+      <c r="B21" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>109</v>
@@ -4678,19 +4823,19 @@
       <c r="D21" s="2">
         <v>34</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="15">
         <v>390000</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="6">
         <v>9</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="5" t="s">
         <v>183</v>
       </c>
     </row>
@@ -4705,50 +4850,50 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" style="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" style="22" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7265625" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>96</v>
       </c>
     </row>
@@ -4756,34 +4901,34 @@
       <c r="A2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>45810</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="13">
         <v>300000</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>3</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>725</v>
       </c>
-      <c r="H2" s="20">
+      <c r="H2" s="15">
         <v>20000</v>
       </c>
-      <c r="I2" s="20">
+      <c r="I2" s="15">
         <v>29500</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="6">
         <v>1</v>
       </c>
     </row>
@@ -4791,34 +4936,34 @@
       <c r="A3" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>45811</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="13">
         <v>100000</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>3</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>650</v>
       </c>
-      <c r="H3" s="20">
+      <c r="H3" s="15">
         <v>15000</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="15">
         <v>18500</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="6">
         <v>1</v>
       </c>
     </row>
@@ -4826,34 +4971,34 @@
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>45812</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="13">
         <v>500000</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>3</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>780</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="15">
         <v>30000</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="15">
         <v>37000</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>1</v>
       </c>
     </row>
@@ -4861,34 +5006,34 @@
       <c r="A5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>45813</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="13">
         <v>600000</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>590</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="15">
         <v>45000</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="15">
         <v>43000</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4896,34 +5041,34 @@
       <c r="A6" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>45814</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="13">
         <v>80000</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <v>3</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>520</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="15">
         <v>22000</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="15">
         <v>28500</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4931,34 +5076,34 @@
       <c r="A7" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>45815</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="13">
         <v>700000</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>3</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>735</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="15">
         <v>35000</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="15">
         <v>47000</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <v>1</v>
       </c>
     </row>
@@ -4966,34 +5111,34 @@
       <c r="A8" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>45816</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="13">
         <v>200000</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>3</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>680</v>
       </c>
-      <c r="H8" s="20">
+      <c r="H8" s="15">
         <v>12000</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="15">
         <v>21000</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5001,34 +5146,34 @@
       <c r="A9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>45817</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="13">
         <v>1000000</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>3</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>760</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="15">
         <v>60000</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="15">
         <v>52000</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5036,34 +5181,34 @@
       <c r="A10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>45818</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="13">
         <v>120000</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>3</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>605</v>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="15">
         <v>18000</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="15">
         <v>21000</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5071,34 +5216,34 @@
       <c r="A11" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>45819</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="13">
         <v>350000</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>3</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>745</v>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="15">
         <v>20000</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="15">
         <v>33000</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5106,34 +5251,34 @@
       <c r="A12" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>45820</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="13">
         <v>120000</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>3</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>730</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="15">
         <v>15000</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="15">
         <v>22000</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5141,34 +5286,34 @@
       <c r="A13" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>45821</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="13">
         <v>900000</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>3</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="6">
         <v>790</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="15">
         <v>40000</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="15">
         <v>61000</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5176,34 +5321,34 @@
       <c r="A14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>45822</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="13">
         <v>250000</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>3</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>540</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="15">
         <v>25000</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="15">
         <v>26000</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="6">
         <v>0</v>
       </c>
     </row>
@@ -5211,34 +5356,34 @@
       <c r="A15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>45823</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="13">
         <v>150000</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>3</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="6">
         <v>770</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="15">
         <v>18000</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="15">
         <v>24000</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5246,34 +5391,34 @@
       <c r="A16" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>45824</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="13">
         <v>300000</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>3</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="6">
         <v>610</v>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="15">
         <v>28000</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="15">
         <v>31000</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="6">
         <v>0</v>
       </c>
     </row>
@@ -5281,34 +5426,34 @@
       <c r="A17" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>45825</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="14">
         <v>240000</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>3</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="6">
         <v>450</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="17">
         <v>15000</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="17">
         <v>55000</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5316,34 +5461,34 @@
       <c r="A18" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>45826</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="14">
         <v>150000</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>3</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="6">
         <v>500</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="17">
         <v>35000</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="17">
         <v>24000</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5351,34 +5496,34 @@
       <c r="A19" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>45827</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="14">
         <v>250000</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>3</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="6">
         <v>600</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="17">
         <v>25000</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="17">
         <v>60000</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5386,34 +5531,34 @@
       <c r="A20" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>45828</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="14">
         <v>600000</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <v>3</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="6">
         <v>342</v>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="17">
         <v>8000</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="17">
         <v>250000</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5421,34 +5566,34 @@
       <c r="A21" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>45829</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="14">
         <v>450000</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <v>3</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="6">
         <v>768</v>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="17">
         <v>3000</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="17">
         <v>120000</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5459,92 +5604,93 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:T50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.36328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" style="36" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.7265625" style="6"/>
-    <col min="14" max="14" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.26953125" style="17" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.7265625" style="5"/>
+    <col min="14" max="14" width="21.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.90625" style="5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.36328125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="22.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="27" t="s">
         <v>213</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="40" t="s">
         <v>214</v>
       </c>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>45840</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="13">
         <v>50000</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="9">
         <f>48%/12</f>
         <v>0.04</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="15">
         <v>1000</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="6">
         <v>3</v>
       </c>
-      <c r="I2" s="8">
-        <v>46298</v>
-      </c>
-      <c r="J2" s="7">
+      <c r="I2" s="7">
+        <v>46297</v>
+      </c>
+      <c r="J2" s="15">
         <f>E2*F2*3+E2+G2</f>
         <v>57000</v>
       </c>
@@ -5553,32 +5699,32 @@
       <c r="A3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>45872</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="13">
         <v>70000</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="9">
         <f t="shared" ref="F3:F21" si="0">48%/12</f>
         <v>0.04</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="15">
         <v>3000</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="6">
         <v>3</v>
       </c>
-      <c r="I3" s="8">
-        <v>46299</v>
-      </c>
-      <c r="J3" s="7">
+      <c r="I3" s="7">
+        <v>46330</v>
+      </c>
+      <c r="J3" s="15">
         <f>E3*F3*3+G3+E3</f>
         <v>81400</v>
       </c>
@@ -5587,32 +5733,32 @@
       <c r="A4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>45842</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="13">
         <v>90000</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="15">
         <v>2000</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>3</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="7">
         <v>46300</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="15">
         <f>E2*F2*3+G4+E4</f>
         <v>98000</v>
       </c>
@@ -5621,32 +5767,32 @@
       <c r="A5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="7">
         <v>45907</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="13">
         <v>110000</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="15">
         <v>3000</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="6">
         <v>3</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="7">
         <v>46301</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="15">
         <f t="shared" ref="J5:J21" si="1">E5*F5*H5+G5+E5</f>
         <v>126200</v>
       </c>
@@ -5655,32 +5801,32 @@
       <c r="A6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>45938</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="13">
         <v>130000</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="15">
         <v>3000</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="6">
         <v>3</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="7">
         <v>46302</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="15">
         <f t="shared" si="1"/>
         <v>148600</v>
       </c>
@@ -5689,32 +5835,32 @@
       <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>45847</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="13">
         <v>150000</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="15">
         <v>5000</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="6">
         <v>3</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="7">
         <v>46303</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
         <v>173000</v>
       </c>
@@ -5723,32 +5869,32 @@
       <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>45848</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="13">
         <v>170000</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="15">
         <v>2500</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="6">
         <v>3</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="7">
         <v>46304</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
         <v>192900</v>
       </c>
@@ -5757,32 +5903,32 @@
       <c r="A9" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>45849</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="13">
         <v>60000</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="15">
         <v>1000</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="6">
         <v>3</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="7">
         <v>46305</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
         <v>68200</v>
       </c>
@@ -5791,32 +5937,32 @@
       <c r="A10" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>45850</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="13">
         <v>80000</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="15">
         <v>2000</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="6">
         <v>3</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="7">
         <v>46306</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
         <v>91600</v>
       </c>
@@ -5825,32 +5971,32 @@
       <c r="A11" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>45851</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="13">
         <v>100000</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="15">
         <v>3000</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="6">
         <v>3</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="7">
         <v>46307</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
         <v>115000</v>
       </c>
@@ -5859,32 +6005,32 @@
       <c r="A12" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>45852</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="13">
         <v>120000</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="15">
         <v>3000</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>3</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="7">
         <v>46308</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
         <v>137400</v>
       </c>
@@ -5893,32 +6039,32 @@
       <c r="A13" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>45853</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="13">
         <v>140000</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="15">
         <v>3000</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="6">
         <v>3</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <v>46309</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
         <v>159800</v>
       </c>
@@ -5927,32 +6073,32 @@
       <c r="A14" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>45854</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="13">
         <v>160000</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="17">
         <v>5000</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>3</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <v>46310</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
         <v>184200</v>
       </c>
@@ -5961,32 +6107,32 @@
       <c r="A15" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>45855</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="13">
         <v>180000</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="17">
         <v>5000</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="6">
         <v>3</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="7">
         <v>46311</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
         <v>206600</v>
       </c>
@@ -5995,536 +6141,610 @@
       <c r="A16" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>45856</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="13">
         <v>200000</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="17">
         <v>5000</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="6">
         <v>3</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="7">
         <v>46312</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
         <v>229000</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>45857</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="13">
         <v>70000</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="17">
         <v>2000</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="6">
         <v>3</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="7">
         <v>46313</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
         <v>80400</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>45858</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="13">
         <v>90000</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="17">
         <v>2000</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="6">
         <v>3</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="7">
         <v>46314</v>
       </c>
-      <c r="J18" s="7">
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
         <v>102800</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>45859</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="13">
         <v>110000</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="17">
         <v>3000</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="6">
         <v>3</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="7">
         <v>46315</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
         <v>126200</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>45860</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="13">
         <v>50000</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="17">
         <v>1000</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="6">
         <v>3</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="7">
         <v>46316</v>
       </c>
-      <c r="J20" s="7">
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
         <v>57000</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>45861</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="13">
         <v>75000</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="9">
         <f t="shared" si="0"/>
         <v>0.04</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="17">
         <v>1000</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="6">
         <v>3</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="7">
         <v>46317</v>
       </c>
-      <c r="J21" s="7">
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
         <v>85000</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="K22" s="15" t="s">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="K22" s="11" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B23" s="17" t="s">
-        <v>223</v>
-      </c>
-      <c r="L23" s="15" t="s">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="36"/>
+      <c r="B23"/>
+      <c r="C23" s="17"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="11" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>142</v>
+      <c r="J23" s="5"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="36"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="37" t="s">
+        <v>220</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="H24" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="E24" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="J24" s="14" t="s">
+      <c r="F24" s="37" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="2">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3">
-        <v>45872</v>
-      </c>
-      <c r="D25" s="10">
-        <f>J2/H2</f>
-        <v>19000</v>
-      </c>
-      <c r="G25" s="13"/>
-      <c r="H25" s="16">
-        <f>SUMIFS(D25:D27, A25:A27,A2, C25:C27, "&lt;="&amp;C27)</f>
-        <v>57000</v>
-      </c>
-      <c r="I25" s="6">
-        <f>SUMIFS(D25:D27, A25:A27,A2, C25:C27, "&lt;="&amp;C27)</f>
-        <v>57000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="2">
-        <v>2</v>
-      </c>
-      <c r="C26" s="3">
-        <v>45903</v>
-      </c>
-      <c r="D26" s="10">
-        <f>J2/H2</f>
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="2">
-        <v>3</v>
-      </c>
-      <c r="C27" s="3">
-        <v>45933</v>
-      </c>
-      <c r="D27" s="10">
-        <f>J2/H2</f>
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="2">
-        <v>1</v>
-      </c>
-      <c r="C28" s="3">
-        <v>45903</v>
-      </c>
-      <c r="D28" s="10">
-        <f>J3/H3</f>
-        <v>27133.333333333332</v>
-      </c>
-      <c r="G28" s="13"/>
-      <c r="H28" s="6">
-        <f>SUMIFS(D28:D30, A28:A30,A3,C28:C30,"&lt;="&amp;C30)</f>
-        <v>81400</v>
-      </c>
-      <c r="I28" s="6">
-        <f>SUMIFS(D28:D30, A28:A30,A3,C28:C30,"&lt;="&amp;C30)</f>
-        <v>81400</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B29" s="2">
-        <v>2</v>
-      </c>
-      <c r="C29" s="3">
-        <v>45933</v>
-      </c>
-      <c r="D29" s="10">
-        <f>J3/H3</f>
-        <v>27133.333333333332</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="2">
-        <v>3</v>
-      </c>
-      <c r="C30" s="3">
-        <v>45964</v>
-      </c>
-      <c r="D30" s="10">
-        <f>J3/H3</f>
-        <v>27133.333333333332</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="23">
-        <v>1</v>
-      </c>
-      <c r="C31" s="24">
-        <v>45874</v>
-      </c>
-      <c r="D31" s="25">
-        <f>J4/H4</f>
-        <v>32666.666666666668</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="23">
-        <v>2</v>
-      </c>
-      <c r="C32" s="24">
-        <v>45905</v>
-      </c>
-      <c r="D32" s="25">
-        <f>J4/H4</f>
-        <v>32666.666666666668</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="23">
-        <v>3</v>
-      </c>
-      <c r="C33" s="24">
-        <v>45935</v>
-      </c>
-      <c r="D33" s="26">
-        <f>D32</f>
-        <v>32666.666666666668</v>
-      </c>
-      <c r="H33" s="6">
-        <f>SUMIFS(D31:D33, A31:A33, A4, C31:C33, "&lt;="&amp;C33)</f>
-        <v>98000</v>
-      </c>
-      <c r="I33" s="6">
-        <f>SUMIFS(D31:D32,A31:A32, A4,C31:C32, "&lt;="&amp;C33)</f>
-        <v>65333.333333333336</v>
-      </c>
-      <c r="J33" s="13">
-        <f>C33</f>
-        <v>45935</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B34" s="2">
-        <v>1</v>
-      </c>
-      <c r="C34" s="13">
-        <v>45937</v>
-      </c>
-      <c r="D34" s="6">
-        <f>J5/H5</f>
-        <v>42066.666666666664</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="2">
-        <v>2</v>
-      </c>
-      <c r="C35" s="13">
-        <v>45968</v>
-      </c>
-      <c r="D35" s="6">
-        <f>J5/H5</f>
-        <v>42066.666666666664</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="2">
-        <v>3</v>
-      </c>
-      <c r="C36" s="13">
-        <v>45998</v>
-      </c>
-      <c r="D36" s="6">
-        <f>J5/H5</f>
-        <v>42066.666666666664</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="2">
-        <v>1</v>
-      </c>
-      <c r="D37" s="6">
-        <f>J6/H6</f>
-        <v>49533.333333333336</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B38" s="2">
-        <v>2</v>
-      </c>
-      <c r="D38" s="6">
-        <f>J6/H5</f>
-        <v>49533.333333333336</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="2">
-        <v>3</v>
-      </c>
-      <c r="D39" s="6">
-        <f>J6/H6</f>
-        <v>49533.333333333336</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>195</v>
-      </c>
+      <c r="G24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="36"/>
+      <c r="B25"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="12" t="e">
+        <f>SUMIFS(#REF!,#REF!, A2,#REF!, "&lt;="&amp;#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E25" s="5" t="e">
+        <f>SUMIFS(#REF!,#REF!, A2,#REF!, "&lt;="&amp;#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F25" s="17"/>
+      <c r="G25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="36"/>
+      <c r="B26"/>
+      <c r="C26" s="17"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="36"/>
+      <c r="B27"/>
+      <c r="C27" s="17"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="36"/>
+      <c r="B28"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="5" t="e">
+        <f>SUMIFS(#REF!,#REF!, A3,#REF!,"&lt;="&amp;#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E28" s="5" t="e">
+        <f>SUMIFS(#REF!,#REF!, A3,#REF!,"&lt;="&amp;#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F28" s="17"/>
+      <c r="G28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="36"/>
+      <c r="B29"/>
+      <c r="C29" s="17"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="36"/>
+      <c r="B30"/>
+      <c r="C30" s="17"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="36"/>
+      <c r="B31"/>
+      <c r="C31" s="17"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="36"/>
+      <c r="B32"/>
+      <c r="C32" s="17"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" s="36"/>
+      <c r="B33"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="5" t="e">
+        <f>SUMIFS(#REF!,#REF!, A4,#REF!, "&lt;="&amp;#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E33" s="5" t="e">
+        <f>SUMIFS(#REF!,#REF!, A4,#REF!, "&lt;="&amp;#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F33" s="17" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" s="36"/>
+      <c r="B34"/>
+      <c r="C34" s="17"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="36"/>
+      <c r="B35"/>
+      <c r="C35" s="17"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="36"/>
+      <c r="B36"/>
+      <c r="C36" s="17"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" s="36"/>
+      <c r="B37"/>
+      <c r="C37" s="17"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" s="36"/>
+      <c r="B38"/>
+      <c r="C38" s="17"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" s="36"/>
+      <c r="B39"/>
+      <c r="C39" s="17"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" s="36"/>
+      <c r="B40"/>
+      <c r="C40" s="17"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" s="36"/>
+      <c r="B41"/>
+      <c r="C41" s="17"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42" s="36"/>
+      <c r="B42"/>
+      <c r="C42" s="17"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43" s="36"/>
+      <c r="B43"/>
+      <c r="C43" s="17"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="36"/>
+      <c r="B44"/>
+      <c r="C44" s="17"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45" s="36"/>
+      <c r="B45"/>
+      <c r="C45" s="17"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" s="36"/>
+      <c r="B46"/>
+      <c r="C46" s="17"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" s="36"/>
+      <c r="B47"/>
+      <c r="C47" s="17"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" s="36"/>
+      <c r="B48"/>
+      <c r="C48" s="17"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A49" s="36"/>
+      <c r="B49"/>
+      <c r="C49" s="17"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A50" s="36"/>
+      <c r="B50"/>
+      <c r="C50" s="17"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Application" sheetId="5" r:id="rId8"/>
     <sheet name="Loan" sheetId="2" r:id="rId9"/>
     <sheet name="Installment" sheetId="12" r:id="rId10"/>
+    <sheet name="Formula Allocation" sheetId="13" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="292">
   <si>
     <t>signup_date</t>
   </si>
@@ -807,6 +808,108 @@
   </si>
   <si>
     <t>outstanding</t>
+  </si>
+  <si>
+    <t>Formula / Rule</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Monthly rate</t>
+  </si>
+  <si>
+    <t>Annual interest rate / 12</t>
+  </si>
+  <si>
+    <t>Converts annual nominal rate to monthly rate.</t>
+  </si>
+  <si>
+    <t>Maturity date</t>
+  </si>
+  <si>
+    <t>EDATE(disbursement date, term_months)</t>
+  </si>
+  <si>
+    <t>Generates contractual maturity date without hard-coding.</t>
+  </si>
+  <si>
+    <t>Instalment due</t>
+  </si>
+  <si>
+    <t>Principal/term + Principal × monthly rate</t>
+  </si>
+  <si>
+    <t>Flat-rate scheduled instalment; processing fee is tracked separately.</t>
+  </si>
+  <si>
+    <t>Cumulative due</t>
+  </si>
+  <si>
+    <t>SUMIFS(amount_due, loan_id, current loan, instalment no &lt;= current)</t>
+  </si>
+  <si>
+    <t>Tracks the contractual amount due up to each instalment.</t>
+  </si>
+  <si>
+    <t>Payments to reporting date</t>
+  </si>
+  <si>
+    <t>SUMIFS(payment_amount, loan_id, current loan, payment_date &lt;= reporting date)</t>
+  </si>
+  <si>
+    <t>Prevents future payments from affecting DPD.</t>
+  </si>
+  <si>
+    <t>FIFO allocation</t>
+  </si>
+  <si>
+    <t>MAX(0, MIN(current amount due, total paid - prior cumulative due))</t>
+  </si>
+  <si>
+    <t>Applies payments to the oldest unpaid instalment first.</t>
+  </si>
+  <si>
+    <t>Arrears</t>
+  </si>
+  <si>
+    <t>MAX(0, cumulative due - cumulative allocated payment)</t>
+  </si>
+  <si>
+    <t>Shows unpaid contractual amount.</t>
+  </si>
+  <si>
+    <t>Oldest unpaid due date</t>
+  </si>
+  <si>
+    <t>MINIFS(due_date where arrears &gt; 0)</t>
+  </si>
+  <si>
+    <t>Identifies the earliest outstanding obligation.</t>
+  </si>
+  <si>
+    <t>MAX(0, reporting date - oldest unpaid due date)</t>
+  </si>
+  <si>
+    <t>Measures days past due; never negative.</t>
+  </si>
+  <si>
+    <t>Current / 1–7 / 8–30 / 31–60 / 61–90 / 90+</t>
+  </si>
+  <si>
+    <t>Standardises delinquency segmentation.</t>
+  </si>
+  <si>
+    <t>Fee treatment</t>
+  </si>
+  <si>
+    <t>Processing fee is charged once at origination and excluded from instalment allocation</t>
+  </si>
+  <si>
+    <t>Keeps repayment allocation focused on scheduled instalments while retaining total borrowing cost.</t>
   </si>
 </sst>
 </file>
@@ -919,7 +1022,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -977,6 +1080,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1009,6 +1115,11 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1527,43 +1638,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="32" t="s">
         <v>256</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="J1" s="33" t="s">
+      <c r="J1" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="L1" s="33" t="s">
+      <c r="L1" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="M1" s="35" t="s">
+      <c r="M1" s="36" t="s">
         <v>217</v>
       </c>
     </row>
@@ -1574,14 +1685,14 @@
       <c r="B2" s="6">
         <v>1</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="27">
         <v>45871</v>
       </c>
       <c r="D2" s="18">
         <f>Loan!J2/Loan!H2</f>
         <v>19000</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="27">
         <v>45871</v>
       </c>
       <c r="F2" t="s">
@@ -1607,14 +1718,14 @@
       <c r="B3" s="6">
         <v>2</v>
       </c>
-      <c r="C3" s="26">
+      <c r="C3" s="27">
         <v>45902</v>
       </c>
       <c r="D3" s="18">
         <f>Loan!J2/Loan!H2</f>
         <v>19000</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <v>45902</v>
       </c>
       <c r="F3" t="s">
@@ -1640,14 +1751,14 @@
       <c r="B4" s="6">
         <v>3</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>45932</v>
       </c>
       <c r="D4" s="18">
         <f>Loan!J2/Loan!H2</f>
         <v>19000</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>45932</v>
       </c>
       <c r="F4" t="s">
@@ -1673,14 +1784,14 @@
       <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <v>45903</v>
       </c>
       <c r="D5" s="18">
         <f>Loan!J3/Loan!H3</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <v>45903</v>
       </c>
       <c r="F5" t="s">
@@ -1714,14 +1825,14 @@
       <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>45933</v>
       </c>
       <c r="D6" s="18">
         <f>D5</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>45933</v>
       </c>
       <c r="F6" t="s">
@@ -1755,14 +1866,14 @@
       <c r="B7" s="6">
         <v>3</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <v>45964</v>
       </c>
       <c r="D7" s="18">
         <f>D5</f>
         <v>27133.333333333332</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <v>45964</v>
       </c>
       <c r="F7" t="s">
@@ -1796,14 +1907,14 @@
       <c r="B8" s="19">
         <v>1</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <v>45873</v>
       </c>
       <c r="D8" s="20">
         <f>Loan!J4/Loan!H4</f>
         <v>32666.666666666668</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <v>45873</v>
       </c>
       <c r="F8" t="s">
@@ -1836,14 +1947,14 @@
       <c r="B9" s="19">
         <v>2</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <v>45904</v>
       </c>
       <c r="D9" s="20">
         <f>D8</f>
         <v>32666.666666666668</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <v>45904</v>
       </c>
       <c r="F9" t="s">
@@ -1876,14 +1987,14 @@
       <c r="B10" s="19">
         <v>3</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>45934</v>
       </c>
       <c r="D10" s="21">
         <f>D8</f>
         <v>32666.666666666668</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <v>45934</v>
       </c>
       <c r="F10" t="s">
@@ -1916,15 +2027,15 @@
       <c r="B11" s="6">
         <v>1</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <v>45937</v>
       </c>
       <c r="D11" s="17">
         <f>Loan!J5/Loan!H5</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E11" s="26">
-        <v>45947</v>
+      <c r="E11" s="27">
+        <v>45937</v>
       </c>
       <c r="F11" t="s">
         <v>253</v>
@@ -1938,7 +2049,7 @@
         <v>42066.666666666664</v>
       </c>
       <c r="I11" s="17">
-        <f>D11</f>
+        <f>SUMIFS(D11:D11,A11:A11,A11)</f>
         <v>42066.666666666664</v>
       </c>
     </row>
@@ -1949,15 +2060,15 @@
       <c r="B12" s="6">
         <v>2</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <v>45968</v>
       </c>
       <c r="D12" s="17">
         <f>D11</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E12" s="26">
-        <v>45975</v>
+      <c r="E12" s="27">
+        <v>45968</v>
       </c>
       <c r="F12" t="s">
         <v>253</v>
@@ -1971,8 +2082,8 @@
         <v>42066.666666666664</v>
       </c>
       <c r="I12" s="17">
-        <f t="shared" ref="I12:I13" si="4">D12</f>
-        <v>42066.666666666664</v>
+        <f>SUMIFS(D11:D12,A11:A12,A12)</f>
+        <v>84133.333333333328</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
@@ -1982,15 +2093,15 @@
       <c r="B13" s="6">
         <v>3</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <v>45998</v>
       </c>
       <c r="D13" s="17">
         <f>D11</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E13" s="26">
-        <v>46010</v>
+      <c r="E13" s="27">
+        <v>45998</v>
       </c>
       <c r="F13" t="s">
         <v>253</v>
@@ -2004,8 +2115,8 @@
         <v>42066.666666666664</v>
       </c>
       <c r="I13" s="17">
-        <f t="shared" si="4"/>
-        <v>42066.666666666664</v>
+        <f>SUMIFS(D11:D13,A11:A13,A13)</f>
+        <v>126200</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
@@ -2015,21 +2126,21 @@
       <c r="B14" s="6">
         <v>1</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <v>45969</v>
       </c>
       <c r="D14" s="17">
         <f>Loan!J6/Loan!H6</f>
         <v>49533.333333333336</v>
       </c>
-      <c r="E14" s="26">
-        <v>45979</v>
+      <c r="E14" s="27">
+        <v>45969</v>
       </c>
       <c r="F14" t="s">
         <v>254</v>
       </c>
       <c r="I14" s="17">
-        <f>D14</f>
+        <f>SUMIFS(D14:D14,A14:A14,A14)</f>
         <v>49533.333333333336</v>
       </c>
     </row>
@@ -2040,22 +2151,22 @@
       <c r="B15" s="6">
         <v>2</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <v>45999</v>
       </c>
       <c r="D15" s="17">
         <f>D14</f>
         <v>49533.333333333336</v>
       </c>
-      <c r="E15" s="26">
-        <v>46006</v>
+      <c r="E15" s="27">
+        <v>45999</v>
       </c>
       <c r="F15" t="s">
         <v>254</v>
       </c>
       <c r="I15" s="17">
-        <f t="shared" ref="I15:I16" si="5">D15</f>
-        <v>49533.333333333336</v>
+        <f>SUMIFS(D15:D16,A15:A16,A15)</f>
+        <v>99066.666666666672</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -2065,22 +2176,22 @@
       <c r="B16" s="6">
         <v>3</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <v>46030</v>
       </c>
       <c r="D16" s="17">
         <f>D15</f>
         <v>49533.333333333336</v>
       </c>
-      <c r="E16" s="26">
-        <v>46042</v>
+      <c r="E16" s="27">
+        <v>46030</v>
       </c>
       <c r="F16" t="s">
         <v>254</v>
       </c>
       <c r="I16" s="17">
-        <f t="shared" si="5"/>
-        <v>49533.333333333336</v>
+        <f>SUMIFS(D14:D16,A14:A16,A16)</f>
+        <v>148600</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
@@ -2090,15 +2201,15 @@
       <c r="B17" s="6">
         <v>1</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <v>45878</v>
       </c>
       <c r="D17" s="17">
         <f>Loan!J7/Loan!H7</f>
         <v>57666.666666666664</v>
       </c>
-      <c r="E17" s="26">
-        <v>45888</v>
+      <c r="E17" s="27">
+        <v>45878</v>
       </c>
       <c r="F17" t="s">
         <v>255</v>
@@ -2115,21 +2226,21 @@
       <c r="B18" s="6">
         <v>2</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <v>45909</v>
       </c>
       <c r="D18" s="17">
         <f>Loan!J7/Loan!H7</f>
         <v>57666.666666666664</v>
       </c>
-      <c r="E18" s="26">
-        <v>45916</v>
+      <c r="E18" s="27">
+        <v>45909</v>
       </c>
       <c r="F18" t="s">
         <v>255</v>
       </c>
       <c r="I18" s="17">
-        <f t="shared" ref="I18:I19" si="6">D18</f>
+        <f t="shared" ref="I18:I19" si="4">D18</f>
         <v>57666.666666666664</v>
       </c>
     </row>
@@ -2140,21 +2251,21 @@
       <c r="B19" s="6">
         <v>3</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="27">
         <v>45939</v>
       </c>
       <c r="D19" s="17">
         <f>Loan!J7/Loan!H7</f>
         <v>57666.666666666664</v>
       </c>
-      <c r="E19" s="26">
-        <v>45951</v>
+      <c r="E19" s="27">
+        <v>45939</v>
       </c>
       <c r="F19" t="s">
         <v>255</v>
       </c>
       <c r="I19" s="17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v>57666.666666666664</v>
       </c>
     </row>
@@ -2165,14 +2276,14 @@
       <c r="B20" s="6">
         <v>1</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="27">
         <v>45879</v>
       </c>
       <c r="D20" s="17">
         <f>Loan!J8/Loan!H8</f>
         <v>64300</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <v>45879</v>
       </c>
       <c r="F20" t="s">
@@ -2190,21 +2301,21 @@
       <c r="B21" s="6">
         <v>2</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <v>45910</v>
       </c>
       <c r="D21" s="17">
         <f>D20</f>
         <v>64300</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <v>45910</v>
       </c>
       <c r="F21" t="s">
         <v>250</v>
       </c>
       <c r="I21" s="17">
-        <f t="shared" ref="I21:I22" si="7">D21</f>
+        <f t="shared" ref="I21:I22" si="5">D21</f>
         <v>64300</v>
       </c>
     </row>
@@ -2215,21 +2326,21 @@
       <c r="B22" s="6">
         <v>3</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <v>45940</v>
       </c>
       <c r="D22" s="17">
         <f>D21</f>
         <v>64300</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <v>45940</v>
       </c>
       <c r="F22" t="s">
         <v>250</v>
       </c>
       <c r="I22" s="17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v>64300</v>
       </c>
     </row>
@@ -2240,14 +2351,14 @@
       <c r="B23" s="6">
         <v>1</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="27">
         <v>45880</v>
       </c>
       <c r="D23" s="17">
         <f>Loan!J9/Loan!H9</f>
         <v>22733.333333333332</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="27">
         <v>45880</v>
       </c>
       <c r="F23" t="s">
@@ -2265,21 +2376,21 @@
       <c r="B24" s="6">
         <v>2</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <v>45911</v>
       </c>
       <c r="D24" s="17">
         <f>D23</f>
         <v>22733.333333333332</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <v>45911</v>
       </c>
       <c r="F24" t="s">
         <v>251</v>
       </c>
       <c r="I24" s="17">
-        <f t="shared" ref="I24:I25" si="8">D24</f>
+        <f t="shared" ref="I24:I25" si="6">D24</f>
         <v>22733.333333333332</v>
       </c>
     </row>
@@ -2290,21 +2401,21 @@
       <c r="B25" s="6">
         <v>3</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <v>45941</v>
       </c>
       <c r="D25" s="17">
         <f>D24</f>
         <v>22733.333333333332</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <v>45941</v>
       </c>
       <c r="F25" t="s">
         <v>251</v>
       </c>
       <c r="I25" s="17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>22733.333333333332</v>
       </c>
     </row>
@@ -2315,14 +2426,14 @@
       <c r="B26" s="6">
         <v>1</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <v>45881</v>
       </c>
       <c r="D26" s="17">
         <f>Loan!J10/Loan!H10</f>
         <v>30533.333333333332</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="27">
         <v>45881</v>
       </c>
       <c r="F26" t="s">
@@ -2340,21 +2451,21 @@
       <c r="B27" s="6">
         <v>2</v>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="27">
         <v>45912</v>
       </c>
       <c r="D27" s="17">
         <f>D26</f>
         <v>30533.333333333332</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="27">
         <v>45912</v>
       </c>
       <c r="F27" t="s">
         <v>252</v>
       </c>
       <c r="I27" s="17">
-        <f t="shared" ref="I27:I28" si="9">D27</f>
+        <f t="shared" ref="I27:I28" si="7">D27</f>
         <v>30533.333333333332</v>
       </c>
     </row>
@@ -2365,21 +2476,21 @@
       <c r="B28" s="6">
         <v>3</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <v>45942</v>
       </c>
       <c r="D28" s="17">
         <f>D27</f>
         <v>30533.333333333332</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="27">
         <v>45942</v>
       </c>
       <c r="F28" t="s">
         <v>252</v>
       </c>
       <c r="I28" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>30533.333333333332</v>
       </c>
     </row>
@@ -2390,15 +2501,15 @@
       <c r="B29" s="6">
         <v>1</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C29" s="27">
         <v>45882</v>
       </c>
       <c r="D29" s="17">
         <f>Loan!J11/Loan!H11</f>
         <v>38333.333333333336</v>
       </c>
-      <c r="E29" s="26">
-        <v>45948</v>
+      <c r="E29" s="27">
+        <v>45882</v>
       </c>
       <c r="F29" t="s">
         <v>253</v>
@@ -2415,21 +2526,21 @@
       <c r="B30" s="6">
         <v>2</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="27">
         <v>45913</v>
       </c>
       <c r="D30" s="17">
         <f>D29</f>
         <v>38333.333333333336</v>
       </c>
-      <c r="E30" s="26">
-        <v>45949</v>
+      <c r="E30" s="27">
+        <v>45913</v>
       </c>
       <c r="F30" t="s">
         <v>253</v>
       </c>
       <c r="I30" s="17">
-        <f t="shared" ref="I30:I31" si="10">D30</f>
+        <f t="shared" ref="I30:I31" si="8">D30</f>
         <v>38333.333333333336</v>
       </c>
     </row>
@@ -2440,21 +2551,21 @@
       <c r="B31" s="6">
         <v>3</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="27">
         <v>45943</v>
       </c>
       <c r="D31" s="17">
         <f>D30</f>
         <v>38333.333333333336</v>
       </c>
-      <c r="E31" s="26">
-        <v>45950</v>
+      <c r="E31" s="27">
+        <v>45943</v>
       </c>
       <c r="F31" t="s">
         <v>253</v>
       </c>
       <c r="I31" s="17">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>38333.333333333336</v>
       </c>
     </row>
@@ -2465,15 +2576,15 @@
       <c r="B32" s="6">
         <v>1</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="27">
         <v>45883</v>
       </c>
       <c r="D32" s="17">
         <f>Loan!J12/Loan!H12</f>
         <v>45800</v>
       </c>
-      <c r="E32" s="26">
-        <v>45865</v>
+      <c r="E32" s="27">
+        <v>45883</v>
       </c>
       <c r="F32" t="s">
         <v>254</v>
@@ -2490,21 +2601,21 @@
       <c r="B33" s="6">
         <v>2</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="27">
         <v>45914</v>
       </c>
       <c r="D33" s="17">
         <f>D32</f>
         <v>45800</v>
       </c>
-      <c r="E33" s="26">
-        <v>45901</v>
+      <c r="E33" s="27">
+        <v>45914</v>
       </c>
       <c r="F33" t="s">
         <v>254</v>
       </c>
       <c r="I33" s="17">
-        <f t="shared" ref="I33:I34" si="11">D33</f>
+        <f t="shared" ref="I33:I34" si="9">D33</f>
         <v>45800</v>
       </c>
     </row>
@@ -2515,21 +2626,21 @@
       <c r="B34" s="6">
         <v>3</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="27">
         <v>45944</v>
       </c>
       <c r="D34" s="17">
         <f>D33</f>
         <v>45800</v>
       </c>
-      <c r="E34" s="26">
-        <v>45936</v>
+      <c r="E34" s="27">
+        <v>45944</v>
       </c>
       <c r="F34" t="s">
         <v>254</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>45800</v>
       </c>
     </row>
@@ -2540,15 +2651,15 @@
       <c r="B35" s="6">
         <v>1</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="27">
         <v>45884</v>
       </c>
       <c r="D35" s="17">
         <f>Loan!J13/Loan!H13</f>
         <v>53266.666666666664</v>
       </c>
-      <c r="E35" s="26">
-        <v>45866</v>
+      <c r="E35" s="27">
+        <v>45884</v>
       </c>
       <c r="F35" t="s">
         <v>255</v>
@@ -2565,15 +2676,15 @@
       <c r="B36" s="6">
         <v>2</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="27">
         <v>45915</v>
       </c>
       <c r="D36" s="17">
         <f>D35</f>
         <v>53266.666666666664</v>
       </c>
-      <c r="E36" s="26">
-        <v>45902</v>
+      <c r="E36" s="27">
+        <v>45915</v>
       </c>
       <c r="F36" t="s">
         <v>255</v>
@@ -2590,15 +2701,15 @@
       <c r="B37" s="6">
         <v>3</v>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="27">
         <v>45945</v>
       </c>
       <c r="D37" s="17">
         <f>D36</f>
         <v>53266.666666666664</v>
       </c>
-      <c r="E37" s="26">
-        <v>45937</v>
+      <c r="E37" s="27">
+        <v>45945</v>
       </c>
       <c r="F37" t="s">
         <v>255</v>
@@ -2615,15 +2726,15 @@
       <c r="B38" s="6">
         <v>1</v>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="27">
         <v>45885</v>
       </c>
       <c r="D38" s="17">
         <f>Loan!J14/Loan!H14</f>
         <v>61400</v>
       </c>
-      <c r="E38" s="26">
-        <v>45867</v>
+      <c r="E38" s="27">
+        <v>45885</v>
       </c>
       <c r="F38" t="s">
         <v>250</v>
@@ -2640,21 +2751,21 @@
       <c r="B39" s="6">
         <v>2</v>
       </c>
-      <c r="C39" s="26">
+      <c r="C39" s="27">
         <v>45916</v>
       </c>
       <c r="D39" s="17">
         <f>D38</f>
         <v>61400</v>
       </c>
-      <c r="E39" s="26">
-        <v>45903</v>
+      <c r="E39" s="27">
+        <v>45916</v>
       </c>
       <c r="F39" t="s">
         <v>250</v>
       </c>
       <c r="I39" s="17">
-        <f t="shared" ref="I39:I40" si="12">D39</f>
+        <f t="shared" ref="I39:I40" si="10">D39</f>
         <v>61400</v>
       </c>
     </row>
@@ -2665,21 +2776,21 @@
       <c r="B40" s="6">
         <v>3</v>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="27">
         <v>45946</v>
       </c>
       <c r="D40" s="17">
         <f>D39</f>
         <v>61400</v>
       </c>
-      <c r="E40" s="26">
-        <v>45938</v>
+      <c r="E40" s="27">
+        <v>45946</v>
       </c>
       <c r="F40" t="s">
         <v>250</v>
       </c>
       <c r="I40" s="17">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>61400</v>
       </c>
     </row>
@@ -2690,15 +2801,15 @@
       <c r="B41" s="6">
         <v>1</v>
       </c>
-      <c r="C41" s="26">
+      <c r="C41" s="27">
         <v>45886</v>
       </c>
       <c r="D41" s="17">
         <f>Loan!J15/Loan!H15</f>
         <v>68866.666666666672</v>
       </c>
-      <c r="E41" s="26">
-        <v>45916</v>
+      <c r="E41" s="27">
+        <v>45886</v>
       </c>
       <c r="F41" t="s">
         <v>251</v>
@@ -2715,21 +2826,21 @@
       <c r="B42" s="6">
         <v>2</v>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="27">
         <v>45917</v>
       </c>
       <c r="D42" s="17">
         <f>D41</f>
         <v>68866.666666666672</v>
       </c>
-      <c r="E42" s="26">
-        <v>45952</v>
+      <c r="E42" s="27">
+        <v>45917</v>
       </c>
       <c r="F42" t="s">
         <v>251</v>
       </c>
       <c r="I42" s="17">
-        <f t="shared" ref="I42:I43" si="13">D42</f>
+        <f t="shared" ref="I42:I43" si="11">D42</f>
         <v>68866.666666666672</v>
       </c>
     </row>
@@ -2740,21 +2851,21 @@
       <c r="B43" s="6">
         <v>3</v>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="27">
         <v>45947</v>
       </c>
       <c r="D43" s="17">
         <f>D42</f>
         <v>68866.666666666672</v>
       </c>
-      <c r="E43" s="26">
-        <v>45917</v>
+      <c r="E43" s="27">
+        <v>45947</v>
       </c>
       <c r="F43" t="s">
         <v>251</v>
       </c>
       <c r="I43" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v>68866.666666666672</v>
       </c>
     </row>
@@ -2765,15 +2876,15 @@
       <c r="B44" s="6">
         <v>1</v>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="27">
         <v>45887</v>
       </c>
       <c r="D44" s="17">
         <f>Loan!J16/Loan!H16</f>
         <v>76333.333333333328</v>
       </c>
-      <c r="E44" s="26">
-        <v>45953</v>
+      <c r="E44" s="27">
+        <v>45887</v>
       </c>
       <c r="F44" t="s">
         <v>252</v>
@@ -2790,21 +2901,21 @@
       <c r="B45" s="6">
         <v>2</v>
       </c>
-      <c r="C45" s="26">
+      <c r="C45" s="27">
         <v>45918</v>
       </c>
       <c r="D45" s="17">
         <f>D44</f>
         <v>76333.333333333328</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="27">
         <v>45918</v>
       </c>
       <c r="F45" t="s">
         <v>252</v>
       </c>
       <c r="I45" s="17">
-        <f t="shared" ref="I45:I46" si="14">D45</f>
+        <f t="shared" ref="I45:I46" si="12">D45</f>
         <v>76333.333333333328</v>
       </c>
     </row>
@@ -2815,21 +2926,21 @@
       <c r="B46" s="6">
         <v>3</v>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="27">
         <v>45948</v>
       </c>
       <c r="D46" s="17">
         <f>D45</f>
         <v>76333.333333333328</v>
       </c>
-      <c r="E46" s="26">
-        <v>45954</v>
+      <c r="E46" s="27">
+        <v>45948</v>
       </c>
       <c r="F46" t="s">
         <v>252</v>
       </c>
       <c r="I46" s="17">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>76333.333333333328</v>
       </c>
     </row>
@@ -2840,15 +2951,15 @@
       <c r="B47" s="6">
         <v>1</v>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="27">
         <v>45888</v>
       </c>
       <c r="D47" s="17">
         <f>Loan!J17/Loan!H17</f>
         <v>26800</v>
       </c>
-      <c r="E47" s="26">
-        <v>45919</v>
+      <c r="E47" s="27">
+        <v>45888</v>
       </c>
       <c r="F47" t="s">
         <v>253</v>
@@ -2865,21 +2976,21 @@
       <c r="B48" s="6">
         <v>2</v>
       </c>
-      <c r="C48" s="26">
+      <c r="C48" s="27">
         <v>45919</v>
       </c>
       <c r="D48" s="17">
         <f>D47</f>
         <v>26800</v>
       </c>
-      <c r="E48" s="26">
-        <v>45955</v>
+      <c r="E48" s="27">
+        <v>45919</v>
       </c>
       <c r="F48" t="s">
         <v>253</v>
       </c>
       <c r="I48" s="17">
-        <f t="shared" ref="I48:I49" si="15">D48</f>
+        <f t="shared" ref="I48:I49" si="13">D48</f>
         <v>26800</v>
       </c>
     </row>
@@ -2890,21 +3001,21 @@
       <c r="B49" s="6">
         <v>3</v>
       </c>
-      <c r="C49" s="26">
+      <c r="C49" s="27">
         <v>45949</v>
       </c>
       <c r="D49" s="17">
         <f>D48</f>
         <v>26800</v>
       </c>
-      <c r="E49" s="26">
-        <v>45920</v>
+      <c r="E49" s="27">
+        <v>45949</v>
       </c>
       <c r="F49" t="s">
         <v>253</v>
       </c>
       <c r="I49" s="17">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>26800</v>
       </c>
     </row>
@@ -2915,15 +3026,15 @@
       <c r="B50" s="6">
         <v>1</v>
       </c>
-      <c r="C50" s="26">
+      <c r="C50" s="27">
         <v>45889</v>
       </c>
       <c r="D50" s="17">
         <f>Loan!J18/Loan!H18</f>
         <v>34266.666666666664</v>
       </c>
-      <c r="E50" s="26">
-        <v>45956</v>
+      <c r="E50" s="27">
+        <v>45889</v>
       </c>
       <c r="F50" t="s">
         <v>254</v>
@@ -2940,21 +3051,21 @@
       <c r="B51" s="6">
         <v>2</v>
       </c>
-      <c r="C51" s="26">
+      <c r="C51" s="27">
         <v>45920</v>
       </c>
       <c r="D51" s="17">
         <f>D50</f>
         <v>34266.666666666664</v>
       </c>
-      <c r="E51" s="26">
-        <v>45952</v>
+      <c r="E51" s="27">
+        <v>45920</v>
       </c>
       <c r="F51" t="s">
         <v>254</v>
       </c>
       <c r="I51" s="17">
-        <f t="shared" ref="I51:I52" si="16">D51</f>
+        <f t="shared" ref="I51:I52" si="14">D51</f>
         <v>34266.666666666664</v>
       </c>
     </row>
@@ -2965,21 +3076,21 @@
       <c r="B52" s="6">
         <v>3</v>
       </c>
-      <c r="C52" s="26">
+      <c r="C52" s="27">
         <v>45950</v>
       </c>
       <c r="D52" s="17">
         <f>D51</f>
         <v>34266.666666666664</v>
       </c>
-      <c r="E52" s="26">
-        <v>45963</v>
+      <c r="E52" s="27">
+        <v>45950</v>
       </c>
       <c r="F52" t="s">
         <v>254</v>
       </c>
       <c r="I52" s="17">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>34266.666666666664</v>
       </c>
     </row>
@@ -2990,15 +3101,15 @@
       <c r="B53" s="6">
         <v>1</v>
       </c>
-      <c r="C53" s="26">
+      <c r="C53" s="27">
         <v>45890</v>
       </c>
       <c r="D53" s="17">
         <f>Loan!J19/Loan!H19</f>
         <v>42066.666666666664</v>
       </c>
-      <c r="E53" s="26">
-        <v>45973</v>
+      <c r="E53" s="27">
+        <v>45890</v>
       </c>
       <c r="F53" t="s">
         <v>255</v>
@@ -3015,18 +3126,21 @@
       <c r="B54" s="6">
         <v>2</v>
       </c>
-      <c r="C54" s="26">
+      <c r="C54" s="27">
         <v>45921</v>
       </c>
       <c r="D54" s="17">
         <f>D53</f>
         <v>42066.666666666664</v>
       </c>
+      <c r="E54" s="27">
+        <v>45921</v>
+      </c>
       <c r="F54" t="s">
         <v>255</v>
       </c>
       <c r="I54" s="17">
-        <f t="shared" ref="I54:I55" si="17">D54</f>
+        <f t="shared" ref="I54:I55" si="15">D54</f>
         <v>42066.666666666664</v>
       </c>
     </row>
@@ -3037,18 +3151,21 @@
       <c r="B55" s="6">
         <v>3</v>
       </c>
-      <c r="C55" s="26">
+      <c r="C55" s="27">
         <v>45951</v>
       </c>
       <c r="D55" s="17">
         <f>D54</f>
         <v>42066.666666666664</v>
       </c>
+      <c r="E55" s="27">
+        <v>45951</v>
+      </c>
       <c r="F55" t="s">
         <v>255</v>
       </c>
       <c r="I55" s="17">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>42066.666666666664</v>
       </c>
     </row>
@@ -3059,13 +3176,16 @@
       <c r="B56" s="6">
         <v>1</v>
       </c>
-      <c r="C56" s="26">
+      <c r="C56" s="27">
         <v>45891</v>
       </c>
       <c r="D56" s="17">
         <f>Loan!J20/Loan!H20</f>
         <v>19000</v>
       </c>
+      <c r="E56" s="27">
+        <v>45891</v>
+      </c>
       <c r="F56" t="s">
         <v>250</v>
       </c>
@@ -3081,18 +3201,21 @@
       <c r="B57" s="6">
         <v>2</v>
       </c>
-      <c r="C57" s="26">
+      <c r="C57" s="27">
         <v>45922</v>
       </c>
       <c r="D57" s="17">
         <f>D56</f>
         <v>19000</v>
       </c>
+      <c r="E57" s="27">
+        <v>45922</v>
+      </c>
       <c r="F57" t="s">
         <v>250</v>
       </c>
       <c r="I57" s="17">
-        <f t="shared" ref="I57:I58" si="18">D57</f>
+        <f t="shared" ref="I57:I58" si="16">D57</f>
         <v>19000</v>
       </c>
     </row>
@@ -3103,18 +3226,21 @@
       <c r="B58" s="6">
         <v>3</v>
       </c>
-      <c r="C58" s="26">
+      <c r="C58" s="27">
         <v>45952</v>
       </c>
       <c r="D58" s="17">
         <f>D56</f>
         <v>19000</v>
       </c>
+      <c r="E58" s="27">
+        <v>45952</v>
+      </c>
       <c r="F58" t="s">
         <v>250</v>
       </c>
       <c r="I58" s="17">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>19000</v>
       </c>
     </row>
@@ -3125,13 +3251,16 @@
       <c r="B59" s="6">
         <v>1</v>
       </c>
-      <c r="C59" s="26">
+      <c r="C59" s="27">
         <v>45892</v>
       </c>
       <c r="D59" s="17">
         <f>Loan!J21/Loan!H21</f>
         <v>28333.333333333332</v>
       </c>
+      <c r="E59" s="27">
+        <v>45892</v>
+      </c>
       <c r="F59" t="s">
         <v>251</v>
       </c>
@@ -3147,18 +3276,21 @@
       <c r="B60" s="6">
         <v>2</v>
       </c>
-      <c r="C60" s="26">
+      <c r="C60" s="27">
         <v>45923</v>
       </c>
       <c r="D60" s="17">
         <f>D59</f>
         <v>28333.333333333332</v>
       </c>
+      <c r="E60" s="27">
+        <v>45923</v>
+      </c>
       <c r="F60" t="s">
         <v>251</v>
       </c>
       <c r="I60" s="17">
-        <f t="shared" ref="I60:I61" si="19">D60</f>
+        <f t="shared" ref="I60:I61" si="17">D60</f>
         <v>28333.333333333332</v>
       </c>
     </row>
@@ -3169,18 +3301,21 @@
       <c r="B61" s="6">
         <v>3</v>
       </c>
-      <c r="C61" s="26">
+      <c r="C61" s="27">
         <v>45953</v>
       </c>
       <c r="D61" s="17">
         <f>D59</f>
         <v>28333.333333333332</v>
       </c>
+      <c r="E61" s="27">
+        <v>45953</v>
+      </c>
       <c r="F61" t="s">
         <v>251</v>
       </c>
       <c r="I61" s="17">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v>28333.333333333332</v>
       </c>
     </row>
@@ -3190,6 +3325,153 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="84.54296875" style="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="42" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5610,7 +5892,7 @@
     <col min="2" max="2" width="12.6328125" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7265625" style="36" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" style="37" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.1796875" style="17" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.26953125" style="5" bestFit="1" customWidth="1"/>
@@ -5626,34 +5908,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="40" t="s">
+      <c r="J1" s="41" t="s">
         <v>214</v>
       </c>
       <c r="Q1" s="10"/>
@@ -6347,7 +6629,7 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="36"/>
+      <c r="A23" s="37"/>
       <c r="B23"/>
       <c r="C23" s="17"/>
       <c r="E23" s="5"/>
@@ -6363,9 +6645,9 @@
       <c r="O23"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="36"/>
+      <c r="A24" s="37"/>
       <c r="B24" s="1"/>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="38" t="s">
         <v>220</v>
       </c>
       <c r="D24" s="11" t="s">
@@ -6374,7 +6656,7 @@
       <c r="E24" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="38" t="s">
         <v>216</v>
       </c>
       <c r="G24" s="5"/>
@@ -6385,7 +6667,7 @@
       <c r="O24"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="36"/>
+      <c r="A25" s="37"/>
       <c r="B25"/>
       <c r="C25" s="17"/>
       <c r="D25" s="12" t="e">
@@ -6405,7 +6687,7 @@
       <c r="O25"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26" s="36"/>
+      <c r="A26" s="37"/>
       <c r="B26"/>
       <c r="C26" s="17"/>
       <c r="E26" s="5"/>
@@ -6418,7 +6700,7 @@
       <c r="O26"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="36"/>
+      <c r="A27" s="37"/>
       <c r="B27"/>
       <c r="C27" s="17"/>
       <c r="E27" s="5"/>
@@ -6431,7 +6713,7 @@
       <c r="O27"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28" s="36"/>
+      <c r="A28" s="37"/>
       <c r="B28"/>
       <c r="C28" s="17"/>
       <c r="D28" s="5" t="e">
@@ -6451,7 +6733,7 @@
       <c r="O28"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29" s="36"/>
+      <c r="A29" s="37"/>
       <c r="B29"/>
       <c r="C29" s="17"/>
       <c r="E29" s="5"/>
@@ -6464,7 +6746,7 @@
       <c r="O29"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="36"/>
+      <c r="A30" s="37"/>
       <c r="B30"/>
       <c r="C30" s="17"/>
       <c r="E30" s="5"/>
@@ -6477,7 +6759,7 @@
       <c r="O30"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="36"/>
+      <c r="A31" s="37"/>
       <c r="B31"/>
       <c r="C31" s="17"/>
       <c r="E31" s="5"/>
@@ -6490,7 +6772,7 @@
       <c r="O31"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A32" s="36"/>
+      <c r="A32" s="37"/>
       <c r="B32"/>
       <c r="C32" s="17"/>
       <c r="E32" s="5"/>
@@ -6503,7 +6785,7 @@
       <c r="O32"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="36"/>
+      <c r="A33" s="37"/>
       <c r="B33"/>
       <c r="C33" s="17"/>
       <c r="D33" s="5" t="e">
@@ -6526,7 +6808,7 @@
       <c r="O33"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="36"/>
+      <c r="A34" s="37"/>
       <c r="B34"/>
       <c r="C34" s="17"/>
       <c r="E34" s="5"/>
@@ -6539,7 +6821,7 @@
       <c r="O34"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A35" s="36"/>
+      <c r="A35" s="37"/>
       <c r="B35"/>
       <c r="C35" s="17"/>
       <c r="E35" s="5"/>
@@ -6552,7 +6834,7 @@
       <c r="O35"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A36" s="36"/>
+      <c r="A36" s="37"/>
       <c r="B36"/>
       <c r="C36" s="17"/>
       <c r="E36" s="5"/>
@@ -6565,7 +6847,7 @@
       <c r="O36"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="36"/>
+      <c r="A37" s="37"/>
       <c r="B37"/>
       <c r="C37" s="17"/>
       <c r="E37" s="5"/>
@@ -6578,7 +6860,7 @@
       <c r="O37"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="36"/>
+      <c r="A38" s="37"/>
       <c r="B38"/>
       <c r="C38" s="17"/>
       <c r="E38" s="5"/>
@@ -6591,7 +6873,7 @@
       <c r="O38"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="36"/>
+      <c r="A39" s="37"/>
       <c r="B39"/>
       <c r="C39" s="17"/>
       <c r="E39" s="5"/>
@@ -6604,7 +6886,7 @@
       <c r="O39"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="36"/>
+      <c r="A40" s="37"/>
       <c r="B40"/>
       <c r="C40" s="17"/>
       <c r="E40" s="5"/>
@@ -6617,7 +6899,7 @@
       <c r="O40"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A41" s="36"/>
+      <c r="A41" s="37"/>
       <c r="B41"/>
       <c r="C41" s="17"/>
       <c r="E41" s="5"/>
@@ -6630,7 +6912,7 @@
       <c r="O41"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A42" s="36"/>
+      <c r="A42" s="37"/>
       <c r="B42"/>
       <c r="C42" s="17"/>
       <c r="E42" s="5"/>
@@ -6643,7 +6925,7 @@
       <c r="O42"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A43" s="36"/>
+      <c r="A43" s="37"/>
       <c r="B43"/>
       <c r="C43" s="17"/>
       <c r="E43" s="5"/>
@@ -6656,7 +6938,7 @@
       <c r="O43"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A44" s="36"/>
+      <c r="A44" s="37"/>
       <c r="B44"/>
       <c r="C44" s="17"/>
       <c r="E44" s="5"/>
@@ -6669,7 +6951,7 @@
       <c r="O44"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A45" s="36"/>
+      <c r="A45" s="37"/>
       <c r="B45"/>
       <c r="C45" s="17"/>
       <c r="E45" s="5"/>
@@ -6682,7 +6964,7 @@
       <c r="O45"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="36"/>
+      <c r="A46" s="37"/>
       <c r="B46"/>
       <c r="C46" s="17"/>
       <c r="E46" s="5"/>
@@ -6695,7 +6977,7 @@
       <c r="O46"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A47" s="36"/>
+      <c r="A47" s="37"/>
       <c r="B47"/>
       <c r="C47" s="17"/>
       <c r="E47" s="5"/>
@@ -6708,7 +6990,7 @@
       <c r="O47"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A48" s="36"/>
+      <c r="A48" s="37"/>
       <c r="B48"/>
       <c r="C48" s="17"/>
       <c r="E48" s="5"/>
@@ -6721,7 +7003,7 @@
       <c r="O48"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A49" s="36"/>
+      <c r="A49" s="37"/>
       <c r="B49"/>
       <c r="C49" s="17"/>
       <c r="E49" s="5"/>
@@ -6734,7 +7016,7 @@
       <c r="O49"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A50" s="36"/>
+      <c r="A50" s="37"/>
       <c r="B50"/>
       <c r="C50" s="17"/>
       <c r="E50" s="5"/>

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="289">
   <si>
     <t>signup_date</t>
   </si>
@@ -840,9 +840,6 @@
     <t>Instalment due</t>
   </si>
   <si>
-    <t>Principal/term + Principal × monthly rate</t>
-  </si>
-  <si>
     <t>Flat-rate scheduled instalment; processing fee is tracked separately.</t>
   </si>
   <si>
@@ -903,13 +900,7 @@
     <t>Standardises delinquency segmentation.</t>
   </si>
   <si>
-    <t>Fee treatment</t>
-  </si>
-  <si>
-    <t>Processing fee is charged once at origination and excluded from instalment allocation</t>
-  </si>
-  <si>
-    <t>Keeps repayment allocation focused on scheduled instalments while retaining total borrowing cost.</t>
+    <t xml:space="preserve">Principal+ interest+ processing fee/term </t>
   </si>
 </sst>
 </file>
@@ -2215,7 +2206,7 @@
         <v>255</v>
       </c>
       <c r="I17" s="17">
-        <f>D17</f>
+        <f t="shared" ref="I17:I62" si="4">SUMIFS(D15:D17,A15:A17,A17)</f>
         <v>57666.666666666664</v>
       </c>
     </row>
@@ -2240,8 +2231,8 @@
         <v>255</v>
       </c>
       <c r="I18" s="17">
-        <f t="shared" ref="I18:I19" si="4">D18</f>
-        <v>57666.666666666664</v>
+        <f t="shared" si="4"/>
+        <v>115333.33333333333</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -2266,7 +2257,7 @@
       </c>
       <c r="I19" s="17">
         <f t="shared" si="4"/>
-        <v>57666.666666666664</v>
+        <v>173000</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -2290,7 +2281,7 @@
         <v>250</v>
       </c>
       <c r="I20" s="17">
-        <f>D20</f>
+        <f t="shared" si="4"/>
         <v>64300</v>
       </c>
     </row>
@@ -2315,8 +2306,8 @@
         <v>250</v>
       </c>
       <c r="I21" s="17">
-        <f t="shared" ref="I21:I22" si="5">D21</f>
-        <v>64300</v>
+        <f t="shared" si="4"/>
+        <v>128600</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -2340,8 +2331,8 @@
         <v>250</v>
       </c>
       <c r="I22" s="17">
-        <f t="shared" si="5"/>
-        <v>64300</v>
+        <f t="shared" si="4"/>
+        <v>192900</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
@@ -2365,7 +2356,7 @@
         <v>251</v>
       </c>
       <c r="I23" s="17">
-        <f>D23</f>
+        <f t="shared" si="4"/>
         <v>22733.333333333332</v>
       </c>
     </row>
@@ -2390,8 +2381,8 @@
         <v>251</v>
       </c>
       <c r="I24" s="17">
-        <f t="shared" ref="I24:I25" si="6">D24</f>
-        <v>22733.333333333332</v>
+        <f t="shared" si="4"/>
+        <v>45466.666666666664</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
@@ -2415,8 +2406,8 @@
         <v>251</v>
       </c>
       <c r="I25" s="17">
-        <f t="shared" si="6"/>
-        <v>22733.333333333332</v>
+        <f t="shared" si="4"/>
+        <v>68200</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
@@ -2440,7 +2431,7 @@
         <v>252</v>
       </c>
       <c r="I26" s="17">
-        <f>D26</f>
+        <f t="shared" si="4"/>
         <v>30533.333333333332</v>
       </c>
     </row>
@@ -2465,8 +2456,8 @@
         <v>252</v>
       </c>
       <c r="I27" s="17">
-        <f t="shared" ref="I27:I28" si="7">D27</f>
-        <v>30533.333333333332</v>
+        <f t="shared" si="4"/>
+        <v>61066.666666666664</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
@@ -2490,8 +2481,8 @@
         <v>252</v>
       </c>
       <c r="I28" s="17">
-        <f t="shared" si="7"/>
-        <v>30533.333333333332</v>
+        <f t="shared" si="4"/>
+        <v>91600</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
@@ -2515,7 +2506,7 @@
         <v>253</v>
       </c>
       <c r="I29" s="17">
-        <f>D29</f>
+        <f t="shared" si="4"/>
         <v>38333.333333333336</v>
       </c>
     </row>
@@ -2540,8 +2531,8 @@
         <v>253</v>
       </c>
       <c r="I30" s="17">
-        <f t="shared" ref="I30:I31" si="8">D30</f>
-        <v>38333.333333333336</v>
+        <f t="shared" si="4"/>
+        <v>76666.666666666672</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
@@ -2565,8 +2556,8 @@
         <v>253</v>
       </c>
       <c r="I31" s="17">
-        <f t="shared" si="8"/>
-        <v>38333.333333333336</v>
+        <f t="shared" si="4"/>
+        <v>115000</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
@@ -2590,7 +2581,7 @@
         <v>254</v>
       </c>
       <c r="I32" s="17">
-        <f>D32</f>
+        <f t="shared" si="4"/>
         <v>45800</v>
       </c>
     </row>
@@ -2615,8 +2606,8 @@
         <v>254</v>
       </c>
       <c r="I33" s="17">
-        <f t="shared" ref="I33:I34" si="9">D33</f>
-        <v>45800</v>
+        <f t="shared" si="4"/>
+        <v>91600</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -2640,7 +2631,7 @@
         <v>254</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" si="9"/>
+        <f t="shared" si="4"/>
         <v>45800</v>
       </c>
     </row>
@@ -2665,7 +2656,7 @@
         <v>255</v>
       </c>
       <c r="I35" s="17">
-        <f>D36</f>
+        <f t="shared" si="4"/>
         <v>53266.666666666664</v>
       </c>
     </row>
@@ -2690,8 +2681,8 @@
         <v>255</v>
       </c>
       <c r="I36" s="17">
-        <f>D37</f>
-        <v>53266.666666666664</v>
+        <f t="shared" si="4"/>
+        <v>106533.33333333333</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
@@ -2715,8 +2706,8 @@
         <v>255</v>
       </c>
       <c r="I37" s="17">
-        <f>D37</f>
-        <v>53266.666666666664</v>
+        <f t="shared" si="4"/>
+        <v>159800</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -2740,7 +2731,7 @@
         <v>250</v>
       </c>
       <c r="I38" s="17">
-        <f>D38</f>
+        <f t="shared" si="4"/>
         <v>61400</v>
       </c>
     </row>
@@ -2765,8 +2756,8 @@
         <v>250</v>
       </c>
       <c r="I39" s="17">
-        <f t="shared" ref="I39:I40" si="10">D39</f>
-        <v>61400</v>
+        <f t="shared" si="4"/>
+        <v>122800</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
@@ -2790,8 +2781,8 @@
         <v>250</v>
       </c>
       <c r="I40" s="17">
-        <f t="shared" si="10"/>
-        <v>61400</v>
+        <f t="shared" si="4"/>
+        <v>184200</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -2815,7 +2806,7 @@
         <v>251</v>
       </c>
       <c r="I41" s="17">
-        <f>D41</f>
+        <f t="shared" si="4"/>
         <v>68866.666666666672</v>
       </c>
     </row>
@@ -2840,8 +2831,8 @@
         <v>251</v>
       </c>
       <c r="I42" s="17">
-        <f t="shared" ref="I42:I43" si="11">D42</f>
-        <v>68866.666666666672</v>
+        <f t="shared" si="4"/>
+        <v>137733.33333333334</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
@@ -2865,8 +2856,8 @@
         <v>251</v>
       </c>
       <c r="I43" s="17">
-        <f t="shared" si="11"/>
-        <v>68866.666666666672</v>
+        <f t="shared" si="4"/>
+        <v>206600</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
@@ -2890,7 +2881,7 @@
         <v>252</v>
       </c>
       <c r="I44" s="17">
-        <f>D44</f>
+        <f t="shared" si="4"/>
         <v>76333.333333333328</v>
       </c>
     </row>
@@ -2915,8 +2906,8 @@
         <v>252</v>
       </c>
       <c r="I45" s="17">
-        <f t="shared" ref="I45:I46" si="12">D45</f>
-        <v>76333.333333333328</v>
+        <f t="shared" si="4"/>
+        <v>152666.66666666666</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2940,8 +2931,8 @@
         <v>252</v>
       </c>
       <c r="I46" s="17">
-        <f t="shared" si="12"/>
-        <v>76333.333333333328</v>
+        <f t="shared" si="4"/>
+        <v>229000</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2965,7 +2956,7 @@
         <v>253</v>
       </c>
       <c r="I47" s="17">
-        <f>D47</f>
+        <f t="shared" si="4"/>
         <v>26800</v>
       </c>
     </row>
@@ -2990,8 +2981,8 @@
         <v>253</v>
       </c>
       <c r="I48" s="17">
-        <f t="shared" ref="I48:I49" si="13">D48</f>
-        <v>26800</v>
+        <f t="shared" si="4"/>
+        <v>53600</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
@@ -3015,7 +3006,7 @@
         <v>253</v>
       </c>
       <c r="I49" s="17">
-        <f t="shared" si="13"/>
+        <f t="shared" si="4"/>
         <v>26800</v>
       </c>
     </row>
@@ -3040,7 +3031,7 @@
         <v>254</v>
       </c>
       <c r="I50" s="17">
-        <f>D50</f>
+        <f t="shared" si="4"/>
         <v>34266.666666666664</v>
       </c>
     </row>
@@ -3065,8 +3056,8 @@
         <v>254</v>
       </c>
       <c r="I51" s="17">
-        <f t="shared" ref="I51:I52" si="14">D51</f>
-        <v>34266.666666666664</v>
+        <f t="shared" si="4"/>
+        <v>68533.333333333328</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
@@ -3090,8 +3081,8 @@
         <v>254</v>
       </c>
       <c r="I52" s="17">
-        <f t="shared" si="14"/>
-        <v>34266.666666666664</v>
+        <f t="shared" si="4"/>
+        <v>102800</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
@@ -3115,7 +3106,7 @@
         <v>255</v>
       </c>
       <c r="I53" s="17">
-        <f>D53</f>
+        <f t="shared" si="4"/>
         <v>42066.666666666664</v>
       </c>
     </row>
@@ -3140,8 +3131,8 @@
         <v>255</v>
       </c>
       <c r="I54" s="17">
-        <f t="shared" ref="I54:I55" si="15">D54</f>
-        <v>42066.666666666664</v>
+        <f t="shared" si="4"/>
+        <v>84133.333333333328</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -3165,8 +3156,8 @@
         <v>255</v>
       </c>
       <c r="I55" s="17">
-        <f t="shared" si="15"/>
-        <v>42066.666666666664</v>
+        <f t="shared" si="4"/>
+        <v>126200</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
@@ -3190,7 +3181,7 @@
         <v>250</v>
       </c>
       <c r="I56" s="17">
-        <f>D56</f>
+        <f t="shared" si="4"/>
         <v>19000</v>
       </c>
     </row>
@@ -3215,8 +3206,8 @@
         <v>250</v>
       </c>
       <c r="I57" s="17">
-        <f t="shared" ref="I57:I58" si="16">D57</f>
-        <v>19000</v>
+        <f t="shared" si="4"/>
+        <v>38000</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
@@ -3240,8 +3231,8 @@
         <v>250</v>
       </c>
       <c r="I58" s="17">
-        <f t="shared" si="16"/>
-        <v>19000</v>
+        <f t="shared" si="4"/>
+        <v>57000</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -3265,7 +3256,7 @@
         <v>251</v>
       </c>
       <c r="I59" s="17">
-        <f>D59</f>
+        <f t="shared" si="4"/>
         <v>28333.333333333332</v>
       </c>
     </row>
@@ -3290,8 +3281,8 @@
         <v>251</v>
       </c>
       <c r="I60" s="17">
-        <f t="shared" ref="I60:I61" si="17">D60</f>
-        <v>28333.333333333332</v>
+        <f t="shared" si="4"/>
+        <v>56666.666666666664</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
@@ -3315,12 +3306,16 @@
         <v>251</v>
       </c>
       <c r="I61" s="17">
-        <f t="shared" si="17"/>
-        <v>28333.333333333332</v>
+        <f t="shared" si="4"/>
+        <v>85000</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="6"/>
+      <c r="I62" s="17">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3376,65 +3371,65 @@
         <v>267</v>
       </c>
       <c r="B4" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="44" t="s">
         <v>268</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" s="44" t="s">
         <v>270</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="C5" s="44" t="s">
         <v>271</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>273</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="C6" s="44" t="s">
         <v>274</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>276</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="C7" s="44" t="s">
         <v>277</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>279</v>
       </c>
-      <c r="B8" s="44" t="s">
+      <c r="C8" s="44" t="s">
         <v>280</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="B9" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="C9" s="44" t="s">
         <v>283</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -3442,10 +3437,10 @@
         <v>217</v>
       </c>
       <c r="B10" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="C10" s="44" t="s">
         <v>285</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -3453,22 +3448,15 @@
         <v>218</v>
       </c>
       <c r="B11" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="C11" s="44" t="s">
         <v>287</v>
       </c>
-      <c r="C11" s="44" t="s">
-        <v>288</v>
-      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="42" t="s">
-        <v>289</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>290</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>291</v>
-      </c>
+      <c r="B12"/>
+      <c r="C12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="3" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="3" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Datagrain" sheetId="3" r:id="rId1"/>

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="3" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="3" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Datagrain" sheetId="3" r:id="rId1"/>
@@ -997,12 +997,21 @@
   </cellStyles>
   <dxfs count="13">
     <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1024,21 +1033,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
@@ -1126,19 +1126,19 @@
     <tableColumn id="4" name="amount_due" dataDxfId="9" dataCellStyle="Comma"/>
     <tableColumn id="5" name="payment_date" dataDxfId="8"/>
     <tableColumn id="6" name="Scenario"/>
-    <tableColumn id="7" name="Payment_amount" dataDxfId="6" dataCellStyle="Comma"/>
-    <tableColumn id="8" name="outstanding" dataDxfId="5" dataCellStyle="Comma"/>
-    <tableColumn id="9" name="cumulative_due" dataDxfId="2" dataCellStyle="Comma"/>
-    <tableColumn id="10" name="cumulative_paid" dataDxfId="0" dataCellStyle="Comma"/>
-    <tableColumn id="11" name="cumulative_arrears_amount" dataDxfId="1" dataCellStyle="Comma"/>
-    <tableColumn id="12" name="Oldest Unpaid Due Date" dataDxfId="4"/>
-    <tableColumn id="13" name="DPD" dataDxfId="7">
+    <tableColumn id="7" name="Payment_amount" dataDxfId="7" dataCellStyle="Comma"/>
+    <tableColumn id="8" name="outstanding" dataDxfId="6" dataCellStyle="Comma"/>
+    <tableColumn id="9" name="cumulative_due" dataDxfId="5" dataCellStyle="Comma"/>
+    <tableColumn id="10" name="cumulative_paid" dataDxfId="4" dataCellStyle="Comma"/>
+    <tableColumn id="11" name="cumulative_arrears_amount" dataDxfId="3" dataCellStyle="Comma"/>
+    <tableColumn id="12" name="Oldest Unpaid Due Date" dataDxfId="2"/>
+    <tableColumn id="13" name="DPD" dataDxfId="1">
       <calculatedColumnFormula>MAX(0,L43-Table1[[#This Row],[due_date]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" name="Bucket">
       <calculatedColumnFormula>IF(M2="","Current",IF(M2&lt;=0,"Current",IF(M2&lt;=7,"1–7",IF(M2&lt;=30,"8–30",IF(M2&lt;=60,"31–60",IF(M2&lt;=90,"61–90","90+"))))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="reporting_date " dataDxfId="3">
+    <tableColumn id="15" name="reporting_date " dataDxfId="0">
       <calculatedColumnFormula>L62</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5353,7 +5353,7 @@
         <v>14000</v>
       </c>
       <c r="H10" s="13">
-        <f t="shared" ref="H9:H10" si="4">D10-G10</f>
+        <f t="shared" ref="H10" si="4">D10-G10</f>
         <v>18666.666666666668</v>
       </c>
       <c r="I10" s="13">
@@ -6054,7 +6054,7 @@
         <v>90+</v>
       </c>
       <c r="O23" s="18">
-        <v>45990</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="3" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Datagrain" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="262">
   <si>
     <t>signup_date</t>
   </si>
@@ -815,6 +815,9 @@
   </si>
   <si>
     <t xml:space="preserve">reporting_date </t>
+  </si>
+  <si>
+    <t>Rejected</t>
   </si>
 </sst>
 </file>
@@ -907,7 +910,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -989,6 +992,9 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2325,7 +2331,7 @@
     <col min="6" max="6" width="15" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2353,7 +2359,7 @@
       <c r="H1" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="41" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2643,8 +2649,8 @@
       <c r="H11" s="4">
         <v>9</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>152</v>
+      <c r="I11" s="8">
+        <v>45817</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -2933,7 +2939,7 @@
       <c r="H21" s="4">
         <v>9</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="8" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3269,7 +3275,7 @@
         <v>52000</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>97</v>
+        <v>261</v>
       </c>
       <c r="K9" s="4">
         <v>1</v>
@@ -3409,7 +3415,7 @@
         <v>61000</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>97</v>
+        <v>261</v>
       </c>
       <c r="K13" s="4">
         <v>1</v>

--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -9,17 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="4" r:id="rId1"/>
-    <sheet name="Metric" sheetId="14" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="15" r:id="rId3"/>
-    <sheet name="Application" sheetId="5" r:id="rId4"/>
-    <sheet name="Loan" sheetId="2" r:id="rId5"/>
-    <sheet name="Installment" sheetId="12" r:id="rId6"/>
-    <sheet name="Formula Allocation" sheetId="13" r:id="rId7"/>
+    <sheet name="Application" sheetId="5" r:id="rId2"/>
+    <sheet name="Loan" sheetId="2" r:id="rId3"/>
+    <sheet name="Installment" sheetId="12" r:id="rId4"/>
+    <sheet name="Formula Allocation" sheetId="13" r:id="rId5"/>
+    <sheet name="Metric" sheetId="14" r:id="rId6"/>
+    <sheet name="Reconcilation" sheetId="15" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="16" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="282">
   <si>
     <t>signup_date</t>
   </si>
@@ -762,17 +766,134 @@
   </si>
   <si>
     <t>Total principal disbursed</t>
+  </si>
+  <si>
+    <t>Total contract value — flat formula (₦)</t>
+  </si>
+  <si>
+    <t>Sum of all instalment amount_due (₦)</t>
+  </si>
+  <si>
+    <t>Loan Repayment Dashboard</t>
+  </si>
+  <si>
+    <t>Nigerian microfinance loan book — disbursements, collections &amp; delinquency</t>
+  </si>
+  <si>
+    <t>Controls</t>
+  </si>
+  <si>
+    <t>Channel filter: source data does not currently capture acquisition_channel at customer level (see Reconciliation tab) — filter is provided for future use and defaults to 'All'.</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Portfolio Snapshot</t>
+  </si>
+  <si>
+    <t>Delinquency by DPD Bucket</t>
+  </si>
+  <si>
+    <t>Loan Count (units)</t>
+  </si>
+  <si>
+    <t>% of Loans</t>
+  </si>
+  <si>
+    <t>Arrears Value (₦)</t>
+  </si>
+  <si>
+    <t>Outstanding Principal at Risk (₦)</t>
+  </si>
+  <si>
+    <t>% of Outstanding Principal</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>1-7</t>
+  </si>
+  <si>
+    <t>8-30</t>
+  </si>
+  <si>
+    <t>31-60</t>
+  </si>
+  <si>
+    <t>61-90</t>
+  </si>
+  <si>
+    <t>90+</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Exposure by Product &amp; Origination Month</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>Values = principal disbursed (₦), filtered by Reporting Date, Product, Channel and Customer Type above.</t>
+  </si>
+  <si>
+    <t>Actions Supported by These Results</t>
+  </si>
+  <si>
+    <t>1. Trigger early collections outreach at first delinquency (1–7 DPD), not just at 90+.</t>
+  </si>
+  <si>
+    <t>Every currently delinquent loan in the book has already crossed 90+ DPD — there is currently no population sitting in the 1–60 day buckets. That means the book's early-warning stage is effectively empty: loans appear to jump straight from Current to severely delinquent, most likely because collections only start once accounts are already very late. Add a structured outreach step (SMS/call) as soon as an instalment is 1–7 days overdue.</t>
+  </si>
+  <si>
+    <t>Owner:</t>
+  </si>
+  <si>
+    <t>Collections Team Lead</t>
+  </si>
+  <si>
+    <t>Monitoring metric:</t>
+  </si>
+  <si>
+    <t>Loan count and ₦ value in the 1–7, 8–30 and 31–60 DPD buckets (Dashboard delinquency table) — review weekly. If this population stays near zero after the process is live, it confirms loans are genuinely cured quickly; if it starts filling and 90+ volume falls, it shows the new step is catching cases before they become severely delinquent.</t>
+  </si>
+  <si>
+    <t>2. Reconcile the 3 loans with missing payment-amount data before reporting collection rate externally.</t>
+  </si>
+  <si>
+    <t>L015, L016 and L018 (₦435,600 of contractual exposure, ~15% of the book) have a payment_date recorded but no payment_amount in the source system, so this dashboard conservatively treats them as ₦0 collected. If payments were in fact received, both Amount Collected and Collection Rate are currently understated, and these three loans are overstated in the 90+ bucket.</t>
+  </si>
+  <si>
+    <t>Data/Systems Analyst (Loan Operations), with sign-off from Finance before external reporting</t>
+  </si>
+  <si>
+    <t>Count of Installment rows with a payment_date but blank payment_amount (Reconciliation tab, issue log row 4) — target zero before each external report; re-check portfolio Collection Rate once fixed.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="\₦#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -828,8 +949,69 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="8"/>
+      <color rgb="FF666666"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E78"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -846,6 +1028,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFDE7"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFDE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -878,7 +1090,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -978,6 +1190,62 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="167" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="168" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1104,6 +1372,1773 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Loan Count by DPD Bucket (units) — as of Reporting Date (cell C6 above)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Dashboard!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Loan Count (units)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]Dashboard!$B$20:$B$25</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Current</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1-7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8-30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31-60</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>61-90</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>90+</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Dashboard!$C$20:$C$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="356125320"/>
+        <c:axId val="356125712"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="356125320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>DPD bucket</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="356125712"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="356125712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="B3B3B3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Number of loans (count)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="356125320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Principal Disbursed by Product &amp; Origination Month (₦ Naira) — as of Reporting Date (cell C6 above)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Dashboard!$C$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Business Loan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]Dashboard!$B$30:$B$33</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2025-07</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025-08</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025-09</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2025-10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Dashboard!$C$30:$C$33</c:f>
+              <c:numCache>
+                <c:formatCode>\₦#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>530000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Dashboard!$D$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Personal Loan</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C0504D"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]Dashboard!$B$30:$B$33</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2025-07</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025-08</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025-09</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2025-10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Dashboard!$D$30:$D$33</c:f>
+              <c:numCache>
+                <c:formatCode>\₦#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>935000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Dashboard!$E$29</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Salary Advance</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9BBB59"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>[1]Dashboard!$B$30:$B$33</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2025-07</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2025-08</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025-09</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2025-10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[1]Dashboard!$E$30:$E$33</c:f>
+              <c:numCache>
+                <c:formatCode>\₦#,##0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>430000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>70000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>130000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="356127280"/>
+        <c:axId val="356128848"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="356127280"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Origination month</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="356128848"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="356128848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="B3B3B3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Principal disbursed (₦ Naira)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="\₦#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="B3B3B3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="356127280"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>61880</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>111280</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>61880</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>111130</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Dashboard"/>
+      <sheetName val="Metric Definitions"/>
+      <sheetName val="Reconciliation"/>
+      <sheetName val="Data - Customer"/>
+      <sheetName val="Data - Application"/>
+      <sheetName val="Data - Loan"/>
+      <sheetName val="Data - Installment"/>
+      <sheetName val="Calc - Installment"/>
+      <sheetName val="Calc - Loan Summary"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="19">
+          <cell r="C19" t="str">
+            <v>Loan Count (units)</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>Current</v>
+          </cell>
+          <cell r="C20">
+            <v>11</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>1-7</v>
+          </cell>
+          <cell r="C21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>8-30</v>
+          </cell>
+          <cell r="C22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>31-60</v>
+          </cell>
+          <cell r="C23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>61-90</v>
+          </cell>
+          <cell r="C24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>90+</v>
+          </cell>
+          <cell r="C25">
+            <v>9</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="C29" t="str">
+            <v>Business Loan</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="E29" t="str">
+            <v>Salary Advance</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="C30">
+            <v>530000</v>
+          </cell>
+          <cell r="D30">
+            <v>935000</v>
+          </cell>
+          <cell r="E30">
+            <v>430000</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>2025-08</v>
+          </cell>
+          <cell r="C31">
+            <v>0</v>
+          </cell>
+          <cell r="D31">
+            <v>0</v>
+          </cell>
+          <cell r="E31">
+            <v>70000</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>2025-09</v>
+          </cell>
+          <cell r="C32">
+            <v>110000</v>
+          </cell>
+          <cell r="D32">
+            <v>0</v>
+          </cell>
+          <cell r="E32">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>2025-10</v>
+          </cell>
+          <cell r="C33">
+            <v>0</v>
+          </cell>
+          <cell r="D33">
+            <v>0</v>
+          </cell>
+          <cell r="E33">
+            <v>130000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
+        <row r="5">
+          <cell r="C5" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E5" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H5">
+            <v>50000</v>
+          </cell>
+          <cell r="J5">
+            <v>1</v>
+          </cell>
+          <cell r="M5">
+            <v>0</v>
+          </cell>
+          <cell r="O5">
+            <v>0</v>
+          </cell>
+          <cell r="R5" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6" t="str">
+            <v>Salary Advance</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E6" t="str">
+            <v>Self-employed</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>2025-08</v>
+          </cell>
+          <cell r="H6">
+            <v>70000</v>
+          </cell>
+          <cell r="J6">
+            <v>1</v>
+          </cell>
+          <cell r="M6">
+            <v>0</v>
+          </cell>
+          <cell r="O6">
+            <v>8.5487172896137054E-11</v>
+          </cell>
+          <cell r="R6" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="C7" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E7" t="str">
+            <v>Business Owner</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H7">
+            <v>90000</v>
+          </cell>
+          <cell r="J7">
+            <v>1</v>
+          </cell>
+          <cell r="M7">
+            <v>61000.000000000102</v>
+          </cell>
+          <cell r="O7">
+            <v>57607.003891050575</v>
+          </cell>
+          <cell r="R7" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8" t="str">
+            <v>Business Loan</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E8" t="str">
+            <v>Salaried</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v>2025-09</v>
+          </cell>
+          <cell r="H8">
+            <v>110000</v>
+          </cell>
+          <cell r="J8">
+            <v>1</v>
+          </cell>
+          <cell r="M8">
+            <v>126200.0000000001</v>
+          </cell>
+          <cell r="O8">
+            <v>110000</v>
+          </cell>
+          <cell r="R8" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="C9" t="str">
+            <v>Salary Advance</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E9" t="str">
+            <v>Freelancer</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v>2025-10</v>
+          </cell>
+          <cell r="H9">
+            <v>130000</v>
+          </cell>
+          <cell r="J9">
+            <v>1</v>
+          </cell>
+          <cell r="M9">
+            <v>0</v>
+          </cell>
+          <cell r="O9">
+            <v>1.0103029524088925E-10</v>
+          </cell>
+          <cell r="R9" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10" t="str">
+            <v>Business Loan</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E10" t="str">
+            <v>Business Owner</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H10">
+            <v>150000</v>
+          </cell>
+          <cell r="J10">
+            <v>1</v>
+          </cell>
+          <cell r="M10">
+            <v>4.0745362639427185E-10</v>
+          </cell>
+          <cell r="O10">
+            <v>2.4980018054066022E-10</v>
+          </cell>
+          <cell r="R10" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="C11" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E11" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H11">
+            <v>170000</v>
+          </cell>
+          <cell r="J11">
+            <v>1</v>
+          </cell>
+          <cell r="M11">
+            <v>0</v>
+          </cell>
+          <cell r="O11">
+            <v>0</v>
+          </cell>
+          <cell r="R11" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12" t="str">
+            <v>Business Loan</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E12" t="str">
+            <v>Contractor</v>
+          </cell>
+          <cell r="G12" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H12">
+            <v>60000</v>
+          </cell>
+          <cell r="J12">
+            <v>1</v>
+          </cell>
+          <cell r="M12">
+            <v>0</v>
+          </cell>
+          <cell r="O12">
+            <v>8.659739592076221E-11</v>
+          </cell>
+          <cell r="R12" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>Salary Advance</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E13" t="str">
+            <v>Self-employed</v>
+          </cell>
+          <cell r="G13" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H13">
+            <v>80000</v>
+          </cell>
+          <cell r="J13">
+            <v>1</v>
+          </cell>
+          <cell r="M13">
+            <v>49066.666666666599</v>
+          </cell>
+          <cell r="O13">
+            <v>42852.983988355205</v>
+          </cell>
+          <cell r="R13" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E14" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H14">
+            <v>100000</v>
+          </cell>
+          <cell r="J14">
+            <v>1</v>
+          </cell>
+          <cell r="M14">
+            <v>114999.9999999999</v>
+          </cell>
+          <cell r="O14">
+            <v>100000</v>
+          </cell>
+          <cell r="R14" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="C15" t="str">
+            <v>Salary Advance</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E15" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H15">
+            <v>120000</v>
+          </cell>
+          <cell r="J15">
+            <v>1</v>
+          </cell>
+          <cell r="M15">
+            <v>0</v>
+          </cell>
+          <cell r="O15">
+            <v>0</v>
+          </cell>
+          <cell r="R15" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16" t="str">
+            <v>Business Loan</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E16" t="str">
+            <v>Self-employed</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H16">
+            <v>140000</v>
+          </cell>
+          <cell r="J16">
+            <v>1</v>
+          </cell>
+          <cell r="M16">
+            <v>4.0745362639427185E-10</v>
+          </cell>
+          <cell r="O16">
+            <v>2.4868995751603507E-10</v>
+          </cell>
+          <cell r="R16" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E17" t="str">
+            <v>Business Owner</v>
+          </cell>
+          <cell r="G17" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H17">
+            <v>160000</v>
+          </cell>
+          <cell r="J17">
+            <v>1</v>
+          </cell>
+          <cell r="M17">
+            <v>0</v>
+          </cell>
+          <cell r="O17">
+            <v>0</v>
+          </cell>
+          <cell r="R17" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18" t="str">
+            <v>Salary Advance</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E18" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="G18" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H18">
+            <v>180000</v>
+          </cell>
+          <cell r="J18">
+            <v>1</v>
+          </cell>
+          <cell r="M18">
+            <v>0</v>
+          </cell>
+          <cell r="O18">
+            <v>0</v>
+          </cell>
+          <cell r="R18" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="C19" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E19" t="str">
+            <v>Freelancer</v>
+          </cell>
+          <cell r="G19" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H19">
+            <v>200000</v>
+          </cell>
+          <cell r="J19">
+            <v>1</v>
+          </cell>
+          <cell r="M19">
+            <v>228999.99999999988</v>
+          </cell>
+          <cell r="O19">
+            <v>200000</v>
+          </cell>
+          <cell r="R19" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="C20" t="str">
+            <v>Business Loan</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E20" t="str">
+            <v>Business Owner</v>
+          </cell>
+          <cell r="G20" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H20">
+            <v>70000</v>
+          </cell>
+          <cell r="J20">
+            <v>1</v>
+          </cell>
+          <cell r="M20">
+            <v>80400</v>
+          </cell>
+          <cell r="O20">
+            <v>70000</v>
+          </cell>
+          <cell r="R20" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="C21" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E21" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="G21" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H21">
+            <v>90000</v>
+          </cell>
+          <cell r="J21">
+            <v>1</v>
+          </cell>
+          <cell r="M21">
+            <v>0</v>
+          </cell>
+          <cell r="O21">
+            <v>0</v>
+          </cell>
+          <cell r="R21" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="C22" t="str">
+            <v>Business Loan</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E22" t="str">
+            <v>Contractor</v>
+          </cell>
+          <cell r="G22" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H22">
+            <v>110000</v>
+          </cell>
+          <cell r="J22">
+            <v>1</v>
+          </cell>
+          <cell r="M22">
+            <v>126200.0000000001</v>
+          </cell>
+          <cell r="O22">
+            <v>110000</v>
+          </cell>
+          <cell r="R22" t="str">
+            <v>90+</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="C23" t="str">
+            <v>Salary Advance</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E23" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="G23" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H23">
+            <v>50000</v>
+          </cell>
+          <cell r="J23">
+            <v>1</v>
+          </cell>
+          <cell r="M23">
+            <v>0</v>
+          </cell>
+          <cell r="O23">
+            <v>0</v>
+          </cell>
+          <cell r="R23" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="C24" t="str">
+            <v>Personal Loan</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>Unknown</v>
+          </cell>
+          <cell r="E24" t="str">
+            <v>Employee</v>
+          </cell>
+          <cell r="G24" t="str">
+            <v>2025-07</v>
+          </cell>
+          <cell r="H24">
+            <v>75000</v>
+          </cell>
+          <cell r="J24">
+            <v>1</v>
+          </cell>
+          <cell r="M24">
+            <v>0</v>
+          </cell>
+          <cell r="O24">
+            <v>9.1593399531575415E-11</v>
+          </cell>
+          <cell r="R24" t="str">
+            <v>Current</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2029,265 +4064,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="22.1796875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="82.26953125" style="47" customWidth="1"/>
-    <col min="3" max="3" width="52.1796875" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="B1" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A2" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="B3" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="C4" s="46" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="42" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A6" s="42" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A7" s="42" t="s">
-        <v>206</v>
-      </c>
-      <c r="B7" s="43" t="s">
-        <v>207</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="42" t="s">
-        <v>209</v>
-      </c>
-      <c r="B8" s="43" t="s">
-        <v>210</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A10" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="43" t="s">
-        <v>215</v>
-      </c>
-      <c r="C10" s="46" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="43" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="46" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="B13" s="43" t="s">
-        <v>224</v>
-      </c>
-      <c r="C13" s="46" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A14" s="42" t="s">
-        <v>226</v>
-      </c>
-      <c r="B14" s="43" t="s">
-        <v>227</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="43" t="s">
-        <v>230</v>
-      </c>
-      <c r="C15" s="46" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>233</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="B17" s="43" t="s">
-        <v>236</v>
-      </c>
-      <c r="C17" s="46" t="s">
-        <v>237</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="33.36328125" style="2" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B2" s="2">
-        <v>20</v>
-      </c>
-      <c r="C2" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B3" s="2">
-        <v>60</v>
-      </c>
-      <c r="C3" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="26" x14ac:dyDescent="0.35">
-      <c r="A4" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="12">
-        <f>SUM(Loan!E2:E21)</f>
-        <v>2205000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -3044,7 +4820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4173,7 +5949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4954,7 +6730,7 @@
         <v>49533.333333333336</v>
       </c>
       <c r="H15" s="12">
-        <f t="shared" ref="H15:H16" si="9">MAX(0,D15-I15)</f>
+        <f t="shared" ref="H15" si="9">MAX(0,D15-I15)</f>
         <v>0</v>
       </c>
       <c r="I15" s="12">
@@ -7335,7 +9111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7473,4 +9249,1045 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="82.26953125" style="47" customWidth="1"/>
+    <col min="3" max="3" width="52.1796875" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A2" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A3" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="C3" s="46" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A6" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A7" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="46" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A10" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="C11" s="46" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="46" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A14" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="42" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="46" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="46" t="s">
+        <v>237</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.36328125" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="2">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B3" s="2">
+        <v>60</v>
+      </c>
+      <c r="C3" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A4" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="B4" s="12">
+        <f>SUM(Loan!E2:E21)</f>
+        <v>2205000</v>
+      </c>
+      <c r="C4" s="18">
+        <f>B4</f>
+        <v>2205000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A5" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="12">
+        <f>SUM(Loan!J2:J21)</f>
+        <v>2520300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="26" x14ac:dyDescent="0.35">
+      <c r="A6" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="C6" s="12">
+        <f>SUM(Installment!I33:I61)</f>
+        <v>2637400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U46"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3" style="48" customWidth="1"/>
+    <col min="2" max="15" width="15" style="48" customWidth="1"/>
+    <col min="16" max="16" width="10" style="48" customWidth="1"/>
+    <col min="21" max="21" width="1" style="48" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U1" s="49"/>
+    </row>
+    <row r="2" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="U2" s="49"/>
+    </row>
+    <row r="3" spans="2:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="51" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="52" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="54">
+        <v>46050</v>
+      </c>
+      <c r="D6" s="54"/>
+      <c r="F6" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+    </row>
+    <row r="7" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" s="56"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+    </row>
+    <row r="8" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="D8" s="56"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="55"/>
+    </row>
+    <row r="9" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="D9" s="56"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="55"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
+      <c r="L9" s="55"/>
+    </row>
+    <row r="11" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="52" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="51" t="str">
+        <f>"As of "&amp;TEXT($C$6,"dd mmm yyyy")&amp;"  |  Product: "&amp;$C$7&amp;"  |  Channel: "&amp;$C$8&amp;"  |  Customer Type: "&amp;$C$9</f>
+        <v>As of 28 Jan 2026  |  Product: All  |  Channel: All  |  Customer Type: All</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="L13" s="57"/>
+      <c r="M13" s="57"/>
+      <c r="N13" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="O13" s="57"/>
+      <c r="P13" s="57"/>
+      <c r="Q13" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="R13" s="57"/>
+      <c r="S13" s="57"/>
+    </row>
+    <row r="14" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="58">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0))</f>
+        <v>20</v>
+      </c>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*('[1]Calc - Loan Summary'!$O$5:$O$24&gt;0)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0))</f>
+        <v>13</v>
+      </c>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="59">
+        <f>SUM(Installment!H8:H61)</f>
+        <v>431666.66666666657</v>
+      </c>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="59">
+        <f>SUM(Installment!D2:D61)</f>
+        <v>2520299.9999999995</v>
+      </c>
+      <c r="L14" s="59"/>
+      <c r="M14" s="59"/>
+      <c r="N14" s="59">
+        <f>SUM(Installment!J2:J61)</f>
+        <v>3416466.666666667</v>
+      </c>
+      <c r="O14" s="59"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="60">
+        <f>IFERROR(N14/K14,0)</f>
+        <v>1.3555793622452357</v>
+      </c>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+    </row>
+    <row r="15" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="59"/>
+      <c r="L15" s="59"/>
+      <c r="M15" s="59"/>
+      <c r="N15" s="59"/>
+      <c r="O15" s="59"/>
+      <c r="P15" s="59"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="60"/>
+      <c r="S15" s="60"/>
+    </row>
+    <row r="16" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="59"/>
+      <c r="L16" s="59"/>
+      <c r="M16" s="59"/>
+      <c r="N16" s="59"/>
+      <c r="O16" s="59"/>
+      <c r="P16" s="59"/>
+      <c r="Q16" s="60"/>
+      <c r="R16" s="60"/>
+      <c r="S16" s="60"/>
+    </row>
+    <row r="18" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="52" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="C19" s="61" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>254</v>
+      </c>
+      <c r="E19" s="61" t="s">
+        <v>255</v>
+      </c>
+      <c r="F19" s="61" t="s">
+        <v>256</v>
+      </c>
+      <c r="G19" s="61" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="62" t="s">
+        <v>258</v>
+      </c>
+      <c r="C20" s="63">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B20))</f>
+        <v>11</v>
+      </c>
+      <c r="D20" s="64">
+        <f>IFERROR(C20/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E20" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B20)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B20)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
+        <v>3.6470826358936392E-10</v>
+      </c>
+      <c r="G20" s="64">
+        <f>IFERROR(F20/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
+        <v>5.2821056975290308E-16</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="62" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" s="63">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B21))</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="64">
+        <f>IFERROR(C21/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B21)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B21)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="64">
+        <f>IFERROR(F21/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="62" t="s">
+        <v>260</v>
+      </c>
+      <c r="C22" s="63">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B22))</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="64">
+        <f>IFERROR(C22/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B22)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B22)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="64">
+        <f>IFERROR(F22/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" s="63">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B23))</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="64">
+        <f>IFERROR(C23/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B23)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B23)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
+        <v>0</v>
+      </c>
+      <c r="G23" s="64">
+        <f>IFERROR(F23/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="66" t="s">
+        <v>262</v>
+      </c>
+      <c r="C24" s="67">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B24))</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="68">
+        <f>IFERROR(C24/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="69">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B24)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="69">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B24)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="68">
+        <f>IFERROR(F24/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="66" t="s">
+        <v>263</v>
+      </c>
+      <c r="C25" s="67">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B25))</f>
+        <v>9</v>
+      </c>
+      <c r="D25" s="68">
+        <f>IFERROR(C25/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
+        <v>0.45</v>
+      </c>
+      <c r="E25" s="69">
+        <f>SUM(Installment!K4:K61)</f>
+        <v>734866.66666666663</v>
+      </c>
+      <c r="F25" s="69">
+        <f>SUM(Table1[outstanding])</f>
+        <v>431666.66666666657</v>
+      </c>
+      <c r="G25" s="68">
+        <f>IFERROR(F25/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
+        <v>0.62518708432683279</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="70" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" s="70">
+        <f>SUM(C20:C25)</f>
+        <v>20</v>
+      </c>
+      <c r="D26" s="71">
+        <f>SUM(D20:D25)</f>
+        <v>1</v>
+      </c>
+      <c r="E26" s="72">
+        <f>SUM(E20:E25)</f>
+        <v>734866.66666666663</v>
+      </c>
+      <c r="F26" s="72">
+        <f>SUM(F20:F25)</f>
+        <v>431666.66666666692</v>
+      </c>
+      <c r="G26" s="71">
+        <f>SUM(G20:G25)</f>
+        <v>0.62518708432683334</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="52" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="61" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="62" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B30)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>530000</v>
+      </c>
+      <c r="D30" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B30)*('[1]Calc - Loan Summary'!$C$5:$C$24="Personal Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>935000</v>
+      </c>
+      <c r="E30" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B30)*('[1]Calc - Loan Summary'!$C$5:$C$24="Salary Advance")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>430000</v>
+      </c>
+      <c r="F30" s="73">
+        <f>SUM(C30:E30)</f>
+        <v>1895000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="62" t="s">
+        <v>267</v>
+      </c>
+      <c r="C31" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B31)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B31)*('[1]Calc - Loan Summary'!$C$5:$C$24="Personal Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B31)*('[1]Calc - Loan Summary'!$C$5:$C$24="Salary Advance")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>70000</v>
+      </c>
+      <c r="F31" s="73">
+        <f>SUM(C31:E31)</f>
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="62" t="s">
+        <v>268</v>
+      </c>
+      <c r="C32" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B32)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>110000</v>
+      </c>
+      <c r="D32" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B32)*('[1]Calc - Loan Summary'!$C$5:$C$24="Personal Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B32)*('[1]Calc - Loan Summary'!$C$5:$C$24="Salary Advance")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="73">
+        <f>SUM(C32:E32)</f>
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="62" t="s">
+        <v>269</v>
+      </c>
+      <c r="C33" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B33)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B33)*('[1]Calc - Loan Summary'!$C$5:$C$24="Personal Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="65">
+        <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B33)*('[1]Calc - Loan Summary'!$C$5:$C$24="Salary Advance")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
+        <v>130000</v>
+      </c>
+      <c r="F33" s="73">
+        <f>SUM(C33:E33)</f>
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="70" t="s">
+        <v>264</v>
+      </c>
+      <c r="C34" s="72">
+        <f>SUM(C30:C33)</f>
+        <v>640000</v>
+      </c>
+      <c r="D34" s="72">
+        <f>SUM(D30:D33)</f>
+        <v>935000</v>
+      </c>
+      <c r="E34" s="72">
+        <f>SUM(E30:E33)</f>
+        <v>630000</v>
+      </c>
+      <c r="F34" s="72">
+        <f>SUM(F30:F33)</f>
+        <v>2205000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="74" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="52" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="75" t="s">
+        <v>272</v>
+      </c>
+      <c r="C38" s="75"/>
+      <c r="D38" s="75"/>
+      <c r="E38" s="75"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="75"/>
+      <c r="L38" s="75"/>
+      <c r="M38" s="75"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="75"/>
+    </row>
+    <row r="39" spans="2:15" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="76" t="s">
+        <v>273</v>
+      </c>
+      <c r="C39" s="76"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="76"/>
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+      <c r="I39" s="76"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="76"/>
+      <c r="M39" s="76"/>
+      <c r="N39" s="76"/>
+      <c r="O39" s="76"/>
+    </row>
+    <row r="40" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="C40" s="76" t="s">
+        <v>275</v>
+      </c>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
+      <c r="I40" s="76"/>
+      <c r="J40" s="76"/>
+      <c r="K40" s="76"/>
+      <c r="L40" s="76"/>
+      <c r="M40" s="76"/>
+      <c r="N40" s="76"/>
+      <c r="O40" s="76"/>
+    </row>
+    <row r="41" spans="2:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="78" t="s">
+        <v>276</v>
+      </c>
+      <c r="C41" s="76" t="s">
+        <v>277</v>
+      </c>
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
+      <c r="J41" s="76"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="76"/>
+      <c r="M41" s="76"/>
+      <c r="N41" s="76"/>
+      <c r="O41" s="76"/>
+    </row>
+    <row r="42" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="79"/>
+    </row>
+    <row r="43" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="75" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43" s="75"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="75"/>
+      <c r="H43" s="75"/>
+      <c r="I43" s="75"/>
+      <c r="J43" s="75"/>
+      <c r="K43" s="75"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="75"/>
+      <c r="N43" s="75"/>
+      <c r="O43" s="75"/>
+    </row>
+    <row r="44" spans="2:15" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="76" t="s">
+        <v>279</v>
+      </c>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
+      <c r="I44" s="76"/>
+      <c r="J44" s="76"/>
+      <c r="K44" s="76"/>
+      <c r="L44" s="76"/>
+      <c r="M44" s="76"/>
+      <c r="N44" s="76"/>
+      <c r="O44" s="76"/>
+    </row>
+    <row r="45" spans="2:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="77" t="s">
+        <v>274</v>
+      </c>
+      <c r="C45" s="76" t="s">
+        <v>280</v>
+      </c>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="76"/>
+      <c r="I45" s="76"/>
+      <c r="J45" s="76"/>
+      <c r="K45" s="76"/>
+      <c r="L45" s="76"/>
+      <c r="M45" s="76"/>
+      <c r="N45" s="76"/>
+      <c r="O45" s="76"/>
+    </row>
+    <row r="46" spans="2:15" ht="54.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="77" t="s">
+        <v>276</v>
+      </c>
+      <c r="C46" s="76" t="s">
+        <v>281</v>
+      </c>
+      <c r="D46" s="76"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="76"/>
+      <c r="J46" s="76"/>
+      <c r="K46" s="76"/>
+      <c r="L46" s="76"/>
+      <c r="M46" s="76"/>
+      <c r="N46" s="76"/>
+      <c r="O46" s="76"/>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="C45:O45"/>
+    <mergeCell ref="C46:O46"/>
+    <mergeCell ref="B38:O38"/>
+    <mergeCell ref="B39:O39"/>
+    <mergeCell ref="C40:O40"/>
+    <mergeCell ref="C41:O41"/>
+    <mergeCell ref="B43:O43"/>
+    <mergeCell ref="B44:O44"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="B14:D16"/>
+    <mergeCell ref="E14:G16"/>
+    <mergeCell ref="H14:J16"/>
+    <mergeCell ref="K14:M16"/>
+    <mergeCell ref="N14:P16"/>
+    <mergeCell ref="Q14:S16"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:L9"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="C9">
+      <formula1>"All,Business Owner,Contractor,Employee,Freelancer,Salaried,Self-employed"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" sqref="C8">
+      <formula1>"All,Unknown"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" sqref="C7">
+      <formula1>"All,Business Loan,Personal Loan,Salary Advance"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="date" showErrorMessage="1" errorTitle="Invalid date" error="Enter a date between 2025-07-01 and 2027-12-31." sqref="C6">
+      <formula1>DATE(2025,7,1)</formula1>
+      <formula2>DATE(2027,12,31)</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/week_1/Synthetic Data.xlsx
+++ b/week_1/Synthetic Data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7450" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="4" r:id="rId1"/>
@@ -889,9 +889,9 @@
   <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="\₦#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="\₦#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -1197,23 +1197,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1221,25 +1204,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="167" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="168" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
@@ -1247,6 +1224,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1414,7 +1414,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1556,11 +1555,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="356125320"/>
-        <c:axId val="356125712"/>
+        <c:axId val="11162648"/>
+        <c:axId val="11165392"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="356125320"/>
+        <c:axId val="11162648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1592,7 +1591,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1627,7 +1625,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="356125712"/>
+        <c:crossAx val="11165392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1635,7 +1633,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="356125712"/>
+        <c:axId val="11165392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1676,7 +1674,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1711,7 +1708,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="356125320"/>
+        <c:crossAx val="11162648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1785,7 +1782,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2126,11 +2122,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="356127280"/>
-        <c:axId val="356128848"/>
+        <c:axId val="11160296"/>
+        <c:axId val="11158336"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="356127280"/>
+        <c:axId val="11160296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2162,7 +2158,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2197,7 +2192,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="356128848"/>
+        <c:crossAx val="11158336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2205,7 +2200,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="356128848"/>
+        <c:axId val="11158336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2246,7 +2241,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2281,7 +2275,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="356127280"/>
+        <c:crossAx val="11160296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2294,7 +2288,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9566,67 +9559,67 @@
       <c r="B6" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="77">
         <v>46050</v>
       </c>
-      <c r="D6" s="54"/>
-      <c r="F6" s="55" t="s">
+      <c r="D6" s="77"/>
+      <c r="F6" s="78" t="s">
         <v>249</v>
       </c>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="78"/>
     </row>
     <row r="7" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="79" t="s">
         <v>250</v>
       </c>
-      <c r="D7" s="56"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
+      <c r="D7" s="79"/>
+      <c r="F7" s="78"/>
+      <c r="G7" s="78"/>
+      <c r="H7" s="78"/>
+      <c r="I7" s="78"/>
+      <c r="J7" s="78"/>
+      <c r="K7" s="78"/>
+      <c r="L7" s="78"/>
     </row>
     <row r="8" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="53" t="s">
         <v>229</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="79" t="s">
         <v>250</v>
       </c>
-      <c r="D8" s="56"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="55"/>
+      <c r="D8" s="79"/>
+      <c r="F8" s="78"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="78"/>
+      <c r="I8" s="78"/>
+      <c r="J8" s="78"/>
+      <c r="K8" s="78"/>
+      <c r="L8" s="78"/>
     </row>
     <row r="9" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="53" t="s">
         <v>226</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="79" t="s">
         <v>250</v>
       </c>
-      <c r="D9" s="56"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
-      <c r="L9" s="55"/>
+      <c r="D9" s="79"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="78"/>
+      <c r="I9" s="78"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="78"/>
+      <c r="L9" s="78"/>
     </row>
     <row r="11" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="52" t="s">
@@ -9640,114 +9633,114 @@
       </c>
     </row>
     <row r="13" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="73" t="s">
         <v>194</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57" t="s">
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73" t="s">
         <v>197</v>
       </c>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57" t="s">
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="I13" s="57"/>
-      <c r="J13" s="57"/>
-      <c r="K13" s="57" t="s">
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73" t="s">
         <v>203</v>
       </c>
-      <c r="L13" s="57"/>
-      <c r="M13" s="57"/>
-      <c r="N13" s="57" t="s">
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73" t="s">
         <v>206</v>
       </c>
-      <c r="O13" s="57"/>
-      <c r="P13" s="57"/>
-      <c r="Q13" s="57" t="s">
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="73" t="s">
         <v>209</v>
       </c>
-      <c r="R13" s="57"/>
-      <c r="S13" s="57"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="73"/>
     </row>
     <row r="14" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="58">
+      <c r="B14" s="74">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0))</f>
         <v>20</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58">
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*('[1]Calc - Loan Summary'!$O$5:$O$24&gt;0)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0))</f>
         <v>13</v>
       </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="59">
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="75">
         <f>SUM(Installment!H8:H61)</f>
         <v>431666.66666666657</v>
       </c>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59">
+      <c r="I14" s="75"/>
+      <c r="J14" s="75"/>
+      <c r="K14" s="75">
         <f>SUM(Installment!D2:D61)</f>
         <v>2520299.9999999995</v>
       </c>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59"/>
-      <c r="N14" s="59">
+      <c r="L14" s="75"/>
+      <c r="M14" s="75"/>
+      <c r="N14" s="75">
         <f>SUM(Installment!J2:J61)</f>
         <v>3416466.666666667</v>
       </c>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="60">
+      <c r="O14" s="75"/>
+      <c r="P14" s="75"/>
+      <c r="Q14" s="76">
         <f>IFERROR(N14/K14,0)</f>
         <v>1.3555793622452357</v>
       </c>
-      <c r="R14" s="60"/>
-      <c r="S14" s="60"/>
+      <c r="R14" s="76"/>
+      <c r="S14" s="76"/>
     </row>
     <row r="15" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="59"/>
-      <c r="K15" s="59"/>
-      <c r="L15" s="59"/>
-      <c r="M15" s="59"/>
-      <c r="N15" s="59"/>
-      <c r="O15" s="59"/>
-      <c r="P15" s="59"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="60"/>
-      <c r="S15" s="60"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="75"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="75"/>
+      <c r="Q15" s="76"/>
+      <c r="R15" s="76"/>
+      <c r="S15" s="76"/>
     </row>
     <row r="16" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="59"/>
-      <c r="J16" s="59"/>
-      <c r="K16" s="59"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="59"/>
-      <c r="N16" s="59"/>
-      <c r="O16" s="59"/>
-      <c r="P16" s="59"/>
-      <c r="Q16" s="60"/>
-      <c r="R16" s="60"/>
-      <c r="S16" s="60"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="75"/>
+      <c r="I16" s="75"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="75"/>
+      <c r="M16" s="75"/>
+      <c r="N16" s="75"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="75"/>
+      <c r="Q16" s="76"/>
+      <c r="R16" s="76"/>
+      <c r="S16" s="76"/>
     </row>
     <row r="18" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="52" t="s">
@@ -9755,196 +9748,196 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="54" t="s">
         <v>220</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="D19" s="61" t="s">
+      <c r="D19" s="54" t="s">
         <v>254</v>
       </c>
-      <c r="E19" s="61" t="s">
+      <c r="E19" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="F19" s="61" t="s">
+      <c r="F19" s="54" t="s">
         <v>256</v>
       </c>
-      <c r="G19" s="61" t="s">
+      <c r="G19" s="54" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="62" t="s">
+      <c r="B20" s="55" t="s">
         <v>258</v>
       </c>
-      <c r="C20" s="63">
+      <c r="C20" s="56">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B20))</f>
         <v>11</v>
       </c>
-      <c r="D20" s="64">
+      <c r="D20" s="57">
         <f>IFERROR(C20/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
         <v>0.55000000000000004</v>
       </c>
-      <c r="E20" s="65">
+      <c r="E20" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B20)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="65">
+      <c r="F20" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B20)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
         <v>3.6470826358936392E-10</v>
       </c>
-      <c r="G20" s="64">
+      <c r="G20" s="57">
         <f>IFERROR(F20/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
         <v>5.2821056975290308E-16</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="55" t="s">
         <v>259</v>
       </c>
-      <c r="C21" s="63">
+      <c r="C21" s="56">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B21))</f>
         <v>0</v>
       </c>
-      <c r="D21" s="64">
+      <c r="D21" s="57">
         <f>IFERROR(C21/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="65">
+      <c r="E21" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B21)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
         <v>0</v>
       </c>
-      <c r="F21" s="65">
+      <c r="F21" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B21)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="64">
+      <c r="G21" s="57">
         <f>IFERROR(F21/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="62" t="s">
+      <c r="B22" s="55" t="s">
         <v>260</v>
       </c>
-      <c r="C22" s="63">
+      <c r="C22" s="56">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B22))</f>
         <v>0</v>
       </c>
-      <c r="D22" s="64">
+      <c r="D22" s="57">
         <f>IFERROR(C22/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="65">
+      <c r="E22" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B22)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="65">
+      <c r="F22" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B22)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="64">
+      <c r="G22" s="57">
         <f>IFERROR(F22/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="62" t="s">
+      <c r="B23" s="55" t="s">
         <v>261</v>
       </c>
-      <c r="C23" s="63">
+      <c r="C23" s="56">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B23))</f>
         <v>0</v>
       </c>
-      <c r="D23" s="64">
+      <c r="D23" s="57">
         <f>IFERROR(C23/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="65">
+      <c r="E23" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B23)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="65">
+      <c r="F23" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B23)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="64">
+      <c r="G23" s="57">
         <f>IFERROR(F23/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="59" t="s">
         <v>262</v>
       </c>
-      <c r="C24" s="67">
+      <c r="C24" s="60">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B24))</f>
         <v>0</v>
       </c>
-      <c r="D24" s="68">
+      <c r="D24" s="61">
         <f>IFERROR(C24/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="69">
+      <c r="E24" s="62">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B24)*'[1]Calc - Loan Summary'!$M$5:$M$24)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="69">
+      <c r="F24" s="62">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B24)*'[1]Calc - Loan Summary'!$O$5:$O$24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="68">
+      <c r="G24" s="61">
         <f>IFERROR(F24/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="C25" s="67">
+      <c r="C25" s="60">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$R$5:$R$24=$B25))</f>
         <v>9</v>
       </c>
-      <c r="D25" s="68">
+      <c r="D25" s="61">
         <f>IFERROR(C25/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)),0)</f>
         <v>0.45</v>
       </c>
-      <c r="E25" s="69">
+      <c r="E25" s="62">
         <f>SUM(Installment!K4:K61)</f>
         <v>734866.66666666663</v>
       </c>
-      <c r="F25" s="69">
+      <c r="F25" s="62">
         <f>SUM(Table1[outstanding])</f>
         <v>431666.66666666657</v>
       </c>
-      <c r="G25" s="68">
+      <c r="G25" s="61">
         <f>IFERROR(F25/SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*'[1]Calc - Loan Summary'!$O$5:$O$24),0)</f>
         <v>0.62518708432683279</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="63" t="s">
         <v>264</v>
       </c>
-      <c r="C26" s="70">
+      <c r="C26" s="63">
         <f>SUM(C20:C25)</f>
         <v>20</v>
       </c>
-      <c r="D26" s="71">
+      <c r="D26" s="64">
         <f>SUM(D20:D25)</f>
         <v>1</v>
       </c>
-      <c r="E26" s="72">
+      <c r="E26" s="65">
         <f>SUM(E20:E25)</f>
         <v>734866.66666666663</v>
       </c>
-      <c r="F26" s="72">
+      <c r="F26" s="65">
         <f>SUM(F20:F25)</f>
         <v>431666.66666666692</v>
       </c>
-      <c r="G26" s="71">
+      <c r="G26" s="64">
         <f>SUM(G20:G25)</f>
         <v>0.62518708432683334</v>
       </c>
@@ -9955,129 +9948,129 @@
       </c>
     </row>
     <row r="29" spans="2:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="61" t="s">
+      <c r="B29" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="D29" s="61" t="s">
+      <c r="D29" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="E29" s="61" t="s">
+      <c r="E29" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="F29" s="61" t="s">
+      <c r="F29" s="54" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="55" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="65">
+      <c r="C30" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B30)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>530000</v>
       </c>
-      <c r="D30" s="65">
+      <c r="D30" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B30)*('[1]Calc - Loan Summary'!$C$5:$C$24="Personal Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>935000</v>
       </c>
-      <c r="E30" s="65">
+      <c r="E30" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B30)*('[1]Calc - Loan Summary'!$C$5:$C$24="Salary Advance")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>430000</v>
       </c>
-      <c r="F30" s="73">
+      <c r="F30" s="66">
         <f>SUM(C30:E30)</f>
         <v>1895000</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="55" t="s">
         <v>267</v>
       </c>
-      <c r="C31" s="65">
+      <c r="C31" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B31)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="65">
+      <c r="D31" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B31)*('[1]Calc - Loan Summary'!$C$5:$C$24="Personal Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="65">
+      <c r="E31" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B31)*('[1]Calc - Loan Summary'!$C$5:$C$24="Salary Advance")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>70000</v>
       </c>
-      <c r="F31" s="73">
+      <c r="F31" s="66">
         <f>SUM(C31:E31)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="62" t="s">
+      <c r="B32" s="55" t="s">
         <v>268</v>
       </c>
-      <c r="C32" s="65">
+      <c r="C32" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B32)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>110000</v>
       </c>
-      <c r="D32" s="65">
+      <c r="D32" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B32)*('[1]Calc - Loan Summary'!$C$5:$C$24="Personal Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="65">
+      <c r="E32" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B32)*('[1]Calc - Loan Summary'!$C$5:$C$24="Salary Advance")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>0</v>
       </c>
-      <c r="F32" s="73">
+      <c r="F32" s="66">
         <f>SUM(C32:E32)</f>
         <v>110000</v>
       </c>
     </row>
     <row r="33" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="62" t="s">
+      <c r="B33" s="55" t="s">
         <v>269</v>
       </c>
-      <c r="C33" s="65">
+      <c r="C33" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B33)*('[1]Calc - Loan Summary'!$C$5:$C$24="Business Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>0</v>
       </c>
-      <c r="D33" s="65">
+      <c r="D33" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B33)*('[1]Calc - Loan Summary'!$C$5:$C$24="Personal Loan")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="65">
+      <c r="E33" s="58">
         <f>SUMPRODUCT(('[1]Calc - Loan Summary'!$J$5:$J$24=1)*(('[1]Calc - Loan Summary'!$C$5:$C$24=$C$7)+($C$7="All")&gt;0)*(('[1]Calc - Loan Summary'!$D$5:$D$24=$C$8)+($C$8="All")&gt;0)*(('[1]Calc - Loan Summary'!$E$5:$E$24=$C$9)+($C$9="All")&gt;0)*('[1]Calc - Loan Summary'!$G$5:$G$24=$B33)*('[1]Calc - Loan Summary'!$C$5:$C$24="Salary Advance")*'[1]Calc - Loan Summary'!$H$5:$H$24)</f>
         <v>130000</v>
       </c>
-      <c r="F33" s="73">
+      <c r="F33" s="66">
         <f>SUM(C33:E33)</f>
         <v>130000</v>
       </c>
     </row>
     <row r="34" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="70" t="s">
+      <c r="B34" s="63" t="s">
         <v>264</v>
       </c>
-      <c r="C34" s="72">
+      <c r="C34" s="65">
         <f>SUM(C30:C33)</f>
         <v>640000</v>
       </c>
-      <c r="D34" s="72">
+      <c r="D34" s="65">
         <f>SUM(D30:D33)</f>
         <v>935000</v>
       </c>
-      <c r="E34" s="72">
+      <c r="E34" s="65">
         <f>SUM(E30:E33)</f>
         <v>630000</v>
       </c>
-      <c r="F34" s="72">
+      <c r="F34" s="65">
         <f>SUM(F30:F33)</f>
         <v>2205000</v>
       </c>
     </row>
     <row r="35" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="74" t="s">
+      <c r="B35" s="67" t="s">
         <v>270</v>
       </c>
     </row>
@@ -10087,162 +10080,179 @@
       </c>
     </row>
     <row r="38" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="75" t="s">
+      <c r="B38" s="72" t="s">
         <v>272</v>
       </c>
-      <c r="C38" s="75"/>
-      <c r="D38" s="75"/>
-      <c r="E38" s="75"/>
-      <c r="F38" s="75"/>
-      <c r="G38" s="75"/>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="75"/>
-      <c r="L38" s="75"/>
-      <c r="M38" s="75"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="75"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="72"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="72"/>
+      <c r="H38" s="72"/>
+      <c r="I38" s="72"/>
+      <c r="J38" s="72"/>
+      <c r="K38" s="72"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="72"/>
     </row>
     <row r="39" spans="2:15" ht="84.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="76" t="s">
+      <c r="B39" s="71" t="s">
         <v>273</v>
       </c>
-      <c r="C39" s="76"/>
-      <c r="D39" s="76"/>
-      <c r="E39" s="76"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="76"/>
-      <c r="L39" s="76"/>
-      <c r="M39" s="76"/>
-      <c r="N39" s="76"/>
-      <c r="O39" s="76"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="71"/>
     </row>
     <row r="40" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="77" t="s">
+      <c r="B40" s="68" t="s">
         <v>274</v>
       </c>
-      <c r="C40" s="76" t="s">
+      <c r="C40" s="71" t="s">
         <v>275</v>
       </c>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
-      <c r="I40" s="76"/>
-      <c r="J40" s="76"/>
-      <c r="K40" s="76"/>
-      <c r="L40" s="76"/>
-      <c r="M40" s="76"/>
-      <c r="N40" s="76"/>
-      <c r="O40" s="76"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="71"/>
     </row>
     <row r="41" spans="2:15" ht="64.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="78" t="s">
+      <c r="B41" s="69" t="s">
         <v>276</v>
       </c>
-      <c r="C41" s="76" t="s">
+      <c r="C41" s="71" t="s">
         <v>277</v>
       </c>
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
-      <c r="I41" s="76"/>
-      <c r="J41" s="76"/>
-      <c r="K41" s="76"/>
-      <c r="L41" s="76"/>
-      <c r="M41" s="76"/>
-      <c r="N41" s="76"/>
-      <c r="O41" s="76"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="71"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="71"/>
+      <c r="L41" s="71"/>
+      <c r="M41" s="71"/>
+      <c r="N41" s="71"/>
+      <c r="O41" s="71"/>
     </row>
     <row r="42" spans="2:15" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="79"/>
+      <c r="B42" s="70"/>
     </row>
     <row r="43" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="75" t="s">
+      <c r="B43" s="72" t="s">
         <v>278</v>
       </c>
-      <c r="C43" s="75"/>
-      <c r="D43" s="75"/>
-      <c r="E43" s="75"/>
-      <c r="F43" s="75"/>
-      <c r="G43" s="75"/>
-      <c r="H43" s="75"/>
-      <c r="I43" s="75"/>
-      <c r="J43" s="75"/>
-      <c r="K43" s="75"/>
-      <c r="L43" s="75"/>
-      <c r="M43" s="75"/>
-      <c r="N43" s="75"/>
-      <c r="O43" s="75"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="72"/>
+      <c r="F43" s="72"/>
+      <c r="G43" s="72"/>
+      <c r="H43" s="72"/>
+      <c r="I43" s="72"/>
+      <c r="J43" s="72"/>
+      <c r="K43" s="72"/>
+      <c r="L43" s="72"/>
+      <c r="M43" s="72"/>
+      <c r="N43" s="72"/>
+      <c r="O43" s="72"/>
     </row>
     <row r="44" spans="2:15" ht="69.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="76" t="s">
+      <c r="B44" s="71" t="s">
         <v>279</v>
       </c>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
-      <c r="I44" s="76"/>
-      <c r="J44" s="76"/>
-      <c r="K44" s="76"/>
-      <c r="L44" s="76"/>
-      <c r="M44" s="76"/>
-      <c r="N44" s="76"/>
-      <c r="O44" s="76"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="71"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="71"/>
+      <c r="J44" s="71"/>
+      <c r="K44" s="71"/>
+      <c r="L44" s="71"/>
+      <c r="M44" s="71"/>
+      <c r="N44" s="71"/>
+      <c r="O44" s="71"/>
     </row>
     <row r="45" spans="2:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="77" t="s">
+      <c r="B45" s="68" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="76" t="s">
+      <c r="C45" s="71" t="s">
         <v>280</v>
       </c>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="76"/>
-      <c r="H45" s="76"/>
-      <c r="I45" s="76"/>
-      <c r="J45" s="76"/>
-      <c r="K45" s="76"/>
-      <c r="L45" s="76"/>
-      <c r="M45" s="76"/>
-      <c r="N45" s="76"/>
-      <c r="O45" s="76"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="71"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="71"/>
+      <c r="J45" s="71"/>
+      <c r="K45" s="71"/>
+      <c r="L45" s="71"/>
+      <c r="M45" s="71"/>
+      <c r="N45" s="71"/>
+      <c r="O45" s="71"/>
     </row>
     <row r="46" spans="2:15" ht="54.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="77" t="s">
+      <c r="B46" s="68" t="s">
         <v>276</v>
       </c>
-      <c r="C46" s="76" t="s">
+      <c r="C46" s="71" t="s">
         <v>281</v>
       </c>
-      <c r="D46" s="76"/>
-      <c r="E46" s="76"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="76"/>
-      <c r="H46" s="76"/>
-      <c r="I46" s="76"/>
-      <c r="J46" s="76"/>
-      <c r="K46" s="76"/>
-      <c r="L46" s="76"/>
-      <c r="M46" s="76"/>
-      <c r="N46" s="76"/>
-      <c r="O46" s="76"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="71"/>
+      <c r="H46" s="71"/>
+      <c r="I46" s="71"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="71"/>
+      <c r="L46" s="71"/>
+      <c r="M46" s="71"/>
+      <c r="N46" s="71"/>
+      <c r="O46" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:L9"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="B14:D16"/>
+    <mergeCell ref="E14:G16"/>
+    <mergeCell ref="H14:J16"/>
+    <mergeCell ref="K14:M16"/>
+    <mergeCell ref="N14:P16"/>
+    <mergeCell ref="Q14:S16"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:M13"/>
     <mergeCell ref="C45:O45"/>
     <mergeCell ref="C46:O46"/>
     <mergeCell ref="B38:O38"/>
@@ -10251,23 +10261,6 @@
     <mergeCell ref="C41:O41"/>
     <mergeCell ref="B43:O43"/>
     <mergeCell ref="B44:O44"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="B14:D16"/>
-    <mergeCell ref="E14:G16"/>
-    <mergeCell ref="H14:J16"/>
-    <mergeCell ref="K14:M16"/>
-    <mergeCell ref="N14:P16"/>
-    <mergeCell ref="Q14:S16"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F6:L9"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:M13"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" sqref="C9">
